--- a/output/Data and Chart Outputs/au_hydro_storage.xlsx
+++ b/output/Data and Chart Outputs/au_hydro_storage.xlsx
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -785,6 +785,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>Published file Last-Modified: not given</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>https://www.hydro.com.au/water/energy-in-storage</t>
         </is>

--- a/output/Data and Chart Outputs/au_hydro_storage.xlsx
+++ b/output/Data and Chart Outputs/au_hydro_storage.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tasmania hydro energy in storage (Hydro Tasmania) - water year (Oct-Sep), data to 2026-09-28</a:t>
+              <a:t>Tasmania hydro energy in storage (Hydro Tasmania) - water year (Oct-Sep), data to 2026-10-05</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,7 +190,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>5-year range (2020/21-2024/25)</v>
+            <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
             <a:solidFill>
@@ -764,7 +764,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tasmania (Hydro Tasmania's storages - the NEM's largest hydro system), weekly, 28 Sep 2020 to 28 Sep 2026. Snowy Hydro (NSW/VIC) does not publish a storage series.</t>
+          <t>Tasmania (Hydro Tasmania's storages - the NEM's largest hydro system), weekly, 28 Sep 2020 to 05 Oct 2026. Snowy Hydro (NSW/VIC) does not publish a storage series.</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>WY 2024/25</t>
+          <t>WY 2025/26</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>WY 2025/26</t>
+          <t>WY 2026/27</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -878,13 +878,13 @@
         <v>7160.39</v>
       </c>
       <c r="E2" t="n">
-        <v>6571.49</v>
+        <v>6751.83</v>
       </c>
       <c r="F2" t="n">
-        <v>6936.14</v>
+        <v>6919.79</v>
       </c>
       <c r="G2" t="n">
-        <v>6919.79</v>
+        <v>7307.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -908,13 +908,13 @@
         <v>7155.54</v>
       </c>
       <c r="E3" t="n">
-        <v>6572.03</v>
+        <v>6753.84</v>
       </c>
       <c r="F3" t="n">
-        <v>6938.52</v>
+        <v>6945.01</v>
       </c>
       <c r="G3" t="n">
-        <v>6945.01</v>
+        <v>7304.09</v>
       </c>
     </row>
     <row r="4">
@@ -933,13 +933,13 @@
         <v>7150.68</v>
       </c>
       <c r="E4" t="n">
-        <v>6571.81</v>
+        <v>6755.1</v>
       </c>
       <c r="F4" t="n">
-        <v>6940.9</v>
+        <v>6970.22</v>
       </c>
       <c r="G4" t="n">
-        <v>6970.22</v>
+        <v>7300.98</v>
       </c>
     </row>
     <row r="5">
@@ -958,13 +958,13 @@
         <v>7145.83</v>
       </c>
       <c r="E5" t="n">
-        <v>6573.34</v>
+        <v>6758.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6943.29</v>
+        <v>6995.44</v>
       </c>
       <c r="G5" t="n">
-        <v>6995.44</v>
+        <v>7297.86</v>
       </c>
     </row>
     <row r="6">
@@ -983,13 +983,13 @@
         <v>7167.17</v>
       </c>
       <c r="E6" t="n">
-        <v>6580.1</v>
+        <v>6766.33</v>
       </c>
       <c r="F6" t="n">
-        <v>6945.67</v>
+        <v>7020.66</v>
       </c>
       <c r="G6" t="n">
-        <v>7020.66</v>
+        <v>7294.75</v>
       </c>
     </row>
     <row r="7">
@@ -1008,12 +1008,9 @@
         <v>7188.52</v>
       </c>
       <c r="E7" t="n">
-        <v>6592.6</v>
+        <v>6774.57</v>
       </c>
       <c r="F7" t="n">
-        <v>6948.05</v>
-      </c>
-      <c r="G7" t="n">
         <v>7045.88</v>
       </c>
     </row>
@@ -1033,12 +1030,9 @@
         <v>7209.86</v>
       </c>
       <c r="E8" t="n">
-        <v>6605.1</v>
+        <v>6785.64</v>
       </c>
       <c r="F8" t="n">
-        <v>6950.43</v>
-      </c>
-      <c r="G8" t="n">
         <v>7085.28</v>
       </c>
     </row>
@@ -1058,12 +1052,9 @@
         <v>7231.2</v>
       </c>
       <c r="E9" t="n">
-        <v>6618.69</v>
+        <v>6797.8</v>
       </c>
       <c r="F9" t="n">
-        <v>6958.22</v>
-      </c>
-      <c r="G9" t="n">
         <v>7124.69</v>
       </c>
     </row>
@@ -1083,12 +1074,9 @@
         <v>7252.54</v>
       </c>
       <c r="E10" t="n">
-        <v>6632.27</v>
+        <v>6809.95</v>
       </c>
       <c r="F10" t="n">
-        <v>6966</v>
-      </c>
-      <c r="G10" t="n">
         <v>7164.09</v>
       </c>
     </row>
@@ -1108,12 +1096,9 @@
         <v>7273.89</v>
       </c>
       <c r="E11" t="n">
-        <v>6648.59</v>
+        <v>6824.84</v>
       </c>
       <c r="F11" t="n">
-        <v>6973.79</v>
-      </c>
-      <c r="G11" t="n">
         <v>7203.49</v>
       </c>
     </row>
@@ -1133,12 +1118,9 @@
         <v>7295.23</v>
       </c>
       <c r="E12" t="n">
-        <v>6676.01</v>
+        <v>6850.84</v>
       </c>
       <c r="F12" t="n">
-        <v>6981.57</v>
-      </c>
-      <c r="G12" t="n">
         <v>7242.89</v>
       </c>
     </row>
@@ -1158,12 +1140,9 @@
         <v>7305.51</v>
       </c>
       <c r="E13" t="n">
-        <v>6701.23</v>
+        <v>6874.63</v>
       </c>
       <c r="F13" t="n">
-        <v>6989.36</v>
-      </c>
-      <c r="G13" t="n">
         <v>7282.3</v>
       </c>
     </row>
@@ -1177,18 +1156,15 @@
         <v>5933.24</v>
       </c>
       <c r="C14" t="n">
-        <v>1382.55</v>
+        <v>1388.46</v>
       </c>
       <c r="D14" t="n">
-        <v>7315.79</v>
+        <v>7321.7</v>
       </c>
       <c r="E14" t="n">
-        <v>6720.76</v>
+        <v>6898.41</v>
       </c>
       <c r="F14" t="n">
-        <v>6997.14</v>
-      </c>
-      <c r="G14" t="n">
         <v>7321.7</v>
       </c>
     </row>
@@ -1202,18 +1178,15 @@
         <v>5988.83</v>
       </c>
       <c r="C15" t="n">
-        <v>1337.23</v>
+        <v>1337.74</v>
       </c>
       <c r="D15" t="n">
-        <v>7326.07</v>
+        <v>7326.57</v>
       </c>
       <c r="E15" t="n">
-        <v>6740.29</v>
+        <v>6915.29</v>
       </c>
       <c r="F15" t="n">
-        <v>7004.93</v>
-      </c>
-      <c r="G15" t="n">
         <v>7326.57</v>
       </c>
     </row>
@@ -1233,12 +1206,9 @@
         <v>7336.34</v>
       </c>
       <c r="E16" t="n">
-        <v>6757.67</v>
+        <v>6930.02</v>
       </c>
       <c r="F16" t="n">
-        <v>7001.97</v>
-      </c>
-      <c r="G16" t="n">
         <v>7331.45</v>
       </c>
     </row>
@@ -1258,12 +1228,9 @@
         <v>7346.62</v>
       </c>
       <c r="E17" t="n">
-        <v>6775.05</v>
+        <v>6944.75</v>
       </c>
       <c r="F17" t="n">
-        <v>6999</v>
-      </c>
-      <c r="G17" t="n">
         <v>7336.32</v>
       </c>
     </row>
@@ -1283,12 +1250,9 @@
         <v>7356.9</v>
       </c>
       <c r="E18" t="n">
-        <v>6791.81</v>
+        <v>6958.86</v>
       </c>
       <c r="F18" t="n">
-        <v>6996.04</v>
-      </c>
-      <c r="G18" t="n">
         <v>7341.2</v>
       </c>
     </row>
@@ -1308,12 +1272,9 @@
         <v>7367.18</v>
       </c>
       <c r="E19" t="n">
-        <v>6800.48</v>
+        <v>6964.89</v>
       </c>
       <c r="F19" t="n">
-        <v>6993.07</v>
-      </c>
-      <c r="G19" t="n">
         <v>7346.07</v>
       </c>
     </row>
@@ -1333,12 +1294,9 @@
         <v>7380.38</v>
       </c>
       <c r="E20" t="n">
-        <v>6809.74</v>
+        <v>6971.49</v>
       </c>
       <c r="F20" t="n">
-        <v>6990.11</v>
-      </c>
-      <c r="G20" t="n">
         <v>7350.95</v>
       </c>
     </row>
@@ -1358,12 +1316,9 @@
         <v>7393.57</v>
       </c>
       <c r="E21" t="n">
-        <v>6814.65</v>
+        <v>6978.1</v>
       </c>
       <c r="F21" t="n">
-        <v>6987.14</v>
-      </c>
-      <c r="G21" t="n">
         <v>7355.82</v>
       </c>
     </row>
@@ -1383,12 +1338,9 @@
         <v>7406.77</v>
       </c>
       <c r="E22" t="n">
-        <v>6819.56</v>
+        <v>6985.78</v>
       </c>
       <c r="F22" t="n">
-        <v>6984.18</v>
-      </c>
-      <c r="G22" t="n">
         <v>7366.06</v>
       </c>
     </row>
@@ -1408,12 +1360,9 @@
         <v>7419.96</v>
       </c>
       <c r="E23" t="n">
-        <v>6824.03</v>
+        <v>6993.02</v>
       </c>
       <c r="F23" t="n">
-        <v>6978.99</v>
-      </c>
-      <c r="G23" t="n">
         <v>7376.31</v>
       </c>
     </row>
@@ -1433,12 +1382,9 @@
         <v>7433.16</v>
       </c>
       <c r="E24" t="n">
-        <v>6828.5</v>
+        <v>7000.26</v>
       </c>
       <c r="F24" t="n">
-        <v>6973.8</v>
-      </c>
-      <c r="G24" t="n">
         <v>7386.55</v>
       </c>
     </row>
@@ -1458,12 +1404,9 @@
         <v>7446.35</v>
       </c>
       <c r="E25" t="n">
-        <v>6832.6</v>
+        <v>7007.13</v>
       </c>
       <c r="F25" t="n">
-        <v>6968.61</v>
-      </c>
-      <c r="G25" t="n">
         <v>7396.8</v>
       </c>
     </row>
@@ -1483,12 +1426,9 @@
         <v>7459.55</v>
       </c>
       <c r="E26" t="n">
-        <v>6837.62</v>
+        <v>7014.92</v>
       </c>
       <c r="F26" t="n">
-        <v>6963.43</v>
-      </c>
-      <c r="G26" t="n">
         <v>7407.04</v>
       </c>
     </row>
@@ -1508,12 +1448,9 @@
         <v>7482.96</v>
       </c>
       <c r="E27" t="n">
-        <v>6844.68</v>
+        <v>7024.75</v>
       </c>
       <c r="F27" t="n">
-        <v>6958.24</v>
-      </c>
-      <c r="G27" t="n">
         <v>7417.29</v>
       </c>
     </row>
@@ -1533,12 +1470,9 @@
         <v>7506.38</v>
       </c>
       <c r="E28" t="n">
-        <v>6850.37</v>
+        <v>7034.58</v>
       </c>
       <c r="F28" t="n">
-        <v>6953.05</v>
-      </c>
-      <c r="G28" t="n">
         <v>7427.53</v>
       </c>
     </row>
@@ -1558,12 +1492,9 @@
         <v>7529.79</v>
       </c>
       <c r="E29" t="n">
-        <v>6856.05</v>
+        <v>7041.02</v>
       </c>
       <c r="F29" t="n">
-        <v>6947.86</v>
-      </c>
-      <c r="G29" t="n">
         <v>7420.79</v>
       </c>
     </row>
@@ -1583,12 +1514,9 @@
         <v>7553.21</v>
       </c>
       <c r="E30" t="n">
-        <v>6861.54</v>
+        <v>7047.26</v>
       </c>
       <c r="F30" t="n">
-        <v>6941.71</v>
-      </c>
-      <c r="G30" t="n">
         <v>7414.04</v>
       </c>
     </row>
@@ -1608,12 +1536,9 @@
         <v>7576.62</v>
       </c>
       <c r="E31" t="n">
-        <v>6867.04</v>
+        <v>7053.5</v>
       </c>
       <c r="F31" t="n">
-        <v>6935.57</v>
-      </c>
-      <c r="G31" t="n">
         <v>7407.3</v>
       </c>
     </row>
@@ -1633,12 +1558,9 @@
         <v>7600.04</v>
       </c>
       <c r="E32" t="n">
-        <v>6871.84</v>
+        <v>7059.05</v>
       </c>
       <c r="F32" t="n">
-        <v>6929.42</v>
-      </c>
-      <c r="G32" t="n">
         <v>7400.55</v>
       </c>
     </row>
@@ -1658,12 +1580,9 @@
         <v>7623.45</v>
       </c>
       <c r="E33" t="n">
-        <v>6875.92</v>
+        <v>7063.89</v>
       </c>
       <c r="F33" t="n">
-        <v>6923.27</v>
-      </c>
-      <c r="G33" t="n">
         <v>7393.81</v>
       </c>
       <c r="H33" t="inlineStr">
@@ -1688,12 +1607,9 @@
         <v>7625.28</v>
       </c>
       <c r="E34" t="n">
-        <v>6875.69</v>
+        <v>7064.4</v>
       </c>
       <c r="F34" t="n">
-        <v>6917.12</v>
-      </c>
-      <c r="G34" t="n">
         <v>7387.06</v>
       </c>
     </row>
@@ -1704,21 +1620,18 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6433.89</v>
+        <v>6448.53</v>
       </c>
       <c r="C35" t="n">
-        <v>1193.22</v>
+        <v>1178.58</v>
       </c>
       <c r="D35" t="n">
         <v>7627.11</v>
       </c>
       <c r="E35" t="n">
-        <v>6875.63</v>
+        <v>7064.92</v>
       </c>
       <c r="F35" t="n">
-        <v>6910.98</v>
-      </c>
-      <c r="G35" t="n">
         <v>7380.32</v>
       </c>
     </row>
@@ -1729,21 +1642,18 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6424.28</v>
+        <v>6464.69</v>
       </c>
       <c r="C36" t="n">
-        <v>1204.66</v>
+        <v>1164.25</v>
       </c>
       <c r="D36" t="n">
         <v>7628.94</v>
       </c>
       <c r="E36" t="n">
-        <v>6875.58</v>
+        <v>7069.46</v>
       </c>
       <c r="F36" t="n">
-        <v>6904.83</v>
-      </c>
-      <c r="G36" t="n">
         <v>7393.68</v>
       </c>
     </row>
@@ -1754,21 +1664,18 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6414.68</v>
+        <v>6480.86</v>
       </c>
       <c r="C37" t="n">
-        <v>1216.09</v>
+        <v>1149.91</v>
       </c>
       <c r="D37" t="n">
         <v>7630.77</v>
       </c>
       <c r="E37" t="n">
-        <v>6875.19</v>
+        <v>7073.67</v>
       </c>
       <c r="F37" t="n">
-        <v>6897.04</v>
-      </c>
-      <c r="G37" t="n">
         <v>7407.04</v>
       </c>
     </row>
@@ -1779,21 +1686,18 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6405.08</v>
+        <v>6497.02</v>
       </c>
       <c r="C38" t="n">
-        <v>1227.52</v>
+        <v>1135.58</v>
       </c>
       <c r="D38" t="n">
         <v>7632.6</v>
       </c>
       <c r="E38" t="n">
-        <v>6874.81</v>
+        <v>7077.88</v>
       </c>
       <c r="F38" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="G38" t="n">
         <v>7420.4</v>
       </c>
     </row>
@@ -1804,21 +1708,18 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6395.48</v>
+        <v>6513.19</v>
       </c>
       <c r="C39" t="n">
-        <v>1238.95</v>
+        <v>1121.24</v>
       </c>
       <c r="D39" t="n">
         <v>7634.43</v>
       </c>
       <c r="E39" t="n">
-        <v>6872.84</v>
+        <v>7080.5</v>
       </c>
       <c r="F39" t="n">
-        <v>6881.46</v>
-      </c>
-      <c r="G39" t="n">
         <v>7433.77</v>
       </c>
     </row>
@@ -1829,21 +1730,18 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6385.87</v>
+        <v>6506.77</v>
       </c>
       <c r="C40" t="n">
-        <v>1250.39</v>
+        <v>1129.49</v>
       </c>
       <c r="D40" t="n">
         <v>7636.26</v>
       </c>
       <c r="E40" t="n">
-        <v>6866.36</v>
+        <v>7078.61</v>
       </c>
       <c r="F40" t="n">
-        <v>6873.67</v>
-      </c>
-      <c r="G40" t="n">
         <v>7447.13</v>
       </c>
     </row>
@@ -1854,21 +1752,18 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6376.27</v>
+        <v>6500.35</v>
       </c>
       <c r="C41" t="n">
-        <v>1253.98</v>
+        <v>1129.9</v>
       </c>
       <c r="D41" t="n">
         <v>7630.25</v>
       </c>
       <c r="E41" t="n">
-        <v>6858.31</v>
+        <v>7075.15</v>
       </c>
       <c r="F41" t="n">
-        <v>6865.88</v>
-      </c>
-      <c r="G41" t="n">
         <v>7460.49</v>
       </c>
     </row>
@@ -1879,21 +1774,18 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6365.63</v>
+        <v>6493.93</v>
       </c>
       <c r="C42" t="n">
-        <v>1258.62</v>
+        <v>1130.32</v>
       </c>
       <c r="D42" t="n">
         <v>7624.25</v>
       </c>
       <c r="E42" t="n">
-        <v>6850.05</v>
+        <v>7071.7</v>
       </c>
       <c r="F42" t="n">
-        <v>6858.09</v>
-      </c>
-      <c r="G42" t="n">
         <v>7473.85</v>
       </c>
     </row>
@@ -1904,21 +1796,18 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6354.99</v>
+        <v>6487.51</v>
       </c>
       <c r="C43" t="n">
-        <v>1263.25</v>
+        <v>1130.73</v>
       </c>
       <c r="D43" t="n">
         <v>7618.24</v>
       </c>
       <c r="E43" t="n">
-        <v>6841.79</v>
+        <v>7069.95</v>
       </c>
       <c r="F43" t="n">
-        <v>6850.3</v>
-      </c>
-      <c r="G43" t="n">
         <v>7495.76</v>
       </c>
     </row>
@@ -1929,21 +1818,18 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6344.35</v>
+        <v>6481.09</v>
       </c>
       <c r="C44" t="n">
-        <v>1267.89</v>
+        <v>1131.14</v>
       </c>
       <c r="D44" t="n">
         <v>7612.23</v>
       </c>
       <c r="E44" t="n">
-        <v>6832.85</v>
+        <v>7067.52</v>
       </c>
       <c r="F44" t="n">
-        <v>6839.09</v>
-      </c>
-      <c r="G44" t="n">
         <v>7517.68</v>
       </c>
     </row>
@@ -1954,21 +1840,18 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6333.7</v>
+        <v>6474.67</v>
       </c>
       <c r="C45" t="n">
-        <v>1272.52</v>
+        <v>1131.55</v>
       </c>
       <c r="D45" t="n">
         <v>7606.22</v>
       </c>
       <c r="E45" t="n">
-        <v>6823.91</v>
+        <v>7065.09</v>
       </c>
       <c r="F45" t="n">
-        <v>6827.89</v>
-      </c>
-      <c r="G45" t="n">
         <v>7539.59</v>
       </c>
     </row>
@@ -1979,21 +1862,18 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6323.06</v>
+        <v>6468.25</v>
       </c>
       <c r="C46" t="n">
-        <v>1277.15</v>
+        <v>1131.97</v>
       </c>
       <c r="D46" t="n">
         <v>7600.22</v>
       </c>
       <c r="E46" t="n">
-        <v>6813.69</v>
+        <v>7061.38</v>
       </c>
       <c r="F46" t="n">
-        <v>6816.68</v>
-      </c>
-      <c r="G46" t="n">
         <v>7561.5</v>
       </c>
     </row>
@@ -2004,21 +1884,18 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6312.42</v>
+        <v>6480.7</v>
       </c>
       <c r="C47" t="n">
-        <v>1281.79</v>
+        <v>1113.51</v>
       </c>
       <c r="D47" t="n">
         <v>7594.21</v>
       </c>
       <c r="E47" t="n">
-        <v>6807.25</v>
+        <v>7061.45</v>
       </c>
       <c r="F47" t="n">
-        <v>6805.48</v>
-      </c>
-      <c r="G47" t="n">
         <v>7583.41</v>
       </c>
     </row>
@@ -2029,21 +1906,18 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6301.78</v>
+        <v>6493.14</v>
       </c>
       <c r="C48" t="n">
-        <v>1301.6</v>
+        <v>1112.18</v>
       </c>
       <c r="D48" t="n">
-        <v>7603.38</v>
+        <v>7605.33</v>
       </c>
       <c r="E48" t="n">
-        <v>6803.84</v>
+        <v>7064.55</v>
       </c>
       <c r="F48" t="n">
-        <v>6794.27</v>
-      </c>
-      <c r="G48" t="n">
         <v>7605.33</v>
       </c>
     </row>
@@ -2054,21 +1928,18 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6293.05</v>
+        <v>6505.59</v>
       </c>
       <c r="C49" t="n">
-        <v>1319.51</v>
+        <v>1121.65</v>
       </c>
       <c r="D49" t="n">
-        <v>7612.56</v>
+        <v>7627.24</v>
       </c>
       <c r="E49" t="n">
-        <v>6800.82</v>
+        <v>7067.65</v>
       </c>
       <c r="F49" t="n">
-        <v>6783.07</v>
-      </c>
-      <c r="G49" t="n">
         <v>7627.24</v>
       </c>
     </row>
@@ -2079,21 +1950,18 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6284.31</v>
+        <v>6518.04</v>
       </c>
       <c r="C50" t="n">
-        <v>1337.42</v>
+        <v>1112.97</v>
       </c>
       <c r="D50" t="n">
-        <v>7621.73</v>
+        <v>7631</v>
       </c>
       <c r="E50" t="n">
-        <v>6797.79</v>
+        <v>7067.13</v>
       </c>
       <c r="F50" t="n">
-        <v>6771.86</v>
-      </c>
-      <c r="G50" t="n">
         <v>7631</v>
       </c>
     </row>
@@ -2104,21 +1972,18 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6275.58</v>
+        <v>6530.49</v>
       </c>
       <c r="C51" t="n">
-        <v>1355.32</v>
+        <v>1104.28</v>
       </c>
       <c r="D51" t="n">
-        <v>7630.9</v>
+        <v>7634.77</v>
       </c>
       <c r="E51" t="n">
-        <v>6795.91</v>
+        <v>7067.74</v>
       </c>
       <c r="F51" t="n">
-        <v>6766.37</v>
-      </c>
-      <c r="G51" t="n">
         <v>7634.77</v>
       </c>
     </row>
@@ -2129,21 +1994,18 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6266.84</v>
+        <v>6542.93</v>
       </c>
       <c r="C52" t="n">
-        <v>1373.23</v>
+        <v>1097.14</v>
       </c>
       <c r="D52" t="n">
         <v>7640.07</v>
       </c>
       <c r="E52" t="n">
-        <v>6794.02</v>
+        <v>7068.36</v>
       </c>
       <c r="F52" t="n">
-        <v>6760.88</v>
-      </c>
-      <c r="G52" t="n">
         <v>7638.53</v>
       </c>
     </row>
@@ -2154,21 +2016,18 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6258.11</v>
+        <v>6555.38</v>
       </c>
       <c r="C53" t="n">
-        <v>1391.14</v>
+        <v>1093.87</v>
       </c>
       <c r="D53" t="n">
         <v>7649.25</v>
       </c>
       <c r="E53" t="n">
-        <v>6793.37</v>
+        <v>7070.21</v>
       </c>
       <c r="F53" t="n">
-        <v>6755.39</v>
-      </c>
-      <c r="G53" t="n">
         <v>7642.3</v>
       </c>
     </row>
@@ -2179,21 +2038,18 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6249.37</v>
+        <v>6575.4</v>
       </c>
       <c r="C54" t="n">
-        <v>1409.05</v>
+        <v>1083.02</v>
       </c>
       <c r="D54" t="n">
         <v>7658.42</v>
       </c>
       <c r="E54" t="n">
-        <v>6794.24</v>
+        <v>7073.57</v>
       </c>
       <c r="F54" t="n">
-        <v>6749.89</v>
-      </c>
-      <c r="G54" t="n">
         <v>7646.06</v>
       </c>
     </row>
@@ -2204,21 +2060,18 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6240.64</v>
+        <v>6595.42</v>
       </c>
       <c r="C55" t="n">
-        <v>1406.05</v>
+        <v>1054.41</v>
       </c>
       <c r="D55" t="n">
-        <v>7646.69</v>
+        <v>7649.83</v>
       </c>
       <c r="E55" t="n">
-        <v>6790.92</v>
+        <v>7072.76</v>
       </c>
       <c r="F55" t="n">
-        <v>6744.4</v>
-      </c>
-      <c r="G55" t="n">
         <v>7649.83</v>
       </c>
     </row>
@@ -2229,21 +2082,18 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6225.54</v>
+        <v>6615.44</v>
       </c>
       <c r="C56" t="n">
-        <v>1409.42</v>
+        <v>1038.15</v>
       </c>
       <c r="D56" t="n">
-        <v>7634.96</v>
+        <v>7653.59</v>
       </c>
       <c r="E56" t="n">
-        <v>6786.33</v>
+        <v>7071.94</v>
       </c>
       <c r="F56" t="n">
-        <v>6738.91</v>
-      </c>
-      <c r="G56" t="n">
         <v>7653.59</v>
       </c>
     </row>
@@ -2254,21 +2104,18 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>6210.45</v>
+        <v>6635.45</v>
       </c>
       <c r="C57" t="n">
-        <v>1412.79</v>
+        <v>1025.35</v>
       </c>
       <c r="D57" t="n">
-        <v>7623.23</v>
+        <v>7660.8</v>
       </c>
       <c r="E57" t="n">
-        <v>6781.74</v>
+        <v>7071.81</v>
       </c>
       <c r="F57" t="n">
-        <v>6733.42</v>
-      </c>
-      <c r="G57" t="n">
         <v>7660.8</v>
       </c>
     </row>
@@ -2279,21 +2126,18 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6195.35</v>
+        <v>6655.47</v>
       </c>
       <c r="C58" t="n">
-        <v>1416.16</v>
+        <v>1012.54</v>
       </c>
       <c r="D58" t="n">
-        <v>7611.51</v>
+        <v>7668.01</v>
       </c>
       <c r="E58" t="n">
-        <v>6779.14</v>
+        <v>7073.67</v>
       </c>
       <c r="F58" t="n">
-        <v>6737.86</v>
-      </c>
-      <c r="G58" t="n">
         <v>7668.01</v>
       </c>
     </row>
@@ -2304,21 +2148,18 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6180.25</v>
+        <v>6675.49</v>
       </c>
       <c r="C59" t="n">
-        <v>1419.53</v>
+        <v>999.73</v>
       </c>
       <c r="D59" t="n">
-        <v>7599.78</v>
+        <v>7675.22</v>
       </c>
       <c r="E59" t="n">
-        <v>6776.54</v>
+        <v>7075.53</v>
       </c>
       <c r="F59" t="n">
-        <v>6742.31</v>
-      </c>
-      <c r="G59" t="n">
         <v>7675.22</v>
       </c>
     </row>
@@ -2329,21 +2170,18 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6165.15</v>
+        <v>6673.87</v>
       </c>
       <c r="C60" t="n">
-        <v>1422.89</v>
+        <v>1008.57</v>
       </c>
       <c r="D60" t="n">
-        <v>7588.05</v>
+        <v>7682.44</v>
       </c>
       <c r="E60" t="n">
-        <v>6773.87</v>
+        <v>7077.32</v>
       </c>
       <c r="F60" t="n">
-        <v>6746.75</v>
-      </c>
-      <c r="G60" t="n">
         <v>7682.44</v>
       </c>
     </row>
@@ -2354,21 +2192,18 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6150.06</v>
+        <v>6662.87</v>
       </c>
       <c r="C61" t="n">
-        <v>1426.26</v>
+        <v>1026.78</v>
       </c>
       <c r="D61" t="n">
-        <v>7576.32</v>
+        <v>7689.65</v>
       </c>
       <c r="E61" t="n">
-        <v>6767.15</v>
+        <v>7075.06</v>
       </c>
       <c r="F61" t="n">
-        <v>6751.2</v>
-      </c>
-      <c r="G61" t="n">
         <v>7689.65</v>
       </c>
     </row>
@@ -2379,21 +2214,18 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6134.96</v>
+        <v>6651.87</v>
       </c>
       <c r="C62" t="n">
-        <v>1425.22</v>
+        <v>1044.99</v>
       </c>
       <c r="D62" t="n">
-        <v>7560.18</v>
+        <v>7696.86</v>
       </c>
       <c r="E62" t="n">
-        <v>6759.54</v>
+        <v>7071.92</v>
       </c>
       <c r="F62" t="n">
-        <v>6755.64</v>
-      </c>
-      <c r="G62" t="n">
         <v>7696.86</v>
       </c>
     </row>
@@ -2404,21 +2236,18 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6130.85</v>
+        <v>6640.87</v>
       </c>
       <c r="C63" t="n">
-        <v>1413.18</v>
+        <v>1063.2</v>
       </c>
       <c r="D63" t="n">
-        <v>7544.04</v>
+        <v>7704.07</v>
       </c>
       <c r="E63" t="n">
-        <v>6754.14</v>
+        <v>7068.78</v>
       </c>
       <c r="F63" t="n">
-        <v>6760.09</v>
-      </c>
-      <c r="G63" t="n">
         <v>7704.07</v>
       </c>
       <c r="H63" t="inlineStr">
@@ -2434,21 +2263,18 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6126.75</v>
+        <v>6629.87</v>
       </c>
       <c r="C64" t="n">
-        <v>1401.15</v>
+        <v>1069.74</v>
       </c>
       <c r="D64" t="n">
-        <v>7527.9</v>
+        <v>7699.61</v>
       </c>
       <c r="E64" t="n">
-        <v>6748.73</v>
+        <v>7063.3</v>
       </c>
       <c r="F64" t="n">
-        <v>6764.53</v>
-      </c>
-      <c r="G64" t="n">
         <v>7699.61</v>
       </c>
     </row>
@@ -2459,21 +2285,18 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6122.64</v>
+        <v>6618.87</v>
       </c>
       <c r="C65" t="n">
-        <v>1389.11</v>
+        <v>1076.28</v>
       </c>
       <c r="D65" t="n">
-        <v>7511.75</v>
+        <v>7695.15</v>
       </c>
       <c r="E65" t="n">
-        <v>6745.9</v>
+        <v>7060.4</v>
       </c>
       <c r="F65" t="n">
-        <v>6781.82</v>
-      </c>
-      <c r="G65" t="n">
         <v>7695.15</v>
       </c>
     </row>
@@ -2484,21 +2307,18 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6118.54</v>
+        <v>6607.87</v>
       </c>
       <c r="C66" t="n">
-        <v>1377.08</v>
+        <v>1082.82</v>
       </c>
       <c r="D66" t="n">
-        <v>7495.61</v>
+        <v>7690.69</v>
       </c>
       <c r="E66" t="n">
-        <v>6743.06</v>
+        <v>7057.49</v>
       </c>
       <c r="F66" t="n">
-        <v>6799.11</v>
-      </c>
-      <c r="G66" t="n">
         <v>7690.69</v>
       </c>
     </row>
@@ -2509,21 +2329,18 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6114.43</v>
+        <v>6591.31</v>
       </c>
       <c r="C67" t="n">
-        <v>1365.04</v>
+        <v>1094.92</v>
       </c>
       <c r="D67" t="n">
-        <v>7479.47</v>
+        <v>7686.23</v>
       </c>
       <c r="E67" t="n">
-        <v>6739.11</v>
+        <v>7053.47</v>
       </c>
       <c r="F67" t="n">
-        <v>6816.4</v>
-      </c>
-      <c r="G67" t="n">
         <v>7686.23</v>
       </c>
     </row>
@@ -2534,21 +2351,18 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6110.33</v>
+        <v>6574.74</v>
       </c>
       <c r="C68" t="n">
-        <v>1353</v>
+        <v>1107.03</v>
       </c>
       <c r="D68" t="n">
-        <v>7463.33</v>
+        <v>7681.77</v>
       </c>
       <c r="E68" t="n">
-        <v>6733.41</v>
+        <v>7047.69</v>
       </c>
       <c r="F68" t="n">
-        <v>6833.7</v>
-      </c>
-      <c r="G68" t="n">
         <v>7681.77</v>
       </c>
     </row>
@@ -2559,21 +2373,18 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6106.22</v>
+        <v>6558.18</v>
       </c>
       <c r="C69" t="n">
-        <v>1339.55</v>
+        <v>1119.13</v>
       </c>
       <c r="D69" t="n">
-        <v>7445.77</v>
+        <v>7677.31</v>
       </c>
       <c r="E69" t="n">
-        <v>6727.41</v>
+        <v>7041.63</v>
       </c>
       <c r="F69" t="n">
-        <v>6850.99</v>
-      </c>
-      <c r="G69" t="n">
         <v>7677.31</v>
       </c>
     </row>
@@ -2584,21 +2395,18 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6110.84</v>
+        <v>6541.62</v>
       </c>
       <c r="C70" t="n">
-        <v>1317.37</v>
+        <v>1131.23</v>
       </c>
       <c r="D70" t="n">
-        <v>7428.21</v>
+        <v>7672.85</v>
       </c>
       <c r="E70" t="n">
-        <v>6723.17</v>
+        <v>7035.57</v>
       </c>
       <c r="F70" t="n">
-        <v>6868.28</v>
-      </c>
-      <c r="G70" t="n">
         <v>7672.85</v>
       </c>
     </row>
@@ -2609,21 +2417,18 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6115.46</v>
+        <v>6525.06</v>
       </c>
       <c r="C71" t="n">
-        <v>1295.19</v>
+        <v>1149.72</v>
       </c>
       <c r="D71" t="n">
-        <v>7410.65</v>
+        <v>7674.78</v>
       </c>
       <c r="E71" t="n">
-        <v>6718.92</v>
+        <v>7030.79</v>
       </c>
       <c r="F71" t="n">
-        <v>6885.57</v>
-      </c>
-      <c r="G71" t="n">
         <v>7674.78</v>
       </c>
     </row>
@@ -2634,21 +2439,18 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6120.08</v>
+        <v>6508.49</v>
       </c>
       <c r="C72" t="n">
-        <v>1273.01</v>
+        <v>1168.21</v>
       </c>
       <c r="D72" t="n">
-        <v>7393.09</v>
+        <v>7676.71</v>
       </c>
       <c r="E72" t="n">
-        <v>6712.02</v>
+        <v>7023.35</v>
       </c>
       <c r="F72" t="n">
-        <v>6889.58</v>
-      </c>
-      <c r="G72" t="n">
         <v>7676.71</v>
       </c>
     </row>
@@ -2659,21 +2461,18 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6124.69</v>
+        <v>6491.93</v>
       </c>
       <c r="C73" t="n">
-        <v>1250.84</v>
+        <v>1186.71</v>
       </c>
       <c r="D73" t="n">
-        <v>7375.53</v>
+        <v>7678.64</v>
       </c>
       <c r="E73" t="n">
-        <v>6705.12</v>
+        <v>7015.91</v>
       </c>
       <c r="F73" t="n">
-        <v>6893.59</v>
-      </c>
-      <c r="G73" t="n">
         <v>7678.64</v>
       </c>
     </row>
@@ -2684,21 +2483,18 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6129.31</v>
+        <v>6487.22</v>
       </c>
       <c r="C74" t="n">
-        <v>1228.66</v>
+        <v>1193.35</v>
       </c>
       <c r="D74" t="n">
-        <v>7357.97</v>
+        <v>7680.56</v>
       </c>
       <c r="E74" t="n">
-        <v>6700.59</v>
+        <v>7010.84</v>
       </c>
       <c r="F74" t="n">
-        <v>6897.6</v>
-      </c>
-      <c r="G74" t="n">
         <v>7680.56</v>
       </c>
     </row>
@@ -2709,21 +2505,18 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6133.93</v>
+        <v>6482.5</v>
       </c>
       <c r="C75" t="n">
-        <v>1206.48</v>
+        <v>1199.99</v>
       </c>
       <c r="D75" t="n">
-        <v>7340.41</v>
+        <v>7682.49</v>
       </c>
       <c r="E75" t="n">
-        <v>6699.47</v>
+        <v>7009.18</v>
       </c>
       <c r="F75" t="n">
-        <v>6901.61</v>
-      </c>
-      <c r="G75" t="n">
         <v>7682.49</v>
       </c>
     </row>
@@ -2734,21 +2527,18 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6138.55</v>
+        <v>6477.79</v>
       </c>
       <c r="C76" t="n">
-        <v>1180.6</v>
+        <v>1206.63</v>
       </c>
       <c r="D76" t="n">
-        <v>7319.15</v>
+        <v>7684.42</v>
       </c>
       <c r="E76" t="n">
-        <v>6697.62</v>
+        <v>7006.79</v>
       </c>
       <c r="F76" t="n">
-        <v>6905.62</v>
-      </c>
-      <c r="G76" t="n">
         <v>7684.42</v>
       </c>
     </row>
@@ -2759,21 +2549,18 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6122.98</v>
+        <v>6473.08</v>
       </c>
       <c r="C77" t="n">
-        <v>1174.91</v>
+        <v>1213.27</v>
       </c>
       <c r="D77" t="n">
-        <v>7297.89</v>
+        <v>7686.35</v>
       </c>
       <c r="E77" t="n">
-        <v>6691.73</v>
+        <v>7004.4</v>
       </c>
       <c r="F77" t="n">
-        <v>6909.63</v>
-      </c>
-      <c r="G77" t="n">
         <v>7686.35</v>
       </c>
     </row>
@@ -2784,21 +2571,18 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6107.41</v>
+        <v>6468.37</v>
       </c>
       <c r="C78" t="n">
-        <v>1169.21</v>
+        <v>1214.75</v>
       </c>
       <c r="D78" t="n">
-        <v>7276.63</v>
+        <v>7683.12</v>
       </c>
       <c r="E78" t="n">
-        <v>6685.83</v>
+        <v>7000.97</v>
       </c>
       <c r="F78" t="n">
-        <v>6913.64</v>
-      </c>
-      <c r="G78" t="n">
         <v>7683.12</v>
       </c>
     </row>
@@ -2809,21 +2593,18 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6091.84</v>
+        <v>6463.65</v>
       </c>
       <c r="C79" t="n">
-        <v>1163.52</v>
+        <v>1216.23</v>
       </c>
       <c r="D79" t="n">
-        <v>7255.36</v>
+        <v>7679.88</v>
       </c>
       <c r="E79" t="n">
-        <v>6678.74</v>
+        <v>6996.35</v>
       </c>
       <c r="F79" t="n">
-        <v>6911.65</v>
-      </c>
-      <c r="G79" t="n">
         <v>7679.88</v>
       </c>
     </row>
@@ -2834,21 +2615,18 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6076.28</v>
+        <v>6458.94</v>
       </c>
       <c r="C80" t="n">
-        <v>1157.83</v>
+        <v>1217.71</v>
       </c>
       <c r="D80" t="n">
-        <v>7234.1</v>
+        <v>7676.65</v>
       </c>
       <c r="E80" t="n">
-        <v>6671.65</v>
+        <v>6991.73</v>
       </c>
       <c r="F80" t="n">
-        <v>6909.67</v>
-      </c>
-      <c r="G80" t="n">
         <v>7676.65</v>
       </c>
     </row>
@@ -2859,21 +2637,18 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6060.71</v>
+        <v>6450.78</v>
       </c>
       <c r="C81" t="n">
-        <v>1152.13</v>
+        <v>1222.64</v>
       </c>
       <c r="D81" t="n">
-        <v>7212.84</v>
+        <v>7673.42</v>
       </c>
       <c r="E81" t="n">
-        <v>6663.87</v>
+        <v>6986.41</v>
       </c>
       <c r="F81" t="n">
-        <v>6907.68</v>
-      </c>
-      <c r="G81" t="n">
         <v>7673.42</v>
       </c>
     </row>
@@ -2884,21 +2659,18 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6045.14</v>
+        <v>6442.62</v>
       </c>
       <c r="C82" t="n">
-        <v>1146.44</v>
+        <v>1227.57</v>
       </c>
       <c r="D82" t="n">
-        <v>7191.58</v>
+        <v>7670.19</v>
       </c>
       <c r="E82" t="n">
-        <v>6651.65</v>
+        <v>6976.66</v>
       </c>
       <c r="F82" t="n">
-        <v>6905.69</v>
-      </c>
-      <c r="G82" t="n">
         <v>7670.19</v>
       </c>
     </row>
@@ -2909,21 +2681,18 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6029.57</v>
+        <v>6434.46</v>
       </c>
       <c r="C83" t="n">
-        <v>1148.03</v>
+        <v>1232.49</v>
       </c>
       <c r="D83" t="n">
-        <v>7177.6</v>
+        <v>7666.95</v>
       </c>
       <c r="E83" t="n">
-        <v>6640.88</v>
+        <v>6968.36</v>
       </c>
       <c r="F83" t="n">
-        <v>6903.7</v>
-      </c>
-      <c r="G83" t="n">
         <v>7666.95</v>
       </c>
     </row>
@@ -2934,21 +2703,18 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6023.34</v>
+        <v>6426.3</v>
       </c>
       <c r="C84" t="n">
-        <v>1140.28</v>
+        <v>1237.42</v>
       </c>
       <c r="D84" t="n">
-        <v>7163.63</v>
+        <v>7663.72</v>
       </c>
       <c r="E84" t="n">
-        <v>6631.98</v>
+        <v>6960.06</v>
       </c>
       <c r="F84" t="n">
-        <v>6901.72</v>
-      </c>
-      <c r="G84" t="n">
         <v>7663.72</v>
       </c>
     </row>
@@ -2959,21 +2725,18 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6017.12</v>
+        <v>6418.14</v>
       </c>
       <c r="C85" t="n">
-        <v>1132.53</v>
+        <v>1257.95</v>
       </c>
       <c r="D85" t="n">
-        <v>7149.65</v>
+        <v>7676.09</v>
       </c>
       <c r="E85" t="n">
-        <v>6623.09</v>
+        <v>6954.88</v>
       </c>
       <c r="F85" t="n">
-        <v>6899.73</v>
-      </c>
-      <c r="G85" t="n">
         <v>7676.09</v>
       </c>
     </row>
@@ -2984,21 +2747,18 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6010.89</v>
+        <v>6409.98</v>
       </c>
       <c r="C86" t="n">
-        <v>1124.78</v>
+        <v>1278.48</v>
       </c>
       <c r="D86" t="n">
-        <v>7135.68</v>
+        <v>7688.46</v>
       </c>
       <c r="E86" t="n">
-        <v>6614.84</v>
+        <v>6950.36</v>
       </c>
       <c r="F86" t="n">
-        <v>6901.01</v>
-      </c>
-      <c r="G86" t="n">
         <v>7688.46</v>
       </c>
     </row>
@@ -3009,21 +2769,18 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6004.67</v>
+        <v>6401.82</v>
       </c>
       <c r="C87" t="n">
-        <v>1117.03</v>
+        <v>1299.01</v>
       </c>
       <c r="D87" t="n">
-        <v>7121.7</v>
+        <v>7700.83</v>
       </c>
       <c r="E87" t="n">
-        <v>6606.6</v>
+        <v>6945.84</v>
       </c>
       <c r="F87" t="n">
-        <v>6902.3</v>
-      </c>
-      <c r="G87" t="n">
         <v>7700.83</v>
       </c>
     </row>
@@ -3034,21 +2791,18 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>5998.44</v>
+        <v>6391.7</v>
       </c>
       <c r="C88" t="n">
-        <v>1109.28</v>
+        <v>1321.51</v>
       </c>
       <c r="D88" t="n">
-        <v>7107.73</v>
+        <v>7713.21</v>
       </c>
       <c r="E88" t="n">
-        <v>6597.97</v>
+        <v>6940.92</v>
       </c>
       <c r="F88" t="n">
-        <v>6903.58</v>
-      </c>
-      <c r="G88" t="n">
         <v>7713.21</v>
       </c>
     </row>
@@ -3059,21 +2813,18 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5992.22</v>
+        <v>6381.58</v>
       </c>
       <c r="C89" t="n">
-        <v>1101.53</v>
+        <v>1344</v>
       </c>
       <c r="D89" t="n">
-        <v>7093.75</v>
+        <v>7725.58</v>
       </c>
       <c r="E89" t="n">
-        <v>6589.44</v>
+        <v>6936.11</v>
       </c>
       <c r="F89" t="n">
-        <v>6904.86</v>
-      </c>
-      <c r="G89" t="n">
         <v>7725.58</v>
       </c>
     </row>
@@ -3084,21 +2835,18 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5985.99</v>
+        <v>6371.46</v>
       </c>
       <c r="C90" t="n">
-        <v>1084.56</v>
+        <v>1366.49</v>
       </c>
       <c r="D90" t="n">
-        <v>7070.55</v>
+        <v>7737.95</v>
       </c>
       <c r="E90" t="n">
-        <v>6579.06</v>
+        <v>6929.46</v>
       </c>
       <c r="F90" t="n">
-        <v>6906.14</v>
-      </c>
-      <c r="G90" t="n">
         <v>7737.95</v>
       </c>
     </row>
@@ -3109,21 +2857,18 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5980.13</v>
+        <v>6361.33</v>
       </c>
       <c r="C91" t="n">
-        <v>1067.22</v>
+        <v>1388.99</v>
       </c>
       <c r="D91" t="n">
-        <v>7047.36</v>
+        <v>7750.32</v>
       </c>
       <c r="E91" t="n">
-        <v>6568.77</v>
+        <v>6922.8</v>
       </c>
       <c r="F91" t="n">
-        <v>6907.43</v>
-      </c>
-      <c r="G91" t="n">
         <v>7750.32</v>
       </c>
     </row>
@@ -3134,21 +2879,18 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5974.28</v>
+        <v>6351.21</v>
       </c>
       <c r="C92" t="n">
-        <v>1049.88</v>
+        <v>1388.33</v>
       </c>
       <c r="D92" t="n">
-        <v>7024.16</v>
+        <v>7739.54</v>
       </c>
       <c r="E92" t="n">
-        <v>6558.47</v>
+        <v>6911.52</v>
       </c>
       <c r="F92" t="n">
-        <v>6908.71</v>
-      </c>
-      <c r="G92" t="n">
         <v>7739.54</v>
       </c>
     </row>
@@ -3159,21 +2901,18 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5968.42</v>
+        <v>6341.09</v>
       </c>
       <c r="C93" t="n">
-        <v>1032.54</v>
+        <v>1387.68</v>
       </c>
       <c r="D93" t="n">
-        <v>7000.97</v>
+        <v>7728.77</v>
       </c>
       <c r="E93" t="n">
-        <v>6545.6</v>
+        <v>6897.66</v>
       </c>
       <c r="F93" t="n">
-        <v>6897.13</v>
-      </c>
-      <c r="G93" t="n">
         <v>7728.77</v>
       </c>
     </row>
@@ -3184,21 +2923,18 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5962.57</v>
+        <v>6330.97</v>
       </c>
       <c r="C94" t="n">
-        <v>1015.2</v>
+        <v>1387.02</v>
       </c>
       <c r="D94" t="n">
-        <v>6977.77</v>
+        <v>7717.99</v>
       </c>
       <c r="E94" t="n">
-        <v>6532.72</v>
+        <v>6883.81</v>
       </c>
       <c r="F94" t="n">
-        <v>6885.56</v>
-      </c>
-      <c r="G94" t="n">
         <v>7717.99</v>
       </c>
       <c r="H94" t="inlineStr">
@@ -3214,21 +2950,18 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5956.71</v>
+        <v>6320.42</v>
       </c>
       <c r="C95" t="n">
-        <v>997.86</v>
+        <v>1386.79</v>
       </c>
       <c r="D95" t="n">
-        <v>6954.58</v>
+        <v>7707.22</v>
       </c>
       <c r="E95" t="n">
-        <v>6519.77</v>
+        <v>6869.87</v>
       </c>
       <c r="F95" t="n">
-        <v>6873.98</v>
-      </c>
-      <c r="G95" t="n">
         <v>7707.22</v>
       </c>
     </row>
@@ -3239,21 +2972,18 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5950.86</v>
+        <v>6309.88</v>
       </c>
       <c r="C96" t="n">
-        <v>980.52</v>
+        <v>1386.57</v>
       </c>
       <c r="D96" t="n">
-        <v>6931.38</v>
+        <v>7696.44</v>
       </c>
       <c r="E96" t="n">
-        <v>6506.52</v>
+        <v>6855.64</v>
       </c>
       <c r="F96" t="n">
-        <v>6862.4</v>
-      </c>
-      <c r="G96" t="n">
         <v>7696.44</v>
       </c>
     </row>
@@ -3264,21 +2994,18 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5945</v>
+        <v>6299.33</v>
       </c>
       <c r="C97" t="n">
-        <v>977.97</v>
+        <v>1386.34</v>
       </c>
       <c r="D97" t="n">
-        <v>6922.97</v>
+        <v>7685.67</v>
       </c>
       <c r="E97" t="n">
-        <v>6496.23</v>
+        <v>6844.36</v>
       </c>
       <c r="F97" t="n">
-        <v>6850.82</v>
-      </c>
-      <c r="G97" t="n">
         <v>7685.67</v>
       </c>
     </row>
@@ -3289,21 +3016,18 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5931.73</v>
+        <v>6288.78</v>
       </c>
       <c r="C98" t="n">
-        <v>982.8200000000001</v>
+        <v>1386.11</v>
       </c>
       <c r="D98" t="n">
-        <v>6914.56</v>
+        <v>7674.89</v>
       </c>
       <c r="E98" t="n">
-        <v>6484.45</v>
+        <v>6833.08</v>
       </c>
       <c r="F98" t="n">
-        <v>6839.25</v>
-      </c>
-      <c r="G98" t="n">
         <v>7674.89</v>
       </c>
     </row>
@@ -3314,21 +3038,18 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5918.47</v>
+        <v>6278.23</v>
       </c>
       <c r="C99" t="n">
-        <v>987.6799999999999</v>
+        <v>1384.01</v>
       </c>
       <c r="D99" t="n">
-        <v>6906.15</v>
+        <v>7662.24</v>
       </c>
       <c r="E99" t="n">
-        <v>6472.68</v>
+        <v>6821.44</v>
       </c>
       <c r="F99" t="n">
-        <v>6827.67</v>
-      </c>
-      <c r="G99" t="n">
         <v>7662.24</v>
       </c>
     </row>
@@ -3339,21 +3060,18 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5905.2</v>
+        <v>6267.69</v>
       </c>
       <c r="C100" t="n">
-        <v>992.53</v>
+        <v>1381.91</v>
       </c>
       <c r="D100" t="n">
-        <v>6897.73</v>
+        <v>7649.6</v>
       </c>
       <c r="E100" t="n">
-        <v>6460.33</v>
+        <v>6809.2</v>
       </c>
       <c r="F100" t="n">
-        <v>6813.19</v>
-      </c>
-      <c r="G100" t="n">
         <v>7649.6</v>
       </c>
     </row>
@@ -3364,21 +3082,18 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5891.94</v>
+        <v>6257.14</v>
       </c>
       <c r="C101" t="n">
-        <v>997.39</v>
+        <v>1379.81</v>
       </c>
       <c r="D101" t="n">
-        <v>6889.32</v>
+        <v>7636.95</v>
       </c>
       <c r="E101" t="n">
-        <v>6447.97</v>
+        <v>6796.97</v>
       </c>
       <c r="F101" t="n">
-        <v>6798.71</v>
-      </c>
-      <c r="G101" t="n">
         <v>7636.95</v>
       </c>
     </row>
@@ -3389,21 +3104,18 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5878.67</v>
+        <v>6248.52</v>
       </c>
       <c r="C102" t="n">
-        <v>1002.24</v>
+        <v>1375.78</v>
       </c>
       <c r="D102" t="n">
-        <v>6880.91</v>
+        <v>7624.31</v>
       </c>
       <c r="E102" t="n">
-        <v>6436</v>
+        <v>6785.13</v>
       </c>
       <c r="F102" t="n">
-        <v>6784.23</v>
-      </c>
-      <c r="G102" t="n">
         <v>7624.31</v>
       </c>
     </row>
@@ -3414,21 +3126,18 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5865.41</v>
+        <v>6239.91</v>
       </c>
       <c r="C103" t="n">
-        <v>1007.09</v>
+        <v>1371.76</v>
       </c>
       <c r="D103" t="n">
-        <v>6872.5</v>
+        <v>7611.66</v>
       </c>
       <c r="E103" t="n">
-        <v>6423.51</v>
+        <v>6772.77</v>
       </c>
       <c r="F103" t="n">
-        <v>6769.74</v>
-      </c>
-      <c r="G103" t="n">
         <v>7611.66</v>
       </c>
     </row>
@@ -3439,21 +3148,18 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5852.14</v>
+        <v>6231.29</v>
       </c>
       <c r="C104" t="n">
-        <v>1002.97</v>
+        <v>1367.73</v>
       </c>
       <c r="D104" t="n">
-        <v>6855.11</v>
+        <v>7599.02</v>
       </c>
       <c r="E104" t="n">
-        <v>6409.23</v>
+        <v>6758.61</v>
       </c>
       <c r="F104" t="n">
-        <v>6755.26</v>
-      </c>
-      <c r="G104" t="n">
         <v>7599.02</v>
       </c>
     </row>
@@ -3464,21 +3170,18 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5843.17</v>
+        <v>6222.67</v>
       </c>
       <c r="C105" t="n">
-        <v>994.55</v>
+        <v>1363.7</v>
       </c>
       <c r="D105" t="n">
-        <v>6837.72</v>
+        <v>7586.37</v>
       </c>
       <c r="E105" t="n">
-        <v>6395.8</v>
+        <v>6744.45</v>
       </c>
       <c r="F105" t="n">
-        <v>6740.78</v>
-      </c>
-      <c r="G105" t="n">
         <v>7586.37</v>
       </c>
     </row>
@@ -3489,21 +3192,18 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5834.19</v>
+        <v>6214.05</v>
       </c>
       <c r="C106" t="n">
-        <v>986.13</v>
+        <v>1356.4</v>
       </c>
       <c r="D106" t="n">
-        <v>6820.33</v>
+        <v>7570.45</v>
       </c>
       <c r="E106" t="n">
-        <v>6382.38</v>
+        <v>6729.63</v>
       </c>
       <c r="F106" t="n">
-        <v>6726.3</v>
-      </c>
-      <c r="G106" t="n">
         <v>7570.45</v>
       </c>
     </row>
@@ -3514,21 +3214,18 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5825.22</v>
+        <v>6205.44</v>
       </c>
       <c r="C107" t="n">
-        <v>977.72</v>
+        <v>1349.1</v>
       </c>
       <c r="D107" t="n">
-        <v>6802.93</v>
+        <v>7554.53</v>
       </c>
       <c r="E107" t="n">
-        <v>6370.09</v>
+        <v>6715.96</v>
       </c>
       <c r="F107" t="n">
-        <v>6717.51</v>
-      </c>
-      <c r="G107" t="n">
         <v>7554.53</v>
       </c>
     </row>
@@ -3539,21 +3236,18 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5816.24</v>
+        <v>6196.82</v>
       </c>
       <c r="C108" t="n">
-        <v>969.3</v>
+        <v>1341.79</v>
       </c>
       <c r="D108" t="n">
-        <v>6785.54</v>
+        <v>7538.61</v>
       </c>
       <c r="E108" t="n">
-        <v>6357.81</v>
+        <v>6702.28</v>
       </c>
       <c r="F108" t="n">
-        <v>6708.73</v>
-      </c>
-      <c r="G108" t="n">
         <v>7538.61</v>
       </c>
     </row>
@@ -3564,21 +3258,18 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5807.27</v>
+        <v>6198.37</v>
       </c>
       <c r="C109" t="n">
-        <v>960.88</v>
+        <v>1324.32</v>
       </c>
       <c r="D109" t="n">
-        <v>6768.15</v>
+        <v>7522.7</v>
       </c>
       <c r="E109" t="n">
-        <v>6347.55</v>
+        <v>6690.64</v>
       </c>
       <c r="F109" t="n">
-        <v>6699.94</v>
-      </c>
-      <c r="G109" t="n">
         <v>7522.7</v>
       </c>
     </row>
@@ -3589,21 +3280,18 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5798.29</v>
+        <v>6199.93</v>
       </c>
       <c r="C110" t="n">
-        <v>952.47</v>
+        <v>1306.85</v>
       </c>
       <c r="D110" t="n">
-        <v>6750.76</v>
+        <v>7506.78</v>
       </c>
       <c r="E110" t="n">
-        <v>6337.44</v>
+        <v>6679.14</v>
       </c>
       <c r="F110" t="n">
-        <v>6691.15</v>
-      </c>
-      <c r="G110" t="n">
         <v>7506.78</v>
       </c>
     </row>
@@ -3614,21 +3302,18 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5789.32</v>
+        <v>6201.48</v>
       </c>
       <c r="C111" t="n">
-        <v>941.4299999999999</v>
+        <v>1289.38</v>
       </c>
       <c r="D111" t="n">
-        <v>6730.75</v>
+        <v>7490.86</v>
       </c>
       <c r="E111" t="n">
-        <v>6326.81</v>
+        <v>6667.12</v>
       </c>
       <c r="F111" t="n">
-        <v>6682.36</v>
-      </c>
-      <c r="G111" t="n">
         <v>7490.86</v>
       </c>
     </row>
@@ -3639,21 +3324,18 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5776.31</v>
+        <v>6203.03</v>
       </c>
       <c r="C112" t="n">
-        <v>934.4400000000001</v>
+        <v>1271.91</v>
       </c>
       <c r="D112" t="n">
-        <v>6710.75</v>
+        <v>7474.94</v>
       </c>
       <c r="E112" t="n">
-        <v>6315.37</v>
+        <v>6655.1</v>
       </c>
       <c r="F112" t="n">
-        <v>6673.58</v>
-      </c>
-      <c r="G112" t="n">
         <v>7474.94</v>
       </c>
     </row>
@@ -3664,21 +3346,18 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5763.3</v>
+        <v>6196.26</v>
       </c>
       <c r="C113" t="n">
-        <v>927.45</v>
+        <v>1260.15</v>
       </c>
       <c r="D113" t="n">
-        <v>6690.74</v>
+        <v>7456.41</v>
       </c>
       <c r="E113" t="n">
-        <v>6303.94</v>
+        <v>6642.56</v>
       </c>
       <c r="F113" t="n">
-        <v>6664.79</v>
-      </c>
-      <c r="G113" t="n">
         <v>7456.41</v>
       </c>
     </row>
@@ -3689,21 +3368,18 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5750.29</v>
+        <v>6179.32</v>
       </c>
       <c r="C114" t="n">
-        <v>920.45</v>
+        <v>1258.56</v>
       </c>
       <c r="D114" t="n">
-        <v>6670.74</v>
+        <v>7437.88</v>
       </c>
       <c r="E114" t="n">
-        <v>6291.49</v>
+        <v>6629.01</v>
       </c>
       <c r="F114" t="n">
-        <v>6650.96</v>
-      </c>
-      <c r="G114" t="n">
         <v>7437.88</v>
       </c>
     </row>
@@ -3714,21 +3390,18 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5737.27</v>
+        <v>6162.38</v>
       </c>
       <c r="C115" t="n">
-        <v>913.46</v>
+        <v>1256.97</v>
       </c>
       <c r="D115" t="n">
-        <v>6650.73</v>
+        <v>7419.35</v>
       </c>
       <c r="E115" t="n">
-        <v>6279.04</v>
+        <v>6615.46</v>
       </c>
       <c r="F115" t="n">
-        <v>6637.12</v>
-      </c>
-      <c r="G115" t="n">
         <v>7419.35</v>
       </c>
     </row>
@@ -3739,21 +3412,18 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5724.26</v>
+        <v>6145.44</v>
       </c>
       <c r="C116" t="n">
-        <v>906.46</v>
+        <v>1255.38</v>
       </c>
       <c r="D116" t="n">
-        <v>6630.73</v>
+        <v>7400.82</v>
       </c>
       <c r="E116" t="n">
-        <v>6265.41</v>
+        <v>6600.73</v>
       </c>
       <c r="F116" t="n">
-        <v>6623.29</v>
-      </c>
-      <c r="G116" t="n">
         <v>7400.82</v>
       </c>
     </row>
@@ -3764,21 +3434,18 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5711.25</v>
+        <v>6126.1</v>
       </c>
       <c r="C117" t="n">
-        <v>899.47</v>
+        <v>1256.19</v>
       </c>
       <c r="D117" t="n">
-        <v>6610.72</v>
+        <v>7382.29</v>
       </c>
       <c r="E117" t="n">
-        <v>6251.31</v>
+        <v>6585.52</v>
       </c>
       <c r="F117" t="n">
-        <v>6609.46</v>
-      </c>
-      <c r="G117" t="n">
         <v>7382.29</v>
       </c>
     </row>
@@ -3789,21 +3456,18 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>5698.24</v>
+        <v>6106.76</v>
       </c>
       <c r="C118" t="n">
-        <v>897.39</v>
+        <v>1257</v>
       </c>
       <c r="D118" t="n">
-        <v>6595.63</v>
+        <v>7363.76</v>
       </c>
       <c r="E118" t="n">
-        <v>6236.56</v>
+        <v>6569.66</v>
       </c>
       <c r="F118" t="n">
-        <v>6595.63</v>
-      </c>
-      <c r="G118" t="n">
         <v>7363.76</v>
       </c>
     </row>
@@ -3814,21 +3478,18 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5688.19</v>
+        <v>6087.42</v>
       </c>
       <c r="C119" t="n">
-        <v>893.6</v>
+        <v>1257.81</v>
       </c>
       <c r="D119" t="n">
-        <v>6581.79</v>
+        <v>7345.23</v>
       </c>
       <c r="E119" t="n">
-        <v>6222.4</v>
+        <v>6553.8</v>
       </c>
       <c r="F119" t="n">
-        <v>6581.79</v>
-      </c>
-      <c r="G119" t="n">
         <v>7345.23</v>
       </c>
     </row>
@@ -3839,21 +3500,18 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5678.15</v>
+        <v>6068.07</v>
       </c>
       <c r="C120" t="n">
-        <v>889.8099999999999</v>
+        <v>1253.61</v>
       </c>
       <c r="D120" t="n">
-        <v>6567.96</v>
+        <v>7321.69</v>
       </c>
       <c r="E120" t="n">
-        <v>6208.24</v>
+        <v>6536.94</v>
       </c>
       <c r="F120" t="n">
-        <v>6567.96</v>
-      </c>
-      <c r="G120" t="n">
         <v>7321.69</v>
       </c>
     </row>
@@ -3864,21 +3522,18 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5668.1</v>
+        <v>6048.73</v>
       </c>
       <c r="C121" t="n">
-        <v>884.9299999999999</v>
+        <v>1249.41</v>
       </c>
       <c r="D121" t="n">
-        <v>6553.03</v>
+        <v>7298.15</v>
       </c>
       <c r="E121" t="n">
-        <v>6193.86</v>
+        <v>6519.87</v>
       </c>
       <c r="F121" t="n">
-        <v>6553.03</v>
-      </c>
-      <c r="G121" t="n">
         <v>7298.15</v>
       </c>
     </row>
@@ -3889,21 +3544,18 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5658.05</v>
+        <v>6029.39</v>
       </c>
       <c r="C122" t="n">
-        <v>880.05</v>
+        <v>1245.21</v>
       </c>
       <c r="D122" t="n">
-        <v>6538.1</v>
+        <v>7274.61</v>
       </c>
       <c r="E122" t="n">
-        <v>6179.48</v>
+        <v>6502.79</v>
       </c>
       <c r="F122" t="n">
-        <v>6538.1</v>
-      </c>
-      <c r="G122" t="n">
         <v>7274.61</v>
       </c>
     </row>
@@ -3914,21 +3566,18 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5648</v>
+        <v>6010.05</v>
       </c>
       <c r="C123" t="n">
-        <v>875.17</v>
+        <v>1241.01</v>
       </c>
       <c r="D123" t="n">
-        <v>6523.17</v>
+        <v>7251.06</v>
       </c>
       <c r="E123" t="n">
-        <v>6163.62</v>
+        <v>6484.23</v>
       </c>
       <c r="F123" t="n">
-        <v>6523.17</v>
-      </c>
-      <c r="G123" t="n">
         <v>7251.06</v>
       </c>
     </row>
@@ -3939,21 +3588,18 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5637.96</v>
+        <v>5996.37</v>
       </c>
       <c r="C124" t="n">
-        <v>870.29</v>
+        <v>1231.16</v>
       </c>
       <c r="D124" t="n">
-        <v>6508.25</v>
+        <v>7227.52</v>
       </c>
       <c r="E124" t="n">
-        <v>6148.89</v>
+        <v>6466.8</v>
       </c>
       <c r="F124" t="n">
-        <v>6508.25</v>
-      </c>
-      <c r="G124" t="n">
         <v>7227.52</v>
       </c>
     </row>
@@ -3964,21 +3610,18 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5627.91</v>
+        <v>5982.68</v>
       </c>
       <c r="C125" t="n">
-        <v>865.41</v>
+        <v>1221.3</v>
       </c>
       <c r="D125" t="n">
-        <v>6493.32</v>
+        <v>7203.98</v>
       </c>
       <c r="E125" t="n">
-        <v>6134.38</v>
+        <v>6449.6</v>
       </c>
       <c r="F125" t="n">
-        <v>6493.32</v>
-      </c>
-      <c r="G125" t="n">
         <v>7203.98</v>
       </c>
       <c r="H125" t="inlineStr">
@@ -3994,21 +3637,18 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5642.36</v>
+        <v>5969</v>
       </c>
       <c r="C126" t="n">
-        <v>836.03</v>
+        <v>1211.44</v>
       </c>
       <c r="D126" t="n">
-        <v>6478.39</v>
+        <v>7180.44</v>
       </c>
       <c r="E126" t="n">
-        <v>6124.78</v>
+        <v>6432.39</v>
       </c>
       <c r="F126" t="n">
-        <v>6478.39</v>
-      </c>
-      <c r="G126" t="n">
         <v>7180.44</v>
       </c>
     </row>
@@ -4019,21 +3659,18 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>5656.81</v>
+        <v>5955.31</v>
       </c>
       <c r="C127" t="n">
-        <v>806.65</v>
+        <v>1201.32</v>
       </c>
       <c r="D127" t="n">
-        <v>6463.46</v>
+        <v>7156.63</v>
       </c>
       <c r="E127" t="n">
-        <v>6115.17</v>
+        <v>6415.13</v>
       </c>
       <c r="F127" t="n">
-        <v>6463.46</v>
-      </c>
-      <c r="G127" t="n">
         <v>7156.63</v>
       </c>
     </row>
@@ -4044,21 +3681,18 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5671.26</v>
+        <v>5941.63</v>
       </c>
       <c r="C128" t="n">
-        <v>775.83</v>
+        <v>1191.2</v>
       </c>
       <c r="D128" t="n">
-        <v>6447.09</v>
+        <v>7132.83</v>
       </c>
       <c r="E128" t="n">
-        <v>6105.27</v>
+        <v>6397.59</v>
       </c>
       <c r="F128" t="n">
-        <v>6447.09</v>
-      </c>
-      <c r="G128" t="n">
         <v>7132.83</v>
       </c>
     </row>
@@ -4069,21 +3703,18 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5685.72</v>
+        <v>5927.94</v>
       </c>
       <c r="C129" t="n">
-        <v>745.01</v>
+        <v>1181.07</v>
       </c>
       <c r="D129" t="n">
-        <v>6430.73</v>
+        <v>7109.02</v>
       </c>
       <c r="E129" t="n">
-        <v>6095.38</v>
+        <v>6380.04</v>
       </c>
       <c r="F129" t="n">
-        <v>6430.73</v>
-      </c>
-      <c r="G129" t="n">
         <v>7109.02</v>
       </c>
     </row>
@@ -4094,21 +3725,18 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5700.17</v>
+        <v>5914.26</v>
       </c>
       <c r="C130" t="n">
-        <v>714.2</v>
+        <v>1170.95</v>
       </c>
       <c r="D130" t="n">
-        <v>6414.36</v>
+        <v>7085.21</v>
       </c>
       <c r="E130" t="n">
-        <v>6084.42</v>
+        <v>6361.43</v>
       </c>
       <c r="F130" t="n">
-        <v>6414.36</v>
-      </c>
-      <c r="G130" t="n">
         <v>7085.21</v>
       </c>
     </row>
@@ -4119,21 +3747,18 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5714.62</v>
+        <v>5898.49</v>
       </c>
       <c r="C131" t="n">
-        <v>683.38</v>
+        <v>1162.91</v>
       </c>
       <c r="D131" t="n">
-        <v>6398</v>
+        <v>7061.4</v>
       </c>
       <c r="E131" t="n">
-        <v>6073.05</v>
+        <v>6342.41</v>
       </c>
       <c r="F131" t="n">
-        <v>6398</v>
-      </c>
-      <c r="G131" t="n">
         <v>7061.4</v>
       </c>
     </row>
@@ -4144,21 +3769,18 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5729.07</v>
+        <v>5882.73</v>
       </c>
       <c r="C132" t="n">
-        <v>652.5599999999999</v>
+        <v>1154.87</v>
       </c>
       <c r="D132" t="n">
-        <v>6381.63</v>
+        <v>7037.6</v>
       </c>
       <c r="E132" t="n">
-        <v>6061.24</v>
+        <v>6322.95</v>
       </c>
       <c r="F132" t="n">
-        <v>6381.63</v>
-      </c>
-      <c r="G132" t="n">
         <v>7037.6</v>
       </c>
     </row>
@@ -4169,21 +3791,18 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5729.84</v>
+        <v>5866.96</v>
       </c>
       <c r="C133" t="n">
-        <v>635.4299999999999</v>
+        <v>1146.83</v>
       </c>
       <c r="D133" t="n">
-        <v>6365.27</v>
+        <v>7013.79</v>
       </c>
       <c r="E133" t="n">
-        <v>6046.7</v>
+        <v>6303.49</v>
       </c>
       <c r="F133" t="n">
-        <v>6365.27</v>
-      </c>
-      <c r="G133" t="n">
         <v>7013.79</v>
       </c>
     </row>
@@ -4194,21 +3813,18 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5730.61</v>
+        <v>5851.2</v>
       </c>
       <c r="C134" t="n">
-        <v>618.29</v>
+        <v>1143.7</v>
       </c>
       <c r="D134" t="n">
-        <v>6348.9</v>
+        <v>6994.9</v>
       </c>
       <c r="E134" t="n">
-        <v>6032.16</v>
+        <v>6285.02</v>
       </c>
       <c r="F134" t="n">
-        <v>6348.9</v>
-      </c>
-      <c r="G134" t="n">
         <v>6994.9</v>
       </c>
     </row>
@@ -4219,21 +3835,18 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5731.38</v>
+        <v>5835.43</v>
       </c>
       <c r="C135" t="n">
-        <v>604.53</v>
+        <v>1140.57</v>
       </c>
       <c r="D135" t="n">
-        <v>6335.91</v>
+        <v>6976</v>
       </c>
       <c r="E135" t="n">
-        <v>6018.29</v>
+        <v>6267.22</v>
       </c>
       <c r="F135" t="n">
-        <v>6335.91</v>
-      </c>
-      <c r="G135" t="n">
         <v>6976</v>
       </c>
     </row>
@@ -4244,21 +3857,18 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5732.14</v>
+        <v>5819.67</v>
       </c>
       <c r="C136" t="n">
-        <v>590.78</v>
+        <v>1137.45</v>
       </c>
       <c r="D136" t="n">
-        <v>6322.92</v>
+        <v>6957.11</v>
       </c>
       <c r="E136" t="n">
-        <v>6004.42</v>
+        <v>6249.42</v>
       </c>
       <c r="F136" t="n">
-        <v>6322.92</v>
-      </c>
-      <c r="G136" t="n">
         <v>6957.11</v>
       </c>
     </row>
@@ -4269,21 +3879,18 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5732.91</v>
+        <v>5803.9</v>
       </c>
       <c r="C137" t="n">
-        <v>577.02</v>
+        <v>1134.32</v>
       </c>
       <c r="D137" t="n">
-        <v>6309.93</v>
+        <v>6938.22</v>
       </c>
       <c r="E137" t="n">
-        <v>5990.19</v>
+        <v>6231.25</v>
       </c>
       <c r="F137" t="n">
-        <v>6309.93</v>
-      </c>
-      <c r="G137" t="n">
         <v>6938.22</v>
       </c>
     </row>
@@ -4294,21 +3901,18 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5733.68</v>
+        <v>5782.94</v>
       </c>
       <c r="C138" t="n">
-        <v>563.26</v>
+        <v>1136.39</v>
       </c>
       <c r="D138" t="n">
-        <v>6296.94</v>
+        <v>6919.33</v>
       </c>
       <c r="E138" t="n">
-        <v>5974.92</v>
+        <v>6212.05</v>
       </c>
       <c r="F138" t="n">
-        <v>6296.94</v>
-      </c>
-      <c r="G138" t="n">
         <v>6919.33</v>
       </c>
     </row>
@@ -4319,21 +3923,18 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>5734.45</v>
+        <v>5761.98</v>
       </c>
       <c r="C139" t="n">
-        <v>549.5</v>
+        <v>1138.46</v>
       </c>
       <c r="D139" t="n">
-        <v>6283.95</v>
+        <v>6900.43</v>
       </c>
       <c r="E139" t="n">
-        <v>5960.05</v>
+        <v>6193.25</v>
       </c>
       <c r="F139" t="n">
-        <v>6283.95</v>
-      </c>
-      <c r="G139" t="n">
         <v>6900.43</v>
       </c>
     </row>
@@ -4344,21 +3945,18 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5717.19</v>
+        <v>5741.02</v>
       </c>
       <c r="C140" t="n">
-        <v>553.77</v>
+        <v>1140.52</v>
       </c>
       <c r="D140" t="n">
-        <v>6270.96</v>
+        <v>6881.54</v>
       </c>
       <c r="E140" t="n">
-        <v>5941.57</v>
+        <v>6174.44</v>
       </c>
       <c r="F140" t="n">
-        <v>6270.96</v>
-      </c>
-      <c r="G140" t="n">
         <v>6881.54</v>
       </c>
     </row>
@@ -4369,21 +3967,18 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>5699.92</v>
+        <v>5720.05</v>
       </c>
       <c r="C141" t="n">
-        <v>558.05</v>
+        <v>1146.17</v>
       </c>
       <c r="D141" t="n">
-        <v>6257.97</v>
+        <v>6866.22</v>
       </c>
       <c r="E141" t="n">
-        <v>5923.09</v>
+        <v>6156.35</v>
       </c>
       <c r="F141" t="n">
-        <v>6257.97</v>
-      </c>
-      <c r="G141" t="n">
         <v>6866.22</v>
       </c>
     </row>
@@ -4394,21 +3989,18 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>5682.66</v>
+        <v>5699.09</v>
       </c>
       <c r="C142" t="n">
-        <v>559</v>
+        <v>1151.81</v>
       </c>
       <c r="D142" t="n">
-        <v>6241.66</v>
+        <v>6850.9</v>
       </c>
       <c r="E142" t="n">
-        <v>5903.95</v>
+        <v>6137.6</v>
       </c>
       <c r="F142" t="n">
-        <v>6241.66</v>
-      </c>
-      <c r="G142" t="n">
         <v>6850.9</v>
       </c>
     </row>
@@ -4419,21 +4011,18 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>5665.4</v>
+        <v>5678.13</v>
       </c>
       <c r="C143" t="n">
-        <v>559.95</v>
+        <v>1157.45</v>
       </c>
       <c r="D143" t="n">
-        <v>6225.35</v>
+        <v>6835.58</v>
       </c>
       <c r="E143" t="n">
-        <v>5884.8</v>
+        <v>6118.84</v>
       </c>
       <c r="F143" t="n">
-        <v>6225.35</v>
-      </c>
-      <c r="G143" t="n">
         <v>6835.58</v>
       </c>
     </row>
@@ -4444,21 +4033,18 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>5648.14</v>
+        <v>5657.17</v>
       </c>
       <c r="C144" t="n">
-        <v>560.91</v>
+        <v>1163.1</v>
       </c>
       <c r="D144" t="n">
-        <v>6209.04</v>
+        <v>6820.27</v>
       </c>
       <c r="E144" t="n">
-        <v>5865.78</v>
+        <v>6100.21</v>
       </c>
       <c r="F144" t="n">
-        <v>6209.04</v>
-      </c>
-      <c r="G144" t="n">
         <v>6820.27</v>
       </c>
     </row>
@@ -4469,21 +4055,18 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>5630.87</v>
+        <v>5642.58</v>
       </c>
       <c r="C145" t="n">
-        <v>561.86</v>
+        <v>1162.37</v>
       </c>
       <c r="D145" t="n">
-        <v>6192.74</v>
+        <v>6804.95</v>
       </c>
       <c r="E145" t="n">
-        <v>5848.03</v>
+        <v>6082.84</v>
       </c>
       <c r="F145" t="n">
-        <v>6192.74</v>
-      </c>
-      <c r="G145" t="n">
         <v>6804.95</v>
       </c>
     </row>
@@ -4494,21 +4077,18 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>5613.61</v>
+        <v>5627.98</v>
       </c>
       <c r="C146" t="n">
-        <v>562.8200000000001</v>
+        <v>1161.65</v>
       </c>
       <c r="D146" t="n">
-        <v>6176.43</v>
+        <v>6789.63</v>
       </c>
       <c r="E146" t="n">
-        <v>5830.87</v>
+        <v>6066.08</v>
       </c>
       <c r="F146" t="n">
-        <v>6176.43</v>
-      </c>
-      <c r="G146" t="n">
         <v>6789.63</v>
       </c>
     </row>
@@ -4519,21 +4099,18 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>5603.55</v>
+        <v>5613.39</v>
       </c>
       <c r="C147" t="n">
-        <v>556.5700000000001</v>
+        <v>1160.92</v>
       </c>
       <c r="D147" t="n">
-        <v>6160.12</v>
+        <v>6774.31</v>
       </c>
       <c r="E147" t="n">
-        <v>5815.16</v>
+        <v>6049.31</v>
       </c>
       <c r="F147" t="n">
-        <v>6160.12</v>
-      </c>
-      <c r="G147" t="n">
         <v>6774.31</v>
       </c>
     </row>
@@ -4544,21 +4121,18 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>5593.48</v>
+        <v>5598.79</v>
       </c>
       <c r="C148" t="n">
-        <v>550.33</v>
+        <v>1156.78</v>
       </c>
       <c r="D148" t="n">
-        <v>6143.81</v>
+        <v>6755.57</v>
       </c>
       <c r="E148" t="n">
-        <v>5799.45</v>
+        <v>6031.86</v>
       </c>
       <c r="F148" t="n">
-        <v>6143.81</v>
-      </c>
-      <c r="G148" t="n">
         <v>6755.57</v>
       </c>
     </row>
@@ -4569,21 +4143,18 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>5583.42</v>
+        <v>5584.2</v>
       </c>
       <c r="C149" t="n">
-        <v>543.6900000000001</v>
+        <v>1152.63</v>
       </c>
       <c r="D149" t="n">
-        <v>6127.11</v>
+        <v>6736.83</v>
       </c>
       <c r="E149" t="n">
-        <v>5783.65</v>
+        <v>6014.34</v>
       </c>
       <c r="F149" t="n">
-        <v>6127.11</v>
-      </c>
-      <c r="G149" t="n">
         <v>6736.83</v>
       </c>
     </row>
@@ -4597,18 +4168,15 @@
         <v>5569.6</v>
       </c>
       <c r="C150" t="n">
-        <v>540.8</v>
+        <v>1148.49</v>
       </c>
       <c r="D150" t="n">
-        <v>6110.4</v>
+        <v>6718.09</v>
       </c>
       <c r="E150" t="n">
-        <v>5767.86</v>
+        <v>5996.81</v>
       </c>
       <c r="F150" t="n">
-        <v>6110.4</v>
-      </c>
-      <c r="G150" t="n">
         <v>6718.09</v>
       </c>
     </row>
@@ -4622,18 +4190,15 @@
         <v>5555.01</v>
       </c>
       <c r="C151" t="n">
-        <v>538.6900000000001</v>
+        <v>1144.34</v>
       </c>
       <c r="D151" t="n">
-        <v>6093.7</v>
+        <v>6699.35</v>
       </c>
       <c r="E151" t="n">
-        <v>5753.31</v>
+        <v>5980.53</v>
       </c>
       <c r="F151" t="n">
-        <v>6093.7</v>
-      </c>
-      <c r="G151" t="n">
         <v>6699.35</v>
       </c>
     </row>
@@ -4647,18 +4212,15 @@
         <v>5541.13</v>
       </c>
       <c r="C152" t="n">
-        <v>535.87</v>
+        <v>1139.48</v>
       </c>
       <c r="D152" t="n">
-        <v>6077</v>
+        <v>6680.61</v>
       </c>
       <c r="E152" t="n">
-        <v>5738.91</v>
+        <v>5964.39</v>
       </c>
       <c r="F152" t="n">
-        <v>6077</v>
-      </c>
-      <c r="G152" t="n">
         <v>6680.61</v>
       </c>
     </row>
@@ -4672,18 +4234,15 @@
         <v>5527.25</v>
       </c>
       <c r="C153" t="n">
-        <v>533.05</v>
+        <v>1134.62</v>
       </c>
       <c r="D153" t="n">
-        <v>6060.3</v>
+        <v>6661.87</v>
       </c>
       <c r="E153" t="n">
-        <v>5724.88</v>
+        <v>5948.62</v>
       </c>
       <c r="F153" t="n">
-        <v>6060.3</v>
-      </c>
-      <c r="G153" t="n">
         <v>6661.87</v>
       </c>
       <c r="H153" t="inlineStr">
@@ -4702,18 +4261,15 @@
         <v>5513.37</v>
       </c>
       <c r="C154" t="n">
-        <v>530.23</v>
+        <v>1129.76</v>
       </c>
       <c r="D154" t="n">
-        <v>6043.59</v>
+        <v>6643.13</v>
       </c>
       <c r="E154" t="n">
-        <v>5712.01</v>
+        <v>5932.86</v>
       </c>
       <c r="F154" t="n">
-        <v>6043.59</v>
-      </c>
-      <c r="G154" t="n">
         <v>6643.13</v>
       </c>
     </row>
@@ -4727,18 +4283,15 @@
         <v>5499.48</v>
       </c>
       <c r="C155" t="n">
-        <v>527.41</v>
+        <v>1124.57</v>
       </c>
       <c r="D155" t="n">
-        <v>6026.89</v>
+        <v>6624.06</v>
       </c>
       <c r="E155" t="n">
-        <v>5699.14</v>
+        <v>5917.03</v>
       </c>
       <c r="F155" t="n">
-        <v>6026.89</v>
-      </c>
-      <c r="G155" t="n">
         <v>6624.06</v>
       </c>
     </row>
@@ -4752,18 +4305,15 @@
         <v>5485.6</v>
       </c>
       <c r="C156" t="n">
-        <v>524.55</v>
+        <v>1119.38</v>
       </c>
       <c r="D156" t="n">
-        <v>6010.15</v>
+        <v>6604.98</v>
       </c>
       <c r="E156" t="n">
-        <v>5686.25</v>
+        <v>5901.19</v>
       </c>
       <c r="F156" t="n">
-        <v>6010.15</v>
-      </c>
-      <c r="G156" t="n">
         <v>6604.98</v>
       </c>
     </row>
@@ -4777,18 +4327,15 @@
         <v>5471.72</v>
       </c>
       <c r="C157" t="n">
-        <v>521.6900000000001</v>
+        <v>1114.19</v>
       </c>
       <c r="D157" t="n">
-        <v>5993.41</v>
+        <v>6585.91</v>
       </c>
       <c r="E157" t="n">
-        <v>5673.37</v>
+        <v>5885.36</v>
       </c>
       <c r="F157" t="n">
-        <v>5993.41</v>
-      </c>
-      <c r="G157" t="n">
         <v>6585.91</v>
       </c>
     </row>
@@ -4802,18 +4349,15 @@
         <v>5457.84</v>
       </c>
       <c r="C158" t="n">
-        <v>518.83</v>
+        <v>1109</v>
       </c>
       <c r="D158" t="n">
-        <v>5976.67</v>
+        <v>6566.84</v>
       </c>
       <c r="E158" t="n">
-        <v>5658.53</v>
+        <v>5867.56</v>
       </c>
       <c r="F158" t="n">
-        <v>5976.67</v>
-      </c>
-      <c r="G158" t="n">
         <v>6566.84</v>
       </c>
     </row>
@@ -4827,18 +4371,15 @@
         <v>5476.13</v>
       </c>
       <c r="C159" t="n">
-        <v>483.8</v>
+        <v>1071.64</v>
       </c>
       <c r="D159" t="n">
-        <v>5959.93</v>
+        <v>6547.77</v>
       </c>
       <c r="E159" t="n">
-        <v>5650.12</v>
+        <v>5856.19</v>
       </c>
       <c r="F159" t="n">
-        <v>5959.93</v>
-      </c>
-      <c r="G159" t="n">
         <v>6547.77</v>
       </c>
     </row>
@@ -4852,18 +4393,15 @@
         <v>5494.41</v>
       </c>
       <c r="C160" t="n">
-        <v>448.78</v>
+        <v>1034.28</v>
       </c>
       <c r="D160" t="n">
-        <v>5943.19</v>
+        <v>6528.69</v>
       </c>
       <c r="E160" t="n">
-        <v>5640.94</v>
+        <v>5844.05</v>
       </c>
       <c r="F160" t="n">
-        <v>5943.19</v>
-      </c>
-      <c r="G160" t="n">
         <v>6528.69</v>
       </c>
     </row>
@@ -4874,21 +4412,18 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>5499.24</v>
+        <v>5512.7</v>
       </c>
       <c r="C161" t="n">
-        <v>427.21</v>
+        <v>996.92</v>
       </c>
       <c r="D161" t="n">
-        <v>5926.45</v>
+        <v>6509.62</v>
       </c>
       <c r="E161" t="n">
-        <v>5629.83</v>
+        <v>5831.91</v>
       </c>
       <c r="F161" t="n">
-        <v>5926.45</v>
-      </c>
-      <c r="G161" t="n">
         <v>6509.62</v>
       </c>
     </row>
@@ -4899,21 +4434,18 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>5485.36</v>
+        <v>5522.6</v>
       </c>
       <c r="C162" t="n">
-        <v>424.35</v>
+        <v>977.84</v>
       </c>
       <c r="D162" t="n">
-        <v>5909.71</v>
+        <v>6500.44</v>
       </c>
       <c r="E162" t="n">
-        <v>5618.73</v>
+        <v>5821.75</v>
       </c>
       <c r="F162" t="n">
-        <v>5909.71</v>
-      </c>
-      <c r="G162" t="n">
         <v>6500.44</v>
       </c>
     </row>
@@ -4924,21 +4456,18 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>5471.48</v>
+        <v>5500.75</v>
       </c>
       <c r="C163" t="n">
-        <v>427.98</v>
+        <v>990.51</v>
       </c>
       <c r="D163" t="n">
-        <v>5899.46</v>
+        <v>6491.25</v>
       </c>
       <c r="E163" t="n">
-        <v>5608.93</v>
+        <v>5812.89</v>
       </c>
       <c r="F163" t="n">
-        <v>5899.46</v>
-      </c>
-      <c r="G163" t="n">
         <v>6491.25</v>
       </c>
     </row>
@@ -4949,21 +4478,18 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>5457.59</v>
+        <v>5478.9</v>
       </c>
       <c r="C164" t="n">
-        <v>431.61</v>
+        <v>1003.17</v>
       </c>
       <c r="D164" t="n">
-        <v>5889.2</v>
+        <v>6482.07</v>
       </c>
       <c r="E164" t="n">
-        <v>5599.13</v>
+        <v>5804.02</v>
       </c>
       <c r="F164" t="n">
-        <v>5889.2</v>
-      </c>
-      <c r="G164" t="n">
         <v>6482.07</v>
       </c>
     </row>
@@ -4974,21 +4500,18 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5443.71</v>
+        <v>5459.06</v>
       </c>
       <c r="C165" t="n">
-        <v>435.24</v>
+        <v>1013.83</v>
       </c>
       <c r="D165" t="n">
-        <v>5878.95</v>
+        <v>6472.89</v>
       </c>
       <c r="E165" t="n">
-        <v>5589.72</v>
+        <v>5795.56</v>
       </c>
       <c r="F165" t="n">
-        <v>5878.95</v>
-      </c>
-      <c r="G165" t="n">
         <v>6472.89</v>
       </c>
     </row>
@@ -4999,21 +4522,18 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>5429.83</v>
+        <v>5439.21</v>
       </c>
       <c r="C166" t="n">
-        <v>438.87</v>
+        <v>1024.49</v>
       </c>
       <c r="D166" t="n">
-        <v>5868.7</v>
+        <v>6463.71</v>
       </c>
       <c r="E166" t="n">
-        <v>5574.28</v>
+        <v>5781.05</v>
       </c>
       <c r="F166" t="n">
-        <v>5868.7</v>
-      </c>
-      <c r="G166" t="n">
         <v>6463.71</v>
       </c>
     </row>
@@ -5024,21 +4544,18 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5415.95</v>
+        <v>5419.37</v>
       </c>
       <c r="C167" t="n">
-        <v>442.5</v>
+        <v>1035.16</v>
       </c>
       <c r="D167" t="n">
-        <v>5858.45</v>
+        <v>6454.52</v>
       </c>
       <c r="E167" t="n">
-        <v>5558.82</v>
+        <v>5766.54</v>
       </c>
       <c r="F167" t="n">
-        <v>5858.45</v>
-      </c>
-      <c r="G167" t="n">
         <v>6454.52</v>
       </c>
     </row>
@@ -5049,21 +4566,18 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>5399.19</v>
+        <v>5399.52</v>
       </c>
       <c r="C168" t="n">
-        <v>449</v>
+        <v>1045.82</v>
       </c>
       <c r="D168" t="n">
-        <v>5848.19</v>
+        <v>6445.34</v>
       </c>
       <c r="E168" t="n">
-        <v>5542.79</v>
+        <v>5752.02</v>
       </c>
       <c r="F168" t="n">
-        <v>5848.19</v>
-      </c>
-      <c r="G168" t="n">
         <v>6445.34</v>
       </c>
     </row>
@@ -5077,18 +4591,15 @@
         <v>5379.68</v>
       </c>
       <c r="C169" t="n">
-        <v>458.26</v>
+        <v>1043.83</v>
       </c>
       <c r="D169" t="n">
-        <v>5837.94</v>
+        <v>6423.51</v>
       </c>
       <c r="E169" t="n">
-        <v>5526.76</v>
+        <v>5734.98</v>
       </c>
       <c r="F169" t="n">
-        <v>5837.94</v>
-      </c>
-      <c r="G169" t="n">
         <v>6423.51</v>
       </c>
     </row>
@@ -5102,18 +4613,15 @@
         <v>5359.83</v>
       </c>
       <c r="C170" t="n">
-        <v>463.63</v>
+        <v>1041.84</v>
       </c>
       <c r="D170" t="n">
-        <v>5823.47</v>
+        <v>6401.68</v>
       </c>
       <c r="E170" t="n">
-        <v>5509.89</v>
+        <v>5717.09</v>
       </c>
       <c r="F170" t="n">
-        <v>5823.47</v>
-      </c>
-      <c r="G170" t="n">
         <v>6401.68</v>
       </c>
     </row>
@@ -5127,18 +4635,15 @@
         <v>5339.99</v>
       </c>
       <c r="C171" t="n">
-        <v>469</v>
+        <v>1039.86</v>
       </c>
       <c r="D171" t="n">
-        <v>5808.99</v>
+        <v>6379.85</v>
       </c>
       <c r="E171" t="n">
-        <v>5493.02</v>
+        <v>5699.2</v>
       </c>
       <c r="F171" t="n">
-        <v>5808.99</v>
-      </c>
-      <c r="G171" t="n">
         <v>6379.85</v>
       </c>
     </row>
@@ -5149,21 +4654,18 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>5332.16</v>
+        <v>5332.57</v>
       </c>
       <c r="C172" t="n">
-        <v>462.36</v>
+        <v>1025.44</v>
       </c>
       <c r="D172" t="n">
-        <v>5794.52</v>
+        <v>6358.01</v>
       </c>
       <c r="E172" t="n">
-        <v>5478.63</v>
+        <v>5683.8</v>
       </c>
       <c r="F172" t="n">
-        <v>5794.52</v>
-      </c>
-      <c r="G172" t="n">
         <v>6358.01</v>
       </c>
     </row>
@@ -5174,21 +4676,18 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>5315.4</v>
+        <v>5325.15</v>
       </c>
       <c r="C173" t="n">
-        <v>464.64</v>
+        <v>1011.03</v>
       </c>
       <c r="D173" t="n">
-        <v>5780.04</v>
+        <v>6336.18</v>
       </c>
       <c r="E173" t="n">
-        <v>5462.74</v>
+        <v>5666.9</v>
       </c>
       <c r="F173" t="n">
-        <v>5780.04</v>
-      </c>
-      <c r="G173" t="n">
         <v>6336.18</v>
       </c>
     </row>
@@ -5199,21 +4698,18 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>5298.64</v>
+        <v>5317.73</v>
       </c>
       <c r="C174" t="n">
-        <v>466.93</v>
+        <v>996.62</v>
       </c>
       <c r="D174" t="n">
-        <v>5765.57</v>
+        <v>6314.35</v>
       </c>
       <c r="E174" t="n">
-        <v>5446.54</v>
+        <v>5649.68</v>
       </c>
       <c r="F174" t="n">
-        <v>5765.57</v>
-      </c>
-      <c r="G174" t="n">
         <v>6314.35</v>
       </c>
     </row>
@@ -5224,21 +4720,18 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>5295.6</v>
+        <v>5310.32</v>
       </c>
       <c r="C175" t="n">
-        <v>455.5</v>
+        <v>982.2</v>
       </c>
       <c r="D175" t="n">
-        <v>5751.09</v>
+        <v>6292.52</v>
       </c>
       <c r="E175" t="n">
-        <v>5433.09</v>
+        <v>5632.47</v>
       </c>
       <c r="F175" t="n">
-        <v>5751.09</v>
-      </c>
-      <c r="G175" t="n">
         <v>6292.52</v>
       </c>
     </row>
@@ -5249,21 +4742,18 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>5292.56</v>
+        <v>5302.9</v>
       </c>
       <c r="C176" t="n">
-        <v>444.06</v>
+        <v>971.79</v>
       </c>
       <c r="D176" t="n">
-        <v>5736.62</v>
+        <v>6274.69</v>
       </c>
       <c r="E176" t="n">
-        <v>5419.63</v>
+        <v>5616.06</v>
       </c>
       <c r="F176" t="n">
-        <v>5736.62</v>
-      </c>
-      <c r="G176" t="n">
         <v>6274.69</v>
       </c>
     </row>
@@ -5274,21 +4764,18 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>5289.52</v>
+        <v>5295.48</v>
       </c>
       <c r="C177" t="n">
-        <v>430.81</v>
+        <v>961.38</v>
       </c>
       <c r="D177" t="n">
-        <v>5720.33</v>
+        <v>6256.85</v>
       </c>
       <c r="E177" t="n">
-        <v>5405.81</v>
+        <v>5599.28</v>
       </c>
       <c r="F177" t="n">
-        <v>5720.33</v>
-      </c>
-      <c r="G177" t="n">
         <v>6256.85</v>
       </c>
     </row>
@@ -5299,21 +4786,18 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>5286.47</v>
+        <v>5288.06</v>
       </c>
       <c r="C178" t="n">
-        <v>417.56</v>
+        <v>950.96</v>
       </c>
       <c r="D178" t="n">
-        <v>5704.04</v>
+        <v>6239.02</v>
       </c>
       <c r="E178" t="n">
-        <v>5391.99</v>
+        <v>5582.5</v>
       </c>
       <c r="F178" t="n">
-        <v>5704.04</v>
-      </c>
-      <c r="G178" t="n">
         <v>6239.02</v>
       </c>
     </row>
@@ -5327,18 +4811,15 @@
         <v>5272.71</v>
       </c>
       <c r="C179" t="n">
-        <v>415.04</v>
+        <v>948.48</v>
       </c>
       <c r="D179" t="n">
-        <v>5687.75</v>
+        <v>6221.19</v>
       </c>
       <c r="E179" t="n">
-        <v>5377.47</v>
+        <v>5565.02</v>
       </c>
       <c r="F179" t="n">
-        <v>5687.75</v>
-      </c>
-      <c r="G179" t="n">
         <v>6221.19</v>
       </c>
     </row>
@@ -5352,18 +4833,15 @@
         <v>5249.79</v>
       </c>
       <c r="C180" t="n">
-        <v>421.66</v>
+        <v>953.5700000000001</v>
       </c>
       <c r="D180" t="n">
-        <v>5671.45</v>
+        <v>6203.36</v>
       </c>
       <c r="E180" t="n">
-        <v>5364.15</v>
+        <v>5548.74</v>
       </c>
       <c r="F180" t="n">
-        <v>5671.45</v>
-      </c>
-      <c r="G180" t="n">
         <v>6203.36</v>
       </c>
     </row>
@@ -5377,18 +4855,15 @@
         <v>5227.12</v>
       </c>
       <c r="C181" t="n">
-        <v>428.04</v>
+        <v>958.4</v>
       </c>
       <c r="D181" t="n">
-        <v>5655.16</v>
+        <v>6185.52</v>
       </c>
       <c r="E181" t="n">
-        <v>5350.87</v>
+        <v>5532.5</v>
       </c>
       <c r="F181" t="n">
-        <v>5655.16</v>
-      </c>
-      <c r="G181" t="n">
         <v>6185.52</v>
       </c>
     </row>
@@ -5402,18 +4877,15 @@
         <v>5204.45</v>
       </c>
       <c r="C182" t="n">
-        <v>434.42</v>
+        <v>963.24</v>
       </c>
       <c r="D182" t="n">
-        <v>5638.87</v>
+        <v>6167.69</v>
       </c>
       <c r="E182" t="n">
-        <v>5336.19</v>
+        <v>5516.27</v>
       </c>
       <c r="F182" t="n">
-        <v>5638.87</v>
-      </c>
-      <c r="G182" t="n">
         <v>6167.69</v>
       </c>
     </row>
@@ -5427,18 +4899,15 @@
         <v>5181.78</v>
       </c>
       <c r="C183" t="n">
-        <v>440.8</v>
+        <v>966.59</v>
       </c>
       <c r="D183" t="n">
-        <v>5622.58</v>
+        <v>6148.37</v>
       </c>
       <c r="E183" t="n">
-        <v>5321.52</v>
+        <v>5499.74</v>
       </c>
       <c r="F183" t="n">
-        <v>5622.58</v>
-      </c>
-      <c r="G183" t="n">
         <v>6148.37</v>
       </c>
     </row>
@@ -5452,18 +4921,15 @@
         <v>5159.12</v>
       </c>
       <c r="C184" t="n">
-        <v>450.92</v>
+        <v>969.9299999999999</v>
       </c>
       <c r="D184" t="n">
-        <v>5610.03</v>
+        <v>6129.05</v>
       </c>
       <c r="E184" t="n">
-        <v>5307.59</v>
+        <v>5483.95</v>
       </c>
       <c r="F184" t="n">
-        <v>5610.03</v>
-      </c>
-      <c r="G184" t="n">
         <v>6129.05</v>
       </c>
       <c r="H184" t="inlineStr">
@@ -5482,18 +4948,15 @@
         <v>5136.45</v>
       </c>
       <c r="C185" t="n">
-        <v>461.04</v>
+        <v>973.28</v>
       </c>
       <c r="D185" t="n">
-        <v>5597.49</v>
+        <v>6109.73</v>
       </c>
       <c r="E185" t="n">
-        <v>5293.66</v>
+        <v>5468.17</v>
       </c>
       <c r="F185" t="n">
-        <v>5597.49</v>
-      </c>
-      <c r="G185" t="n">
         <v>6109.73</v>
       </c>
     </row>
@@ -5507,18 +4970,15 @@
         <v>5113.78</v>
       </c>
       <c r="C186" t="n">
-        <v>471.16</v>
+        <v>976.63</v>
       </c>
       <c r="D186" t="n">
-        <v>5584.94</v>
+        <v>6090.41</v>
       </c>
       <c r="E186" t="n">
-        <v>5280.26</v>
+        <v>5452.92</v>
       </c>
       <c r="F186" t="n">
-        <v>5584.94</v>
-      </c>
-      <c r="G186" t="n">
         <v>6090.41</v>
       </c>
     </row>
@@ -5532,18 +4992,15 @@
         <v>5091.11</v>
       </c>
       <c r="C187" t="n">
-        <v>481.29</v>
+        <v>979.98</v>
       </c>
       <c r="D187" t="n">
-        <v>5572.4</v>
+        <v>6071.09</v>
       </c>
       <c r="E187" t="n">
-        <v>5268.52</v>
+        <v>5439.32</v>
       </c>
       <c r="F187" t="n">
-        <v>5572.4</v>
-      </c>
-      <c r="G187" t="n">
         <v>6071.09</v>
       </c>
     </row>
@@ -5557,18 +5014,15 @@
         <v>5065.48</v>
       </c>
       <c r="C188" t="n">
-        <v>494.37</v>
+        <v>986.29</v>
       </c>
       <c r="D188" t="n">
-        <v>5559.85</v>
+        <v>6051.77</v>
       </c>
       <c r="E188" t="n">
-        <v>5256.18</v>
+        <v>5425.13</v>
       </c>
       <c r="F188" t="n">
-        <v>5559.85</v>
-      </c>
-      <c r="G188" t="n">
         <v>6051.77</v>
       </c>
     </row>
@@ -5582,18 +5036,15 @@
         <v>5039.86</v>
       </c>
       <c r="C189" t="n">
-        <v>507.45</v>
+        <v>992.59</v>
       </c>
       <c r="D189" t="n">
-        <v>5547.31</v>
+        <v>6032.45</v>
       </c>
       <c r="E189" t="n">
-        <v>5245.32</v>
+        <v>5410.94</v>
       </c>
       <c r="F189" t="n">
-        <v>5547.31</v>
-      </c>
-      <c r="G189" t="n">
         <v>6032.45</v>
       </c>
     </row>
@@ -5607,18 +5058,15 @@
         <v>5014.23</v>
       </c>
       <c r="C190" t="n">
-        <v>520.53</v>
+        <v>1028.46</v>
       </c>
       <c r="D190" t="n">
-        <v>5534.76</v>
+        <v>6042.69</v>
       </c>
       <c r="E190" t="n">
-        <v>5234.46</v>
+        <v>5402.66</v>
       </c>
       <c r="F190" t="n">
-        <v>5534.76</v>
-      </c>
-      <c r="G190" t="n">
         <v>6042.69</v>
       </c>
     </row>
@@ -5632,18 +5080,15 @@
         <v>4988.6</v>
       </c>
       <c r="C191" t="n">
-        <v>534.77</v>
+        <v>1064.33</v>
       </c>
       <c r="D191" t="n">
-        <v>5523.38</v>
+        <v>6052.94</v>
       </c>
       <c r="E191" t="n">
-        <v>5223.84</v>
+        <v>5394.61</v>
       </c>
       <c r="F191" t="n">
-        <v>5523.38</v>
-      </c>
-      <c r="G191" t="n">
         <v>6052.94</v>
       </c>
     </row>
@@ -5657,18 +5102,15 @@
         <v>4962.97</v>
       </c>
       <c r="C192" t="n">
-        <v>549.02</v>
+        <v>1100.2</v>
       </c>
       <c r="D192" t="n">
-        <v>5511.99</v>
+        <v>6063.18</v>
       </c>
       <c r="E192" t="n">
-        <v>5213.21</v>
+        <v>5386.57</v>
       </c>
       <c r="F192" t="n">
-        <v>5511.99</v>
-      </c>
-      <c r="G192" t="n">
         <v>6063.18</v>
       </c>
     </row>
@@ -5682,18 +5124,15 @@
         <v>4937.35</v>
       </c>
       <c r="C193" t="n">
-        <v>563.26</v>
+        <v>1136.07</v>
       </c>
       <c r="D193" t="n">
-        <v>5500.61</v>
+        <v>6073.42</v>
       </c>
       <c r="E193" t="n">
-        <v>5201.28</v>
+        <v>5377.21</v>
       </c>
       <c r="F193" t="n">
-        <v>5500.61</v>
-      </c>
-      <c r="G193" t="n">
         <v>6073.42</v>
       </c>
     </row>
@@ -5707,18 +5146,15 @@
         <v>4911.72</v>
       </c>
       <c r="C194" t="n">
-        <v>577.5</v>
+        <v>1171.94</v>
       </c>
       <c r="D194" t="n">
-        <v>5489.22</v>
+        <v>6083.66</v>
       </c>
       <c r="E194" t="n">
-        <v>5188.08</v>
+        <v>5366.6</v>
       </c>
       <c r="F194" t="n">
-        <v>5489.22</v>
-      </c>
-      <c r="G194" t="n">
         <v>6083.66</v>
       </c>
     </row>
@@ -5732,18 +5168,15 @@
         <v>4889.99</v>
       </c>
       <c r="C195" t="n">
-        <v>587.85</v>
+        <v>1203.92</v>
       </c>
       <c r="D195" t="n">
-        <v>5477.84</v>
+        <v>6093.91</v>
       </c>
       <c r="E195" t="n">
-        <v>5175.66</v>
+        <v>5356.76</v>
       </c>
       <c r="F195" t="n">
-        <v>5477.84</v>
-      </c>
-      <c r="G195" t="n">
         <v>6093.91</v>
       </c>
     </row>
@@ -5757,18 +5190,15 @@
         <v>4868.25</v>
       </c>
       <c r="C196" t="n">
-        <v>598.2</v>
+        <v>1235.9</v>
       </c>
       <c r="D196" t="n">
-        <v>5466.45</v>
+        <v>6104.15</v>
       </c>
       <c r="E196" t="n">
-        <v>5166.53</v>
+        <v>5346.93</v>
       </c>
       <c r="F196" t="n">
-        <v>5466.45</v>
-      </c>
-      <c r="G196" t="n">
         <v>6104.15</v>
       </c>
     </row>
@@ -5782,18 +5212,15 @@
         <v>4846.52</v>
       </c>
       <c r="C197" t="n">
-        <v>608.55</v>
+        <v>1273.08</v>
       </c>
       <c r="D197" t="n">
-        <v>5455.07</v>
+        <v>6119.6</v>
       </c>
       <c r="E197" t="n">
-        <v>5157.39</v>
+        <v>5338.13</v>
       </c>
       <c r="F197" t="n">
-        <v>5455.07</v>
-      </c>
-      <c r="G197" t="n">
         <v>6119.6</v>
       </c>
     </row>
@@ -5807,18 +5234,15 @@
         <v>4824.79</v>
       </c>
       <c r="C198" t="n">
-        <v>615.48</v>
+        <v>1310.26</v>
       </c>
       <c r="D198" t="n">
-        <v>5440.26</v>
+        <v>6135.05</v>
       </c>
       <c r="E198" t="n">
-        <v>5147.58</v>
+        <v>5328.66</v>
       </c>
       <c r="F198" t="n">
-        <v>5440.26</v>
-      </c>
-      <c r="G198" t="n">
         <v>6135.05</v>
       </c>
     </row>
@@ -5832,18 +5256,15 @@
         <v>4803.06</v>
       </c>
       <c r="C199" t="n">
-        <v>622.4</v>
+        <v>1347.44</v>
       </c>
       <c r="D199" t="n">
-        <v>5425.46</v>
+        <v>6150.5</v>
       </c>
       <c r="E199" t="n">
-        <v>5137.76</v>
+        <v>5319.18</v>
       </c>
       <c r="F199" t="n">
-        <v>5425.46</v>
-      </c>
-      <c r="G199" t="n">
         <v>6150.5</v>
       </c>
     </row>
@@ -5857,18 +5278,15 @@
         <v>4781.32</v>
       </c>
       <c r="C200" t="n">
-        <v>629.33</v>
+        <v>1384.63</v>
       </c>
       <c r="D200" t="n">
-        <v>5410.65</v>
+        <v>6165.95</v>
       </c>
       <c r="E200" t="n">
-        <v>5127.77</v>
+        <v>5309.53</v>
       </c>
       <c r="F200" t="n">
-        <v>5410.65</v>
-      </c>
-      <c r="G200" t="n">
         <v>6165.95</v>
       </c>
     </row>
@@ -5882,18 +5300,15 @@
         <v>4759.59</v>
       </c>
       <c r="C201" t="n">
-        <v>636.26</v>
+        <v>1421.81</v>
       </c>
       <c r="D201" t="n">
-        <v>5395.85</v>
+        <v>6181.4</v>
       </c>
       <c r="E201" t="n">
-        <v>5120.19</v>
+        <v>5302.29</v>
       </c>
       <c r="F201" t="n">
-        <v>5395.85</v>
-      </c>
-      <c r="G201" t="n">
         <v>6181.4</v>
       </c>
     </row>
@@ -5907,18 +5322,15 @@
         <v>4743.65</v>
       </c>
       <c r="C202" t="n">
-        <v>637.39</v>
+        <v>1453.2</v>
       </c>
       <c r="D202" t="n">
-        <v>5381.04</v>
+        <v>6196.85</v>
       </c>
       <c r="E202" t="n">
-        <v>5113.77</v>
+        <v>5296.21</v>
       </c>
       <c r="F202" t="n">
-        <v>5381.04</v>
-      </c>
-      <c r="G202" t="n">
         <v>6196.85</v>
       </c>
     </row>
@@ -5932,18 +5344,15 @@
         <v>4727.72</v>
       </c>
       <c r="C203" t="n">
-        <v>638.52</v>
+        <v>1484.58</v>
       </c>
       <c r="D203" t="n">
-        <v>5366.24</v>
+        <v>6212.3</v>
       </c>
       <c r="E203" t="n">
-        <v>5104.85</v>
+        <v>5290.12</v>
       </c>
       <c r="F203" t="n">
-        <v>5366.24</v>
-      </c>
-      <c r="G203" t="n">
         <v>6212.3</v>
       </c>
     </row>
@@ -5957,18 +5366,15 @@
         <v>4711.78</v>
       </c>
       <c r="C204" t="n">
-        <v>639.65</v>
+        <v>1489.94</v>
       </c>
       <c r="D204" t="n">
-        <v>5351.43</v>
+        <v>6201.72</v>
       </c>
       <c r="E204" t="n">
-        <v>5095.94</v>
+        <v>5278.84</v>
       </c>
       <c r="F204" t="n">
-        <v>5351.43</v>
-      </c>
-      <c r="G204" t="n">
         <v>6201.72</v>
       </c>
     </row>
@@ -5982,18 +5388,15 @@
         <v>4695.84</v>
       </c>
       <c r="C205" t="n">
-        <v>642.16</v>
+        <v>1495.3</v>
       </c>
       <c r="D205" t="n">
-        <v>5338</v>
+        <v>6191.15</v>
       </c>
       <c r="E205" t="n">
-        <v>5087.3</v>
+        <v>5267.82</v>
       </c>
       <c r="F205" t="n">
-        <v>5338</v>
-      </c>
-      <c r="G205" t="n">
         <v>6191.15</v>
       </c>
     </row>
@@ -6007,18 +5410,15 @@
         <v>4679.9</v>
       </c>
       <c r="C206" t="n">
-        <v>644.67</v>
+        <v>1500.66</v>
       </c>
       <c r="D206" t="n">
-        <v>5324.58</v>
+        <v>6180.57</v>
       </c>
       <c r="E206" t="n">
-        <v>5078.66</v>
+        <v>5256.81</v>
       </c>
       <c r="F206" t="n">
-        <v>5324.58</v>
-      </c>
-      <c r="G206" t="n">
         <v>6180.57</v>
       </c>
     </row>
@@ -6032,18 +5432,15 @@
         <v>4663.97</v>
       </c>
       <c r="C207" t="n">
-        <v>647.1900000000001</v>
+        <v>1506.02</v>
       </c>
       <c r="D207" t="n">
-        <v>5311.15</v>
+        <v>6169.99</v>
       </c>
       <c r="E207" t="n">
-        <v>5069.92</v>
+        <v>5245.69</v>
       </c>
       <c r="F207" t="n">
-        <v>5311.15</v>
-      </c>
-      <c r="G207" t="n">
         <v>6169.99</v>
       </c>
     </row>
@@ -6057,18 +5454,15 @@
         <v>4648.03</v>
       </c>
       <c r="C208" t="n">
-        <v>649.7</v>
+        <v>1511.38</v>
       </c>
       <c r="D208" t="n">
-        <v>5297.73</v>
+        <v>6159.41</v>
       </c>
       <c r="E208" t="n">
-        <v>5058.55</v>
+        <v>5231.95</v>
       </c>
       <c r="F208" t="n">
-        <v>5297.73</v>
-      </c>
-      <c r="G208" t="n">
         <v>6159.41</v>
       </c>
     </row>
@@ -6082,18 +5476,15 @@
         <v>4642.72</v>
       </c>
       <c r="C209" t="n">
-        <v>651.02</v>
+        <v>1506.11</v>
       </c>
       <c r="D209" t="n">
-        <v>5293.74</v>
+        <v>6148.84</v>
       </c>
       <c r="E209" t="n">
-        <v>5049.31</v>
+        <v>5220.33</v>
       </c>
       <c r="F209" t="n">
-        <v>5284.3</v>
-      </c>
-      <c r="G209" t="n">
         <v>6148.84</v>
       </c>
     </row>
@@ -6107,18 +5498,15 @@
         <v>4637.42</v>
       </c>
       <c r="C210" t="n">
-        <v>647.4400000000001</v>
+        <v>1500.84</v>
       </c>
       <c r="D210" t="n">
-        <v>5284.85</v>
+        <v>6138.26</v>
       </c>
       <c r="E210" t="n">
-        <v>5038.03</v>
+        <v>5208.72</v>
       </c>
       <c r="F210" t="n">
-        <v>5270.88</v>
-      </c>
-      <c r="G210" t="n">
         <v>6138.26</v>
       </c>
     </row>
@@ -6132,18 +5520,15 @@
         <v>4632.11</v>
       </c>
       <c r="C211" t="n">
-        <v>643.85</v>
+        <v>1490.7</v>
       </c>
       <c r="D211" t="n">
-        <v>5275.96</v>
+        <v>6122.81</v>
       </c>
       <c r="E211" t="n">
-        <v>5026.75</v>
+        <v>5196.12</v>
       </c>
       <c r="F211" t="n">
-        <v>5257.45</v>
-      </c>
-      <c r="G211" t="n">
         <v>6122.81</v>
       </c>
     </row>
@@ -6157,18 +5542,15 @@
         <v>4626.8</v>
       </c>
       <c r="C212" t="n">
-        <v>640.27</v>
+        <v>1480.55</v>
       </c>
       <c r="D212" t="n">
-        <v>5267.07</v>
+        <v>6107.35</v>
       </c>
       <c r="E212" t="n">
-        <v>5014.62</v>
+        <v>5182.67</v>
       </c>
       <c r="F212" t="n">
-        <v>5239.74</v>
-      </c>
-      <c r="G212" t="n">
         <v>6107.35</v>
       </c>
     </row>
@@ -6182,18 +5564,15 @@
         <v>4621.49</v>
       </c>
       <c r="C213" t="n">
-        <v>636.6900000000001</v>
+        <v>1470.4</v>
       </c>
       <c r="D213" t="n">
-        <v>5258.19</v>
+        <v>6091.9</v>
       </c>
       <c r="E213" t="n">
-        <v>5002.48</v>
+        <v>5169.23</v>
       </c>
       <c r="F213" t="n">
-        <v>5222.04</v>
-      </c>
-      <c r="G213" t="n">
         <v>6091.9</v>
       </c>
     </row>
@@ -6207,18 +5586,15 @@
         <v>4616.19</v>
       </c>
       <c r="C214" t="n">
-        <v>633.11</v>
+        <v>1460.26</v>
       </c>
       <c r="D214" t="n">
-        <v>5249.3</v>
+        <v>6076.44</v>
       </c>
       <c r="E214" t="n">
-        <v>4990.15</v>
+        <v>5155.58</v>
       </c>
       <c r="F214" t="n">
-        <v>5204.33</v>
-      </c>
-      <c r="G214" t="n">
         <v>6076.44</v>
       </c>
       <c r="H214" t="inlineStr">
@@ -6237,18 +5613,15 @@
         <v>4610.88</v>
       </c>
       <c r="C215" t="n">
-        <v>629.53</v>
+        <v>1450.11</v>
       </c>
       <c r="D215" t="n">
-        <v>5240.41</v>
+        <v>6060.99</v>
       </c>
       <c r="E215" t="n">
-        <v>4977.11</v>
+        <v>5141.22</v>
       </c>
       <c r="F215" t="n">
-        <v>5186.62</v>
-      </c>
-      <c r="G215" t="n">
         <v>6060.99</v>
       </c>
     </row>
@@ -6262,18 +5635,15 @@
         <v>4621.34</v>
       </c>
       <c r="C216" t="n">
-        <v>610.1799999999999</v>
+        <v>1424.19</v>
       </c>
       <c r="D216" t="n">
-        <v>5231.52</v>
+        <v>6045.53</v>
       </c>
       <c r="E216" t="n">
-        <v>4967.22</v>
+        <v>5130.02</v>
       </c>
       <c r="F216" t="n">
-        <v>5168.91</v>
-      </c>
-      <c r="G216" t="n">
         <v>6045.53</v>
       </c>
     </row>
@@ -6287,18 +5657,15 @@
         <v>4631.81</v>
       </c>
       <c r="C217" t="n">
-        <v>583.55</v>
+        <v>1398.27</v>
       </c>
       <c r="D217" t="n">
-        <v>5215.36</v>
+        <v>6030.08</v>
       </c>
       <c r="E217" t="n">
-        <v>4955.88</v>
+        <v>5118.82</v>
       </c>
       <c r="F217" t="n">
-        <v>5151.21</v>
-      </c>
-      <c r="G217" t="n">
         <v>6030.08</v>
       </c>
     </row>
@@ -6312,18 +5679,15 @@
         <v>4642.27</v>
       </c>
       <c r="C218" t="n">
-        <v>556.9299999999999</v>
+        <v>1398.8</v>
       </c>
       <c r="D218" t="n">
-        <v>5199.2</v>
+        <v>6041.07</v>
       </c>
       <c r="E218" t="n">
-        <v>4944.54</v>
+        <v>5112.91</v>
       </c>
       <c r="F218" t="n">
-        <v>5133.5</v>
-      </c>
-      <c r="G218" t="n">
         <v>6041.07</v>
       </c>
     </row>
@@ -6337,18 +5701,15 @@
         <v>4652.73</v>
       </c>
       <c r="C219" t="n">
-        <v>530.3099999999999</v>
+        <v>1399.33</v>
       </c>
       <c r="D219" t="n">
-        <v>5183.04</v>
+        <v>6052.06</v>
       </c>
       <c r="E219" t="n">
-        <v>4938.48</v>
+        <v>5112.28</v>
       </c>
       <c r="F219" t="n">
-        <v>5142.2</v>
-      </c>
-      <c r="G219" t="n">
         <v>6052.06</v>
       </c>
     </row>
@@ -6362,18 +5723,15 @@
         <v>4663.19</v>
       </c>
       <c r="C220" t="n">
-        <v>503.69</v>
+        <v>1399.86</v>
       </c>
       <c r="D220" t="n">
-        <v>5166.88</v>
+        <v>6063.05</v>
       </c>
       <c r="E220" t="n">
-        <v>4932.42</v>
+        <v>5111.65</v>
       </c>
       <c r="F220" t="n">
-        <v>5150.91</v>
-      </c>
-      <c r="G220" t="n">
         <v>6063.05</v>
       </c>
     </row>
@@ -6387,18 +5745,15 @@
         <v>4673.66</v>
       </c>
       <c r="C221" t="n">
-        <v>485.96</v>
+        <v>1400.39</v>
       </c>
       <c r="D221" t="n">
-        <v>5159.61</v>
+        <v>6074.05</v>
       </c>
       <c r="E221" t="n">
-        <v>4926.23</v>
+        <v>5110.9</v>
       </c>
       <c r="F221" t="n">
-        <v>5159.61</v>
-      </c>
-      <c r="G221" t="n">
         <v>6074.05</v>
       </c>
     </row>
@@ -6412,18 +5767,15 @@
         <v>4671.19</v>
       </c>
       <c r="C222" t="n">
-        <v>497.13</v>
+        <v>1413.85</v>
       </c>
       <c r="D222" t="n">
-        <v>5168.32</v>
+        <v>6085.04</v>
       </c>
       <c r="E222" t="n">
-        <v>4919.9</v>
+        <v>5110</v>
       </c>
       <c r="F222" t="n">
-        <v>5168.32</v>
-      </c>
-      <c r="G222" t="n">
         <v>6085.04</v>
       </c>
     </row>
@@ -6437,18 +5789,15 @@
         <v>4653.4</v>
       </c>
       <c r="C223" t="n">
-        <v>523.62</v>
+        <v>1442.63</v>
       </c>
       <c r="D223" t="n">
-        <v>5177.02</v>
+        <v>6096.03</v>
       </c>
       <c r="E223" t="n">
-        <v>4908.74</v>
+        <v>5104.26</v>
       </c>
       <c r="F223" t="n">
-        <v>5177.02</v>
-      </c>
-      <c r="G223" t="n">
         <v>6096.03</v>
       </c>
     </row>
@@ -6462,18 +5811,15 @@
         <v>4635.62</v>
       </c>
       <c r="C224" t="n">
-        <v>550.11</v>
+        <v>1471.4</v>
       </c>
       <c r="D224" t="n">
-        <v>5185.73</v>
+        <v>6107.02</v>
       </c>
       <c r="E224" t="n">
-        <v>4901.7</v>
+        <v>5098.53</v>
       </c>
       <c r="F224" t="n">
-        <v>5185.73</v>
-      </c>
-      <c r="G224" t="n">
         <v>6107.02</v>
       </c>
     </row>
@@ -6487,18 +5833,15 @@
         <v>4617.83</v>
       </c>
       <c r="C225" t="n">
-        <v>576.6</v>
+        <v>1475.03</v>
       </c>
       <c r="D225" t="n">
-        <v>5194.43</v>
+        <v>6092.86</v>
       </c>
       <c r="E225" t="n">
-        <v>4894.67</v>
+        <v>5087.76</v>
       </c>
       <c r="F225" t="n">
-        <v>5194.43</v>
-      </c>
-      <c r="G225" t="n">
         <v>6092.86</v>
       </c>
     </row>
@@ -6512,18 +5855,15 @@
         <v>4600.05</v>
       </c>
       <c r="C226" t="n">
-        <v>582.67</v>
+        <v>1478.66</v>
       </c>
       <c r="D226" t="n">
-        <v>5182.72</v>
+        <v>6078.71</v>
       </c>
       <c r="E226" t="n">
-        <v>4883.55</v>
+        <v>5072.92</v>
       </c>
       <c r="F226" t="n">
-        <v>5182.72</v>
-      </c>
-      <c r="G226" t="n">
         <v>6078.71</v>
       </c>
     </row>
@@ -6537,18 +5877,15 @@
         <v>4582.26</v>
       </c>
       <c r="C227" t="n">
-        <v>588.74</v>
+        <v>1482.29</v>
       </c>
       <c r="D227" t="n">
-        <v>5171</v>
+        <v>6064.55</v>
       </c>
       <c r="E227" t="n">
-        <v>4872.43</v>
+        <v>5058.07</v>
       </c>
       <c r="F227" t="n">
-        <v>5171</v>
-      </c>
-      <c r="G227" t="n">
         <v>6064.55</v>
       </c>
     </row>
@@ -6562,18 +5899,15 @@
         <v>4579.26</v>
       </c>
       <c r="C228" t="n">
-        <v>580.03</v>
+        <v>1471.14</v>
       </c>
       <c r="D228" t="n">
-        <v>5159.29</v>
+        <v>6050.4</v>
       </c>
       <c r="E228" t="n">
-        <v>4864.27</v>
+        <v>5046.18</v>
       </c>
       <c r="F228" t="n">
-        <v>5159.29</v>
-      </c>
-      <c r="G228" t="n">
         <v>6050.4</v>
       </c>
     </row>
@@ -6587,18 +5921,15 @@
         <v>4576.26</v>
       </c>
       <c r="C229" t="n">
-        <v>571.3200000000001</v>
+        <v>1459.98</v>
       </c>
       <c r="D229" t="n">
-        <v>5147.58</v>
+        <v>6036.24</v>
       </c>
       <c r="E229" t="n">
-        <v>4858.19</v>
+        <v>5036.37</v>
       </c>
       <c r="F229" t="n">
-        <v>5147.58</v>
-      </c>
-      <c r="G229" t="n">
         <v>6036.24</v>
       </c>
     </row>
@@ -6612,18 +5943,15 @@
         <v>4573.26</v>
       </c>
       <c r="C230" t="n">
-        <v>576.62</v>
+        <v>1448.82</v>
       </c>
       <c r="D230" t="n">
-        <v>5149.88</v>
+        <v>6022.09</v>
       </c>
       <c r="E230" t="n">
-        <v>4859.68</v>
+        <v>5034.12</v>
       </c>
       <c r="F230" t="n">
-        <v>5135.87</v>
-      </c>
-      <c r="G230" t="n">
         <v>6022.09</v>
       </c>
     </row>
@@ -6637,18 +5965,15 @@
         <v>4570.27</v>
       </c>
       <c r="C231" t="n">
-        <v>577.5700000000001</v>
+        <v>1437.66</v>
       </c>
       <c r="D231" t="n">
-        <v>5147.84</v>
+        <v>6007.93</v>
       </c>
       <c r="E231" t="n">
-        <v>4859.85</v>
+        <v>5031.87</v>
       </c>
       <c r="F231" t="n">
-        <v>5124.15</v>
-      </c>
-      <c r="G231" t="n">
         <v>6007.93</v>
       </c>
     </row>
@@ -6662,18 +5987,15 @@
         <v>4567.27</v>
       </c>
       <c r="C232" t="n">
-        <v>578.53</v>
+        <v>1424.38</v>
       </c>
       <c r="D232" t="n">
-        <v>5145.8</v>
+        <v>5991.65</v>
       </c>
       <c r="E232" t="n">
-        <v>4860.03</v>
+        <v>5029.2</v>
       </c>
       <c r="F232" t="n">
-        <v>5112.44</v>
-      </c>
-      <c r="G232" t="n">
         <v>5991.65</v>
       </c>
     </row>
@@ -6687,18 +6009,15 @@
         <v>4564.27</v>
       </c>
       <c r="C233" t="n">
-        <v>579.49</v>
+        <v>1411.09</v>
       </c>
       <c r="D233" t="n">
-        <v>5143.76</v>
+        <v>5975.36</v>
       </c>
       <c r="E233" t="n">
-        <v>4860.75</v>
+        <v>5027.07</v>
       </c>
       <c r="F233" t="n">
-        <v>5103.46</v>
-      </c>
-      <c r="G233" t="n">
         <v>5975.36</v>
       </c>
     </row>
@@ -6712,18 +6031,15 @@
         <v>4561.27</v>
       </c>
       <c r="C234" t="n">
-        <v>580.45</v>
+        <v>1397.81</v>
       </c>
       <c r="D234" t="n">
-        <v>5141.72</v>
+        <v>5959.08</v>
       </c>
       <c r="E234" t="n">
-        <v>4861.48</v>
+        <v>5024.95</v>
       </c>
       <c r="F234" t="n">
-        <v>5094.49</v>
-      </c>
-      <c r="G234" t="n">
         <v>5959.08</v>
       </c>
     </row>
@@ -6737,18 +6053,15 @@
         <v>4545.28</v>
       </c>
       <c r="C235" t="n">
-        <v>594.4</v>
+        <v>1397.51</v>
       </c>
       <c r="D235" t="n">
-        <v>5139.68</v>
+        <v>5942.79</v>
       </c>
       <c r="E235" t="n">
-        <v>4859.6</v>
+        <v>5020.23</v>
       </c>
       <c r="F235" t="n">
-        <v>5085.51</v>
-      </c>
-      <c r="G235" t="n">
         <v>5942.79</v>
       </c>
     </row>
@@ -6762,18 +6075,15 @@
         <v>4529.3</v>
       </c>
       <c r="C236" t="n">
-        <v>608.34</v>
+        <v>1397.21</v>
       </c>
       <c r="D236" t="n">
-        <v>5137.64</v>
+        <v>5926.51</v>
       </c>
       <c r="E236" t="n">
-        <v>4862.07</v>
+        <v>5019.84</v>
       </c>
       <c r="F236" t="n">
-        <v>5076.54</v>
-      </c>
-      <c r="G236" t="n">
         <v>5926.51</v>
       </c>
     </row>
@@ -6787,18 +6097,15 @@
         <v>4513.31</v>
       </c>
       <c r="C237" t="n">
-        <v>622.29</v>
+        <v>1396.92</v>
       </c>
       <c r="D237" t="n">
-        <v>5135.6</v>
+        <v>5910.22</v>
       </c>
       <c r="E237" t="n">
-        <v>4856.19</v>
+        <v>5011.11</v>
       </c>
       <c r="F237" t="n">
-        <v>5067.56</v>
-      </c>
-      <c r="G237" t="n">
         <v>5910.22</v>
       </c>
     </row>
@@ -6812,18 +6119,15 @@
         <v>4497.32</v>
       </c>
       <c r="C238" t="n">
-        <v>650.3099999999999</v>
+        <v>1396.62</v>
       </c>
       <c r="D238" t="n">
-        <v>5147.63</v>
+        <v>5893.94</v>
       </c>
       <c r="E238" t="n">
-        <v>4853.13</v>
+        <v>5002.39</v>
       </c>
       <c r="F238" t="n">
-        <v>5058.59</v>
-      </c>
-      <c r="G238" t="n">
         <v>5893.94</v>
       </c>
     </row>
@@ -6837,18 +6141,15 @@
         <v>4481.33</v>
       </c>
       <c r="C239" t="n">
-        <v>678.33</v>
+        <v>1406.13</v>
       </c>
       <c r="D239" t="n">
-        <v>5159.67</v>
+        <v>5887.46</v>
       </c>
       <c r="E239" t="n">
-        <v>4850.07</v>
+        <v>4995.63</v>
       </c>
       <c r="F239" t="n">
-        <v>5049.61</v>
-      </c>
-      <c r="G239" t="n">
         <v>5887.46</v>
       </c>
     </row>
@@ -6862,18 +6163,15 @@
         <v>4465.35</v>
       </c>
       <c r="C240" t="n">
-        <v>706.36</v>
+        <v>1415.63</v>
       </c>
       <c r="D240" t="n">
-        <v>5171.7</v>
+        <v>5880.98</v>
       </c>
       <c r="E240" t="n">
-        <v>4847.27</v>
+        <v>4989.12</v>
       </c>
       <c r="F240" t="n">
-        <v>5041.94</v>
-      </c>
-      <c r="G240" t="n">
         <v>5880.98</v>
       </c>
     </row>
@@ -6887,18 +6185,15 @@
         <v>4449.36</v>
       </c>
       <c r="C241" t="n">
-        <v>734.38</v>
+        <v>1425.14</v>
       </c>
       <c r="D241" t="n">
-        <v>5183.74</v>
+        <v>5874.5</v>
       </c>
       <c r="E241" t="n">
-        <v>4844.47</v>
+        <v>4982.62</v>
       </c>
       <c r="F241" t="n">
-        <v>5034.26</v>
-      </c>
-      <c r="G241" t="n">
         <v>5874.5</v>
       </c>
     </row>
@@ -6912,18 +6207,15 @@
         <v>4451.51</v>
       </c>
       <c r="C242" t="n">
-        <v>744.26</v>
+        <v>1416.51</v>
       </c>
       <c r="D242" t="n">
-        <v>5195.77</v>
+        <v>5868.02</v>
       </c>
       <c r="E242" t="n">
-        <v>4845.3</v>
+        <v>4979.75</v>
       </c>
       <c r="F242" t="n">
-        <v>5026.59</v>
-      </c>
-      <c r="G242" t="n">
         <v>5868.02</v>
       </c>
     </row>
@@ -6937,18 +6229,15 @@
         <v>4453.66</v>
       </c>
       <c r="C243" t="n">
-        <v>754.15</v>
+        <v>1407.88</v>
       </c>
       <c r="D243" t="n">
-        <v>5207.81</v>
+        <v>5861.54</v>
       </c>
       <c r="E243" t="n">
-        <v>4852</v>
+        <v>4982.74</v>
       </c>
       <c r="F243" t="n">
-        <v>5018.91</v>
-      </c>
-      <c r="G243" t="n">
         <v>5861.54</v>
       </c>
     </row>
@@ -6962,18 +6251,15 @@
         <v>4455.81</v>
       </c>
       <c r="C244" t="n">
-        <v>764.03</v>
+        <v>1399.25</v>
       </c>
       <c r="D244" t="n">
-        <v>5219.84</v>
+        <v>5855.06</v>
       </c>
       <c r="E244" t="n">
-        <v>4860.66</v>
+        <v>4987.7</v>
       </c>
       <c r="F244" t="n">
-        <v>5011.24</v>
-      </c>
-      <c r="G244" t="n">
         <v>5855.06</v>
       </c>
     </row>
@@ -6987,18 +6273,15 @@
         <v>4457.96</v>
       </c>
       <c r="C245" t="n">
-        <v>757.71</v>
+        <v>1390.62</v>
       </c>
       <c r="D245" t="n">
-        <v>5215.67</v>
+        <v>5848.58</v>
       </c>
       <c r="E245" t="n">
-        <v>4866.08</v>
+        <v>4992.66</v>
       </c>
       <c r="F245" t="n">
-        <v>5003.56</v>
-      </c>
-      <c r="G245" t="n">
         <v>5848.58</v>
       </c>
       <c r="H245" t="inlineStr">
@@ -7017,18 +6300,15 @@
         <v>4460.11</v>
       </c>
       <c r="C246" t="n">
-        <v>751.38</v>
+        <v>1400.52</v>
       </c>
       <c r="D246" t="n">
-        <v>5211.49</v>
+        <v>5860.63</v>
       </c>
       <c r="E246" t="n">
-        <v>4871.5</v>
+        <v>5001.33</v>
       </c>
       <c r="F246" t="n">
-        <v>4995.89</v>
-      </c>
-      <c r="G246" t="n">
         <v>5860.63</v>
       </c>
     </row>
@@ -7042,18 +6322,15 @@
         <v>4462.26</v>
       </c>
       <c r="C247" t="n">
-        <v>745.0599999999999</v>
+        <v>1410.42</v>
       </c>
       <c r="D247" t="n">
-        <v>5207.32</v>
+        <v>5872.68</v>
       </c>
       <c r="E247" t="n">
-        <v>4877.54</v>
+        <v>5010.61</v>
       </c>
       <c r="F247" t="n">
-        <v>4991.31</v>
-      </c>
-      <c r="G247" t="n">
         <v>5872.68</v>
       </c>
     </row>
@@ -7067,18 +6344,15 @@
         <v>4464.41</v>
       </c>
       <c r="C248" t="n">
-        <v>738.73</v>
+        <v>1420.32</v>
       </c>
       <c r="D248" t="n">
-        <v>5203.14</v>
+        <v>5884.73</v>
       </c>
       <c r="E248" t="n">
-        <v>4883.58</v>
+        <v>5019.89</v>
       </c>
       <c r="F248" t="n">
-        <v>4986.74</v>
-      </c>
-      <c r="G248" t="n">
         <v>5884.73</v>
       </c>
     </row>
@@ -7092,18 +6366,15 @@
         <v>4450.15</v>
       </c>
       <c r="C249" t="n">
-        <v>763.35</v>
+        <v>1446.62</v>
       </c>
       <c r="D249" t="n">
-        <v>5213.5</v>
+        <v>5896.77</v>
       </c>
       <c r="E249" t="n">
-        <v>4886.33</v>
+        <v>5025.9</v>
       </c>
       <c r="F249" t="n">
-        <v>4982.16</v>
-      </c>
-      <c r="G249" t="n">
         <v>5896.77</v>
       </c>
     </row>
@@ -7117,18 +6388,15 @@
         <v>4435.9</v>
       </c>
       <c r="C250" t="n">
-        <v>816.9400000000001</v>
+        <v>1472.92</v>
       </c>
       <c r="D250" t="n">
-        <v>5252.84</v>
+        <v>5908.82</v>
       </c>
       <c r="E250" t="n">
-        <v>4888.04</v>
+        <v>5030.85</v>
       </c>
       <c r="F250" t="n">
-        <v>4977.58</v>
-      </c>
-      <c r="G250" t="n">
         <v>5908.82</v>
       </c>
     </row>
@@ -7142,18 +6410,15 @@
         <v>4421.64</v>
       </c>
       <c r="C251" t="n">
-        <v>870.53</v>
+        <v>1499.23</v>
       </c>
       <c r="D251" t="n">
-        <v>5292.18</v>
+        <v>5920.87</v>
       </c>
       <c r="E251" t="n">
-        <v>4897.44</v>
+        <v>5043.49</v>
       </c>
       <c r="F251" t="n">
-        <v>4973</v>
-      </c>
-      <c r="G251" t="n">
         <v>5920.87</v>
       </c>
     </row>
@@ -7167,18 +6432,15 @@
         <v>4407.39</v>
       </c>
       <c r="C252" t="n">
-        <v>924.13</v>
+        <v>1525.53</v>
       </c>
       <c r="D252" t="n">
-        <v>5331.52</v>
+        <v>5932.92</v>
       </c>
       <c r="E252" t="n">
-        <v>4914.33</v>
+        <v>5056.14</v>
       </c>
       <c r="F252" t="n">
-        <v>4968.43</v>
-      </c>
-      <c r="G252" t="n">
         <v>5932.92</v>
       </c>
     </row>
@@ -7192,18 +6454,15 @@
         <v>4393.13</v>
       </c>
       <c r="C253" t="n">
-        <v>977.72</v>
+        <v>1546.21</v>
       </c>
       <c r="D253" t="n">
-        <v>5370.85</v>
+        <v>5939.34</v>
       </c>
       <c r="E253" t="n">
-        <v>4931.22</v>
+        <v>5067.66</v>
       </c>
       <c r="F253" t="n">
-        <v>4963.85</v>
-      </c>
-      <c r="G253" t="n">
         <v>5939.34</v>
       </c>
     </row>
@@ -7217,18 +6476,15 @@
         <v>4378.88</v>
       </c>
       <c r="C254" t="n">
-        <v>1031.32</v>
+        <v>1566.88</v>
       </c>
       <c r="D254" t="n">
-        <v>5410.19</v>
+        <v>5945.76</v>
       </c>
       <c r="E254" t="n">
-        <v>4945.73</v>
+        <v>5076.8</v>
       </c>
       <c r="F254" t="n">
-        <v>4947.38</v>
-      </c>
-      <c r="G254" t="n">
         <v>5945.76</v>
       </c>
     </row>
@@ -7242,18 +6498,15 @@
         <v>4364.62</v>
       </c>
       <c r="C255" t="n">
-        <v>1084.91</v>
+        <v>1587.56</v>
       </c>
       <c r="D255" t="n">
-        <v>5449.53</v>
+        <v>5952.18</v>
       </c>
       <c r="E255" t="n">
-        <v>4960.24</v>
+        <v>5085.94</v>
       </c>
       <c r="F255" t="n">
-        <v>4930.91</v>
-      </c>
-      <c r="G255" t="n">
         <v>5952.18</v>
       </c>
     </row>
@@ -7267,18 +6520,15 @@
         <v>4382.51</v>
       </c>
       <c r="C256" t="n">
-        <v>1106.36</v>
+        <v>1576.08</v>
       </c>
       <c r="D256" t="n">
-        <v>5488.87</v>
+        <v>5958.59</v>
       </c>
       <c r="E256" t="n">
-        <v>4981.17</v>
+        <v>5101.51</v>
       </c>
       <c r="F256" t="n">
-        <v>4914.44</v>
-      </c>
-      <c r="G256" t="n">
         <v>5958.59</v>
       </c>
     </row>
@@ -7292,18 +6542,15 @@
         <v>4400.41</v>
       </c>
       <c r="C257" t="n">
-        <v>1111.2</v>
+        <v>1564.6</v>
       </c>
       <c r="D257" t="n">
-        <v>5511.61</v>
+        <v>5965.01</v>
       </c>
       <c r="E257" t="n">
-        <v>4998.79</v>
+        <v>5113.76</v>
       </c>
       <c r="F257" t="n">
-        <v>4897.96</v>
-      </c>
-      <c r="G257" t="n">
         <v>5965.01</v>
       </c>
     </row>
@@ -7317,18 +6564,15 @@
         <v>4418.3</v>
       </c>
       <c r="C258" t="n">
-        <v>1116.05</v>
+        <v>1553.13</v>
       </c>
       <c r="D258" t="n">
-        <v>5534.36</v>
+        <v>5971.43</v>
       </c>
       <c r="E258" t="n">
-        <v>5008.26</v>
+        <v>5117.86</v>
       </c>
       <c r="F258" t="n">
-        <v>4881.49</v>
-      </c>
-      <c r="G258" t="n">
         <v>5971.43</v>
       </c>
     </row>
@@ -7342,18 +6586,15 @@
         <v>4436.2</v>
       </c>
       <c r="C259" t="n">
-        <v>1120.9</v>
+        <v>1541.65</v>
       </c>
       <c r="D259" t="n">
-        <v>5557.1</v>
+        <v>5977.85</v>
       </c>
       <c r="E259" t="n">
-        <v>5008.4</v>
+        <v>5121.96</v>
       </c>
       <c r="F259" t="n">
-        <v>4865.02</v>
-      </c>
-      <c r="G259" t="n">
         <v>5977.85</v>
       </c>
     </row>
@@ -7367,18 +6608,15 @@
         <v>4454.09</v>
       </c>
       <c r="C260" t="n">
-        <v>1125.75</v>
+        <v>1547.99</v>
       </c>
       <c r="D260" t="n">
-        <v>5579.84</v>
+        <v>6002.08</v>
       </c>
       <c r="E260" t="n">
-        <v>5008.53</v>
+        <v>5129.62</v>
       </c>
       <c r="F260" t="n">
-        <v>4848.55</v>
-      </c>
-      <c r="G260" t="n">
         <v>6002.08</v>
       </c>
     </row>
@@ -7392,18 +6630,15 @@
         <v>4471.99</v>
       </c>
       <c r="C261" t="n">
-        <v>1130.6</v>
+        <v>1554.33</v>
       </c>
       <c r="D261" t="n">
-        <v>5602.58</v>
+        <v>6026.32</v>
       </c>
       <c r="E261" t="n">
-        <v>5012.11</v>
+        <v>5140.72</v>
       </c>
       <c r="F261" t="n">
-        <v>4849.28</v>
-      </c>
-      <c r="G261" t="n">
         <v>6026.32</v>
       </c>
     </row>
@@ -7417,18 +6652,15 @@
         <v>4489.88</v>
       </c>
       <c r="C262" t="n">
-        <v>1135.45</v>
+        <v>1560.67</v>
       </c>
       <c r="D262" t="n">
-        <v>5625.33</v>
+        <v>6050.55</v>
       </c>
       <c r="E262" t="n">
-        <v>5015.69</v>
+        <v>5151.82</v>
       </c>
       <c r="F262" t="n">
-        <v>4850.01</v>
-      </c>
-      <c r="G262" t="n">
         <v>6050.55</v>
       </c>
     </row>
@@ -7442,18 +6674,15 @@
         <v>4471.59</v>
       </c>
       <c r="C263" t="n">
-        <v>1176.48</v>
+        <v>1603.19</v>
       </c>
       <c r="D263" t="n">
-        <v>5648.07</v>
+        <v>6074.78</v>
       </c>
       <c r="E263" t="n">
-        <v>5012.03</v>
+        <v>5155.68</v>
       </c>
       <c r="F263" t="n">
-        <v>4850.74</v>
-      </c>
-      <c r="G263" t="n">
         <v>6074.78</v>
       </c>
     </row>
@@ -7467,18 +6696,15 @@
         <v>4453.3</v>
       </c>
       <c r="C264" t="n">
-        <v>1207</v>
+        <v>1645.71</v>
       </c>
       <c r="D264" t="n">
-        <v>5660.3</v>
+        <v>6099.01</v>
       </c>
       <c r="E264" t="n">
-        <v>5006.27</v>
+        <v>5157.44</v>
       </c>
       <c r="F264" t="n">
-        <v>4851.47</v>
-      </c>
-      <c r="G264" t="n">
         <v>6099.01</v>
       </c>
     </row>
@@ -7492,18 +6718,15 @@
         <v>4435.01</v>
       </c>
       <c r="C265" t="n">
-        <v>1237.52</v>
+        <v>1688.24</v>
       </c>
       <c r="D265" t="n">
-        <v>5672.53</v>
+        <v>6123.25</v>
       </c>
       <c r="E265" t="n">
-        <v>5008.17</v>
+        <v>5166.87</v>
       </c>
       <c r="F265" t="n">
-        <v>4852.2</v>
-      </c>
-      <c r="G265" t="n">
         <v>6123.25</v>
       </c>
     </row>
@@ -7517,18 +6740,15 @@
         <v>4416.72</v>
       </c>
       <c r="C266" t="n">
-        <v>1268.04</v>
+        <v>1730.76</v>
       </c>
       <c r="D266" t="n">
-        <v>5684.76</v>
+        <v>6147.48</v>
       </c>
       <c r="E266" t="n">
-        <v>5011.37</v>
+        <v>5176.3</v>
       </c>
       <c r="F266" t="n">
-        <v>4852.93</v>
-      </c>
-      <c r="G266" t="n">
         <v>6147.48</v>
       </c>
     </row>
@@ -7542,18 +6762,15 @@
         <v>4398.43</v>
       </c>
       <c r="C267" t="n">
-        <v>1298.56</v>
+        <v>1738.33</v>
       </c>
       <c r="D267" t="n">
-        <v>5696.99</v>
+        <v>6136.76</v>
       </c>
       <c r="E267" t="n">
-        <v>5014.56</v>
+        <v>5178.73</v>
       </c>
       <c r="F267" t="n">
-        <v>4853.66</v>
-      </c>
-      <c r="G267" t="n">
         <v>6136.76</v>
       </c>
     </row>
@@ -7567,18 +6784,15 @@
         <v>4380.14</v>
       </c>
       <c r="C268" t="n">
-        <v>1329.08</v>
+        <v>1745.91</v>
       </c>
       <c r="D268" t="n">
-        <v>5709.22</v>
+        <v>6126.05</v>
       </c>
       <c r="E268" t="n">
-        <v>5018.45</v>
+        <v>5181.87</v>
       </c>
       <c r="F268" t="n">
-        <v>4857.89</v>
-      </c>
-      <c r="G268" t="n">
         <v>6126.05</v>
       </c>
     </row>
@@ -7592,18 +6806,15 @@
         <v>4361.85</v>
       </c>
       <c r="C269" t="n">
-        <v>1359.6</v>
+        <v>1753.48</v>
       </c>
       <c r="D269" t="n">
-        <v>5721.45</v>
+        <v>6115.33</v>
       </c>
       <c r="E269" t="n">
-        <v>5022.34</v>
+        <v>5185.01</v>
       </c>
       <c r="F269" t="n">
-        <v>4862.13</v>
-      </c>
-      <c r="G269" t="n">
         <v>6115.33</v>
       </c>
     </row>
@@ -7617,18 +6828,15 @@
         <v>4394.03</v>
       </c>
       <c r="C270" t="n">
-        <v>1339.65</v>
+        <v>1710.59</v>
       </c>
       <c r="D270" t="n">
-        <v>5733.68</v>
+        <v>6104.62</v>
       </c>
       <c r="E270" t="n">
-        <v>5036.32</v>
+        <v>5198.24</v>
       </c>
       <c r="F270" t="n">
-        <v>4866.36</v>
-      </c>
-      <c r="G270" t="n">
         <v>6104.62</v>
       </c>
     </row>
@@ -7642,18 +6850,15 @@
         <v>4426.2</v>
       </c>
       <c r="C271" t="n">
-        <v>1329.96</v>
+        <v>1667.7</v>
       </c>
       <c r="D271" t="n">
-        <v>5756.16</v>
+        <v>6093.9</v>
       </c>
       <c r="E271" t="n">
-        <v>5052.36</v>
+        <v>5213.52</v>
       </c>
       <c r="F271" t="n">
-        <v>4870.59</v>
-      </c>
-      <c r="G271" t="n">
         <v>6093.9</v>
       </c>
     </row>
@@ -7667,18 +6872,15 @@
         <v>4458.38</v>
       </c>
       <c r="C272" t="n">
-        <v>1320.26</v>
+        <v>1624.81</v>
       </c>
       <c r="D272" t="n">
-        <v>5778.64</v>
+        <v>6083.19</v>
       </c>
       <c r="E272" t="n">
-        <v>5061.63</v>
+        <v>5222.04</v>
       </c>
       <c r="F272" t="n">
-        <v>4874.82</v>
-      </c>
-      <c r="G272" t="n">
         <v>6083.19</v>
       </c>
     </row>
@@ -7692,18 +6894,15 @@
         <v>4490.55</v>
       </c>
       <c r="C273" t="n">
-        <v>1310.56</v>
+        <v>1581.92</v>
       </c>
       <c r="D273" t="n">
-        <v>5801.12</v>
+        <v>6072.47</v>
       </c>
       <c r="E273" t="n">
-        <v>5073.19</v>
+        <v>5230.56</v>
       </c>
       <c r="F273" t="n">
-        <v>4879.06</v>
-      </c>
-      <c r="G273" t="n">
         <v>6072.47</v>
       </c>
     </row>
@@ -7717,18 +6916,15 @@
         <v>4522.73</v>
       </c>
       <c r="C274" t="n">
-        <v>1300.87</v>
+        <v>1573.95</v>
       </c>
       <c r="D274" t="n">
-        <v>5823.59</v>
+        <v>6096.68</v>
       </c>
       <c r="E274" t="n">
-        <v>5084.74</v>
+        <v>5246.06</v>
       </c>
       <c r="F274" t="n">
-        <v>4883.29</v>
-      </c>
-      <c r="G274" t="n">
         <v>6096.68</v>
       </c>
     </row>
@@ -7742,18 +6938,15 @@
         <v>4554.9</v>
       </c>
       <c r="C275" t="n">
-        <v>1291.17</v>
+        <v>1565.98</v>
       </c>
       <c r="D275" t="n">
-        <v>5846.07</v>
+        <v>6120.88</v>
       </c>
       <c r="E275" t="n">
-        <v>5092.86</v>
+        <v>5258.12</v>
       </c>
       <c r="F275" t="n">
-        <v>4870.32</v>
-      </c>
-      <c r="G275" t="n">
         <v>6120.88</v>
       </c>
       <c r="H275" t="inlineStr">
@@ -7772,18 +6965,15 @@
         <v>4587.08</v>
       </c>
       <c r="C276" t="n">
-        <v>1281.47</v>
+        <v>1558.01</v>
       </c>
       <c r="D276" t="n">
-        <v>5868.55</v>
+        <v>6145.09</v>
       </c>
       <c r="E276" t="n">
-        <v>5100.97</v>
+        <v>5270.18</v>
       </c>
       <c r="F276" t="n">
-        <v>4857.34</v>
-      </c>
-      <c r="G276" t="n">
         <v>6145.09</v>
       </c>
     </row>
@@ -7797,18 +6987,15 @@
         <v>4584.29</v>
       </c>
       <c r="C277" t="n">
-        <v>1306.74</v>
+        <v>1585.01</v>
       </c>
       <c r="D277" t="n">
-        <v>5891.03</v>
+        <v>6169.29</v>
       </c>
       <c r="E277" t="n">
-        <v>5102.1</v>
+        <v>5275.25</v>
       </c>
       <c r="F277" t="n">
-        <v>4844.37</v>
-      </c>
-      <c r="G277" t="n">
         <v>6169.29</v>
       </c>
     </row>
@@ -7822,18 +7009,15 @@
         <v>4581.49</v>
       </c>
       <c r="C278" t="n">
-        <v>1323.22</v>
+        <v>1612.01</v>
       </c>
       <c r="D278" t="n">
-        <v>5904.71</v>
+        <v>6193.5</v>
       </c>
       <c r="E278" t="n">
-        <v>5101.46</v>
+        <v>5278.56</v>
       </c>
       <c r="F278" t="n">
-        <v>4831.4</v>
-      </c>
-      <c r="G278" t="n">
         <v>6193.5</v>
       </c>
     </row>
@@ -7847,18 +7031,15 @@
         <v>4578.7</v>
       </c>
       <c r="C279" t="n">
-        <v>1339.69</v>
+        <v>1639.01</v>
       </c>
       <c r="D279" t="n">
-        <v>5918.39</v>
+        <v>6217.7</v>
       </c>
       <c r="E279" t="n">
-        <v>5099.13</v>
+        <v>5280.18</v>
       </c>
       <c r="F279" t="n">
-        <v>4818.43</v>
-      </c>
-      <c r="G279" t="n">
         <v>6217.7</v>
       </c>
     </row>
@@ -7872,18 +7053,15 @@
         <v>4575.9</v>
       </c>
       <c r="C280" t="n">
-        <v>1356.17</v>
+        <v>1666.01</v>
       </c>
       <c r="D280" t="n">
-        <v>5932.07</v>
+        <v>6241.91</v>
       </c>
       <c r="E280" t="n">
-        <v>5092.36</v>
+        <v>5281.8</v>
       </c>
       <c r="F280" t="n">
-        <v>4805.45</v>
-      </c>
-      <c r="G280" t="n">
         <v>6241.91</v>
       </c>
     </row>
@@ -7897,18 +7075,15 @@
         <v>4573.11</v>
       </c>
       <c r="C281" t="n">
-        <v>1372.64</v>
+        <v>1663.37</v>
       </c>
       <c r="D281" t="n">
-        <v>5945.75</v>
+        <v>6236.48</v>
       </c>
       <c r="E281" t="n">
-        <v>5085.58</v>
+        <v>5277.49</v>
       </c>
       <c r="F281" t="n">
-        <v>4792.48</v>
-      </c>
-      <c r="G281" t="n">
         <v>6236.48</v>
       </c>
     </row>
@@ -7922,18 +7097,15 @@
         <v>4570.31</v>
       </c>
       <c r="C282" t="n">
-        <v>1389.12</v>
+        <v>1660.73</v>
       </c>
       <c r="D282" t="n">
-        <v>5959.43</v>
+        <v>6231.04</v>
       </c>
       <c r="E282" t="n">
-        <v>5083.59</v>
+        <v>5277.98</v>
       </c>
       <c r="F282" t="n">
-        <v>4803.46</v>
-      </c>
-      <c r="G282" t="n">
         <v>6231.04</v>
       </c>
     </row>
@@ -7947,18 +7119,15 @@
         <v>4567.52</v>
       </c>
       <c r="C283" t="n">
-        <v>1405.59</v>
+        <v>1658.09</v>
       </c>
       <c r="D283" t="n">
-        <v>5973.11</v>
+        <v>6225.61</v>
       </c>
       <c r="E283" t="n">
-        <v>5081.61</v>
+        <v>5278.46</v>
       </c>
       <c r="F283" t="n">
-        <v>4814.44</v>
-      </c>
-      <c r="G283" t="n">
         <v>6225.61</v>
       </c>
     </row>
@@ -7972,18 +7141,15 @@
         <v>4574.98</v>
       </c>
       <c r="C284" t="n">
-        <v>1411.81</v>
+        <v>1645.2</v>
       </c>
       <c r="D284" t="n">
-        <v>5986.79</v>
+        <v>6220.17</v>
       </c>
       <c r="E284" t="n">
-        <v>5081.67</v>
+        <v>5281</v>
       </c>
       <c r="F284" t="n">
-        <v>4825.42</v>
-      </c>
-      <c r="G284" t="n">
         <v>6220.17</v>
       </c>
     </row>
@@ -7997,18 +7163,15 @@
         <v>4582.43</v>
       </c>
       <c r="C285" t="n">
-        <v>1440.59</v>
+        <v>1632.31</v>
       </c>
       <c r="D285" t="n">
-        <v>6023.02</v>
+        <v>6214.74</v>
       </c>
       <c r="E285" t="n">
-        <v>5086.25</v>
+        <v>5288.04</v>
       </c>
       <c r="F285" t="n">
-        <v>4836.41</v>
-      </c>
-      <c r="G285" t="n">
         <v>6214.74</v>
       </c>
     </row>
@@ -8022,18 +7185,15 @@
         <v>4589.89</v>
       </c>
       <c r="C286" t="n">
-        <v>1469.36</v>
+        <v>1619.42</v>
       </c>
       <c r="D286" t="n">
-        <v>6059.25</v>
+        <v>6209.3</v>
       </c>
       <c r="E286" t="n">
-        <v>5091.64</v>
+        <v>5295.91</v>
       </c>
       <c r="F286" t="n">
-        <v>4847.39</v>
-      </c>
-      <c r="G286" t="n">
         <v>6209.3</v>
       </c>
     </row>
@@ -8047,18 +7207,15 @@
         <v>4597.34</v>
       </c>
       <c r="C287" t="n">
-        <v>1498.14</v>
+        <v>1606.53</v>
       </c>
       <c r="D287" t="n">
-        <v>6095.48</v>
+        <v>6203.87</v>
       </c>
       <c r="E287" t="n">
-        <v>5103.7</v>
+        <v>5303.77</v>
       </c>
       <c r="F287" t="n">
-        <v>4858.37</v>
-      </c>
-      <c r="G287" t="n">
         <v>6203.87</v>
       </c>
     </row>
@@ -8072,18 +7229,15 @@
         <v>4604.8</v>
       </c>
       <c r="C288" t="n">
-        <v>1526.91</v>
+        <v>1629.25</v>
       </c>
       <c r="D288" t="n">
-        <v>6131.71</v>
+        <v>6234.05</v>
       </c>
       <c r="E288" t="n">
-        <v>5115.76</v>
+        <v>5318.76</v>
       </c>
       <c r="F288" t="n">
-        <v>4869.35</v>
-      </c>
-      <c r="G288" t="n">
         <v>6234.05</v>
       </c>
     </row>
@@ -8097,18 +7251,15 @@
         <v>4612.25</v>
       </c>
       <c r="C289" t="n">
-        <v>1555.69</v>
+        <v>1651.98</v>
       </c>
       <c r="D289" t="n">
-        <v>6167.94</v>
+        <v>6264.23</v>
       </c>
       <c r="E289" t="n">
-        <v>5132.19</v>
+        <v>5338.11</v>
       </c>
       <c r="F289" t="n">
-        <v>4902.17</v>
-      </c>
-      <c r="G289" t="n">
         <v>6264.23</v>
       </c>
     </row>
@@ -8122,18 +7273,15 @@
         <v>4619.71</v>
       </c>
       <c r="C290" t="n">
-        <v>1584.46</v>
+        <v>1674.7</v>
       </c>
       <c r="D290" t="n">
-        <v>6204.17</v>
+        <v>6294.41</v>
       </c>
       <c r="E290" t="n">
-        <v>5148.62</v>
+        <v>5357.47</v>
       </c>
       <c r="F290" t="n">
-        <v>4934.99</v>
-      </c>
-      <c r="G290" t="n">
         <v>6294.41</v>
       </c>
     </row>
@@ -8147,18 +7295,15 @@
         <v>4640.96</v>
       </c>
       <c r="C291" t="n">
-        <v>1599.44</v>
+        <v>1683.63</v>
       </c>
       <c r="D291" t="n">
-        <v>6240.4</v>
+        <v>6324.59</v>
       </c>
       <c r="E291" t="n">
-        <v>5167.8</v>
+        <v>5379.58</v>
       </c>
       <c r="F291" t="n">
-        <v>4967.81</v>
-      </c>
-      <c r="G291" t="n">
         <v>6324.59</v>
       </c>
     </row>
@@ -8172,18 +7317,15 @@
         <v>4662.2</v>
       </c>
       <c r="C292" t="n">
-        <v>1591.08</v>
+        <v>1692.57</v>
       </c>
       <c r="D292" t="n">
-        <v>6253.28</v>
+        <v>6354.77</v>
       </c>
       <c r="E292" t="n">
-        <v>5182.32</v>
+        <v>5397.02</v>
       </c>
       <c r="F292" t="n">
-        <v>5000.63</v>
-      </c>
-      <c r="G292" t="n">
         <v>6354.77</v>
       </c>
     </row>
@@ -8197,18 +7339,15 @@
         <v>4683.45</v>
       </c>
       <c r="C293" t="n">
-        <v>1582.71</v>
+        <v>1701.5</v>
       </c>
       <c r="D293" t="n">
-        <v>6266.16</v>
+        <v>6384.95</v>
       </c>
       <c r="E293" t="n">
-        <v>5198.62</v>
+        <v>5416.25</v>
       </c>
       <c r="F293" t="n">
-        <v>5033.45</v>
-      </c>
-      <c r="G293" t="n">
         <v>6384.95</v>
       </c>
     </row>
@@ -8222,18 +7361,15 @@
         <v>4704.7</v>
       </c>
       <c r="C294" t="n">
-        <v>1574.35</v>
+        <v>1710.43</v>
       </c>
       <c r="D294" t="n">
-        <v>6279.04</v>
+        <v>6415.13</v>
       </c>
       <c r="E294" t="n">
-        <v>5215.16</v>
+        <v>5435.47</v>
       </c>
       <c r="F294" t="n">
-        <v>5066.27</v>
-      </c>
-      <c r="G294" t="n">
         <v>6415.13</v>
       </c>
     </row>
@@ -8247,18 +7383,15 @@
         <v>4711.21</v>
       </c>
       <c r="C295" t="n">
-        <v>1580.72</v>
+        <v>1742.87</v>
       </c>
       <c r="D295" t="n">
-        <v>6291.93</v>
+        <v>6454.08</v>
       </c>
       <c r="E295" t="n">
-        <v>5231.71</v>
+        <v>5456.45</v>
       </c>
       <c r="F295" t="n">
-        <v>5099.09</v>
-      </c>
-      <c r="G295" t="n">
         <v>6454.08</v>
       </c>
     </row>
@@ -8272,18 +7405,15 @@
         <v>4710.2</v>
       </c>
       <c r="C296" t="n">
-        <v>1594.61</v>
+        <v>1782.83</v>
       </c>
       <c r="D296" t="n">
-        <v>6304.81</v>
+        <v>6493.03</v>
       </c>
       <c r="E296" t="n">
-        <v>5250.11</v>
+        <v>5479.28</v>
       </c>
       <c r="F296" t="n">
-        <v>5141.18</v>
-      </c>
-      <c r="G296" t="n">
         <v>6493.03</v>
       </c>
     </row>
@@ -8297,18 +7427,15 @@
         <v>4709.19</v>
       </c>
       <c r="C297" t="n">
-        <v>1608.49</v>
+        <v>1822.79</v>
       </c>
       <c r="D297" t="n">
-        <v>6317.69</v>
+        <v>6531.98</v>
       </c>
       <c r="E297" t="n">
-        <v>5268.51</v>
+        <v>5502.11</v>
       </c>
       <c r="F297" t="n">
-        <v>5183.27</v>
-      </c>
-      <c r="G297" t="n">
         <v>6531.98</v>
       </c>
     </row>
@@ -8322,18 +7449,15 @@
         <v>4708.19</v>
       </c>
       <c r="C298" t="n">
-        <v>1622.38</v>
+        <v>1862.75</v>
       </c>
       <c r="D298" t="n">
-        <v>6330.57</v>
+        <v>6570.94</v>
       </c>
       <c r="E298" t="n">
-        <v>5288.91</v>
+        <v>5526.94</v>
       </c>
       <c r="F298" t="n">
-        <v>5225.36</v>
-      </c>
-      <c r="G298" t="n">
         <v>6570.94</v>
       </c>
     </row>
@@ -8347,18 +7471,15 @@
         <v>4707.18</v>
       </c>
       <c r="C299" t="n">
-        <v>1631.74</v>
+        <v>1902.71</v>
       </c>
       <c r="D299" t="n">
-        <v>6338.92</v>
+        <v>6609.89</v>
       </c>
       <c r="E299" t="n">
-        <v>5308.39</v>
+        <v>5550.86</v>
       </c>
       <c r="F299" t="n">
-        <v>5267.44</v>
-      </c>
-      <c r="G299" t="n">
         <v>6609.89</v>
       </c>
     </row>
@@ -8372,18 +7493,15 @@
         <v>4713.64</v>
       </c>
       <c r="C300" t="n">
-        <v>1633.63</v>
+        <v>1935.2</v>
       </c>
       <c r="D300" t="n">
-        <v>6347.28</v>
+        <v>6648.84</v>
       </c>
       <c r="E300" t="n">
-        <v>5329.38</v>
+        <v>5576.27</v>
       </c>
       <c r="F300" t="n">
-        <v>5309.53</v>
-      </c>
-      <c r="G300" t="n">
         <v>6648.84</v>
       </c>
     </row>
@@ -8397,18 +7515,15 @@
         <v>4720.11</v>
       </c>
       <c r="C301" t="n">
-        <v>1635.52</v>
+        <v>1967.68</v>
       </c>
       <c r="D301" t="n">
-        <v>6355.63</v>
+        <v>6687.79</v>
       </c>
       <c r="E301" t="n">
-        <v>5363.71</v>
+        <v>5601.68</v>
       </c>
       <c r="F301" t="n">
-        <v>5351.62</v>
-      </c>
-      <c r="G301" t="n">
         <v>6687.79</v>
       </c>
     </row>
@@ -8422,18 +7537,15 @@
         <v>4726.57</v>
       </c>
       <c r="C302" t="n">
-        <v>1637.41</v>
+        <v>1991.27</v>
       </c>
       <c r="D302" t="n">
-        <v>6363.98</v>
+        <v>6717.84</v>
       </c>
       <c r="E302" t="n">
-        <v>5398.04</v>
+        <v>5625.32</v>
       </c>
       <c r="F302" t="n">
-        <v>5393.71</v>
-      </c>
-      <c r="G302" t="n">
         <v>6717.84</v>
       </c>
     </row>
@@ -8447,18 +7559,15 @@
         <v>4733.03</v>
       </c>
       <c r="C303" t="n">
-        <v>1639.3</v>
+        <v>2014.86</v>
       </c>
       <c r="D303" t="n">
-        <v>6372.33</v>
+        <v>6747.89</v>
       </c>
       <c r="E303" t="n">
-        <v>5424.19</v>
+        <v>5640.76</v>
       </c>
       <c r="F303" t="n">
-        <v>5394.86</v>
-      </c>
-      <c r="G303" t="n">
         <v>6747.89</v>
       </c>
     </row>
@@ -8472,18 +7581,15 @@
         <v>4739.49</v>
       </c>
       <c r="C304" t="n">
-        <v>1641.19</v>
+        <v>2038.44</v>
       </c>
       <c r="D304" t="n">
-        <v>6380.69</v>
+        <v>6777.94</v>
       </c>
       <c r="E304" t="n">
-        <v>5450.34</v>
+        <v>5656.21</v>
       </c>
       <c r="F304" t="n">
-        <v>5396.01</v>
-      </c>
-      <c r="G304" t="n">
         <v>6777.94</v>
       </c>
     </row>
@@ -8497,18 +7603,15 @@
         <v>4745.96</v>
       </c>
       <c r="C305" t="n">
-        <v>1643.08</v>
+        <v>2062.03</v>
       </c>
       <c r="D305" t="n">
-        <v>6389.04</v>
+        <v>6807.98</v>
       </c>
       <c r="E305" t="n">
-        <v>5470.26</v>
+        <v>5665.43</v>
       </c>
       <c r="F305" t="n">
-        <v>5397.16</v>
-      </c>
-      <c r="G305" t="n">
         <v>6807.98</v>
       </c>
     </row>
@@ -8522,18 +7625,15 @@
         <v>4752.42</v>
       </c>
       <c r="C306" t="n">
-        <v>1667.04</v>
+        <v>2085.61</v>
       </c>
       <c r="D306" t="n">
-        <v>6419.46</v>
+        <v>6838.03</v>
       </c>
       <c r="E306" t="n">
-        <v>5494.61</v>
+        <v>5679.07</v>
       </c>
       <c r="F306" t="n">
-        <v>5398.32</v>
-      </c>
-      <c r="G306" t="n">
         <v>6838.03</v>
       </c>
       <c r="H306" t="inlineStr">
@@ -8552,18 +7652,15 @@
         <v>4812.58</v>
       </c>
       <c r="C307" t="n">
-        <v>1637.3</v>
+        <v>2055.5</v>
       </c>
       <c r="D307" t="n">
-        <v>6449.88</v>
+        <v>6868.08</v>
       </c>
       <c r="E307" t="n">
-        <v>5529.69</v>
+        <v>5703.46</v>
       </c>
       <c r="F307" t="n">
-        <v>5399.47</v>
-      </c>
-      <c r="G307" t="n">
         <v>6868.08</v>
       </c>
     </row>
@@ -8577,18 +7674,15 @@
         <v>4872.74</v>
       </c>
       <c r="C308" t="n">
-        <v>1607.56</v>
+        <v>2025.39</v>
       </c>
       <c r="D308" t="n">
-        <v>6480.3</v>
+        <v>6898.13</v>
       </c>
       <c r="E308" t="n">
-        <v>5551.31</v>
+        <v>5727.84</v>
       </c>
       <c r="F308" t="n">
-        <v>5400.62</v>
-      </c>
-      <c r="G308" t="n">
         <v>6898.13</v>
       </c>
     </row>
@@ -8602,18 +7696,15 @@
         <v>4932.9</v>
       </c>
       <c r="C309" t="n">
-        <v>1577.83</v>
+        <v>1961.2</v>
       </c>
       <c r="D309" t="n">
-        <v>6510.73</v>
+        <v>6894.1</v>
       </c>
       <c r="E309" t="n">
-        <v>5572.93</v>
+        <v>5745.4</v>
       </c>
       <c r="F309" t="n">
-        <v>5401.77</v>
-      </c>
-      <c r="G309" t="n">
         <v>6894.1</v>
       </c>
     </row>
@@ -8627,18 +7718,15 @@
         <v>4987.63</v>
       </c>
       <c r="C310" t="n">
-        <v>1553.52</v>
+        <v>1902.44</v>
       </c>
       <c r="D310" t="n">
-        <v>6541.15</v>
+        <v>6890.06</v>
       </c>
       <c r="E310" t="n">
-        <v>5595.49</v>
+        <v>5763.91</v>
       </c>
       <c r="F310" t="n">
-        <v>5407.63</v>
-      </c>
-      <c r="G310" t="n">
         <v>6890.06</v>
       </c>
     </row>
@@ -8652,18 +7740,15 @@
         <v>4987.75</v>
       </c>
       <c r="C311" t="n">
-        <v>1583.82</v>
+        <v>1898.28</v>
       </c>
       <c r="D311" t="n">
-        <v>6571.57</v>
+        <v>6886.03</v>
       </c>
       <c r="E311" t="n">
-        <v>5618.05</v>
+        <v>5782.41</v>
       </c>
       <c r="F311" t="n">
-        <v>5413.48</v>
-      </c>
-      <c r="G311" t="n">
         <v>6886.03</v>
       </c>
     </row>
@@ -8677,18 +7762,15 @@
         <v>5002.03</v>
       </c>
       <c r="C312" t="n">
-        <v>1599.96</v>
+        <v>1879.97</v>
       </c>
       <c r="D312" t="n">
-        <v>6601.99</v>
+        <v>6882</v>
       </c>
       <c r="E312" t="n">
-        <v>5643.45</v>
+        <v>5803.75</v>
       </c>
       <c r="F312" t="n">
-        <v>5419.34</v>
-      </c>
-      <c r="G312" t="n">
         <v>6882</v>
       </c>
     </row>
@@ -8702,18 +7784,15 @@
         <v>5016.3</v>
       </c>
       <c r="C313" t="n">
-        <v>1590.25</v>
+        <v>1861.66</v>
       </c>
       <c r="D313" t="n">
-        <v>6606.55</v>
+        <v>6877.97</v>
       </c>
       <c r="E313" t="n">
-        <v>5663.67</v>
+        <v>5819.91</v>
       </c>
       <c r="F313" t="n">
-        <v>5425.19</v>
-      </c>
-      <c r="G313" t="n">
         <v>6877.97</v>
       </c>
     </row>
@@ -8727,18 +7806,15 @@
         <v>5030.58</v>
       </c>
       <c r="C314" t="n">
-        <v>1580.53</v>
+        <v>1843.35</v>
       </c>
       <c r="D314" t="n">
-        <v>6611.11</v>
+        <v>6873.93</v>
       </c>
       <c r="E314" t="n">
-        <v>5673.58</v>
+        <v>5825.77</v>
       </c>
       <c r="F314" t="n">
-        <v>5431.05</v>
-      </c>
-      <c r="G314" t="n">
         <v>6873.93</v>
       </c>
     </row>
@@ -8752,18 +7828,15 @@
         <v>5044.86</v>
       </c>
       <c r="C315" t="n">
-        <v>1570.82</v>
+        <v>1825.04</v>
       </c>
       <c r="D315" t="n">
-        <v>6615.67</v>
+        <v>6869.9</v>
       </c>
       <c r="E315" t="n">
-        <v>5687.45</v>
+        <v>5831.63</v>
       </c>
       <c r="F315" t="n">
-        <v>5436.9</v>
-      </c>
-      <c r="G315" t="n">
         <v>6869.9</v>
       </c>
     </row>
@@ -8777,18 +7850,15 @@
         <v>5059.14</v>
       </c>
       <c r="C316" t="n">
-        <v>1561.1</v>
+        <v>1818.87</v>
       </c>
       <c r="D316" t="n">
-        <v>6620.24</v>
+        <v>6878.01</v>
       </c>
       <c r="E316" t="n">
-        <v>5701.31</v>
+        <v>5839.91</v>
       </c>
       <c r="F316" t="n">
-        <v>5442.76</v>
-      </c>
-      <c r="G316" t="n">
         <v>6878.01</v>
       </c>
     </row>
@@ -8802,18 +7872,15 @@
         <v>5073.41</v>
       </c>
       <c r="C317" t="n">
-        <v>1551.38</v>
+        <v>1812.7</v>
       </c>
       <c r="D317" t="n">
-        <v>6624.8</v>
+        <v>6886.11</v>
       </c>
       <c r="E317" t="n">
-        <v>5713.61</v>
+        <v>5846.63</v>
       </c>
       <c r="F317" t="n">
-        <v>5440.76</v>
-      </c>
-      <c r="G317" t="n">
         <v>6886.11</v>
       </c>
     </row>
@@ -8827,18 +7894,15 @@
         <v>5087.69</v>
       </c>
       <c r="C318" t="n">
-        <v>1541.67</v>
+        <v>1806.53</v>
       </c>
       <c r="D318" t="n">
-        <v>6629.36</v>
+        <v>6894.22</v>
       </c>
       <c r="E318" t="n">
-        <v>5725.9</v>
+        <v>5853.34</v>
       </c>
       <c r="F318" t="n">
-        <v>5438.75</v>
-      </c>
-      <c r="G318" t="n">
         <v>6894.22</v>
       </c>
     </row>
@@ -8852,18 +7916,15 @@
         <v>5101.58</v>
       </c>
       <c r="C319" t="n">
-        <v>1532.34</v>
+        <v>1800.74</v>
       </c>
       <c r="D319" t="n">
-        <v>6633.92</v>
+        <v>6902.32</v>
       </c>
       <c r="E319" t="n">
-        <v>5738.12</v>
+        <v>5859.98</v>
       </c>
       <c r="F319" t="n">
-        <v>5436.75</v>
-      </c>
-      <c r="G319" t="n">
         <v>6902.32</v>
       </c>
     </row>
@@ -8877,18 +7938,15 @@
         <v>5115.48</v>
       </c>
       <c r="C320" t="n">
-        <v>1518.8</v>
+        <v>1794.95</v>
       </c>
       <c r="D320" t="n">
-        <v>6634.27</v>
+        <v>6910.43</v>
       </c>
       <c r="E320" t="n">
-        <v>5749.5</v>
+        <v>5865.78</v>
       </c>
       <c r="F320" t="n">
-        <v>5434.75</v>
-      </c>
-      <c r="G320" t="n">
         <v>6910.43</v>
       </c>
     </row>
@@ -8902,18 +7960,15 @@
         <v>5129.37</v>
       </c>
       <c r="C321" t="n">
-        <v>1505.26</v>
+        <v>1789.17</v>
       </c>
       <c r="D321" t="n">
-        <v>6634.63</v>
+        <v>6918.53</v>
       </c>
       <c r="E321" t="n">
-        <v>5766.39</v>
+        <v>5877.08</v>
       </c>
       <c r="F321" t="n">
-        <v>5432.75</v>
-      </c>
-      <c r="G321" t="n">
         <v>6918.53</v>
       </c>
     </row>
@@ -8927,18 +7982,15 @@
         <v>5143.26</v>
       </c>
       <c r="C322" t="n">
-        <v>1491.72</v>
+        <v>1783.38</v>
       </c>
       <c r="D322" t="n">
-        <v>6634.98</v>
+        <v>6926.64</v>
       </c>
       <c r="E322" t="n">
-        <v>5782.26</v>
+        <v>5888.39</v>
       </c>
       <c r="F322" t="n">
-        <v>5430.74</v>
-      </c>
-      <c r="G322" t="n">
         <v>6926.64</v>
       </c>
     </row>
@@ -8952,18 +8004,15 @@
         <v>5157.15</v>
       </c>
       <c r="C323" t="n">
-        <v>1478.18</v>
+        <v>1790.28</v>
       </c>
       <c r="D323" t="n">
-        <v>6635.33</v>
+        <v>6947.44</v>
       </c>
       <c r="E323" t="n">
-        <v>5798.14</v>
+        <v>5902.23</v>
       </c>
       <c r="F323" t="n">
-        <v>5428.74</v>
-      </c>
-      <c r="G323" t="n">
         <v>6947.44</v>
       </c>
     </row>
@@ -8977,18 +8026,15 @@
         <v>5171.05</v>
       </c>
       <c r="C324" t="n">
-        <v>1464.64</v>
+        <v>1797.18</v>
       </c>
       <c r="D324" t="n">
-        <v>6635.68</v>
+        <v>6968.23</v>
       </c>
       <c r="E324" t="n">
-        <v>5813.85</v>
+        <v>5915.91</v>
       </c>
       <c r="F324" t="n">
-        <v>5425.92</v>
-      </c>
-      <c r="G324" t="n">
         <v>6968.23</v>
       </c>
     </row>
@@ -9002,18 +8048,15 @@
         <v>5184.94</v>
       </c>
       <c r="C325" t="n">
-        <v>1451.1</v>
+        <v>1804.09</v>
       </c>
       <c r="D325" t="n">
-        <v>6636.04</v>
+        <v>6989.03</v>
       </c>
       <c r="E325" t="n">
-        <v>5829.57</v>
+        <v>5929.59</v>
       </c>
       <c r="F325" t="n">
-        <v>5423.09</v>
-      </c>
-      <c r="G325" t="n">
         <v>6989.03</v>
       </c>
     </row>
@@ -9027,18 +8070,15 @@
         <v>5220.51</v>
       </c>
       <c r="C326" t="n">
-        <v>1415.88</v>
+        <v>1789.32</v>
       </c>
       <c r="D326" t="n">
-        <v>6636.39</v>
+        <v>7009.82</v>
       </c>
       <c r="E326" t="n">
-        <v>5849.62</v>
+        <v>5947.61</v>
       </c>
       <c r="F326" t="n">
-        <v>5420.27</v>
-      </c>
-      <c r="G326" t="n">
         <v>7009.82</v>
       </c>
     </row>
@@ -9052,18 +8092,15 @@
         <v>5256.07</v>
       </c>
       <c r="C327" t="n">
-        <v>1384.88</v>
+        <v>1774.54</v>
       </c>
       <c r="D327" t="n">
-        <v>6640.95</v>
+        <v>7030.62</v>
       </c>
       <c r="E327" t="n">
-        <v>5870.51</v>
+        <v>5966.47</v>
       </c>
       <c r="F327" t="n">
-        <v>5417.45</v>
-      </c>
-      <c r="G327" t="n">
         <v>7030.62</v>
       </c>
     </row>
@@ -9077,18 +8114,15 @@
         <v>5291.64</v>
       </c>
       <c r="C328" t="n">
-        <v>1353.87</v>
+        <v>1759.77</v>
       </c>
       <c r="D328" t="n">
-        <v>6645.52</v>
+        <v>7051.41</v>
       </c>
       <c r="E328" t="n">
-        <v>5891.23</v>
+        <v>5985.16</v>
       </c>
       <c r="F328" t="n">
-        <v>5414.63</v>
-      </c>
-      <c r="G328" t="n">
         <v>7051.41</v>
       </c>
     </row>
@@ -9102,18 +8136,15 @@
         <v>5327.21</v>
       </c>
       <c r="C329" t="n">
-        <v>1322.87</v>
+        <v>1745</v>
       </c>
       <c r="D329" t="n">
-        <v>6650.08</v>
+        <v>7072.21</v>
       </c>
       <c r="E329" t="n">
-        <v>5907.62</v>
+        <v>6003.85</v>
       </c>
       <c r="F329" t="n">
-        <v>5411.8</v>
-      </c>
-      <c r="G329" t="n">
         <v>7072.21</v>
       </c>
     </row>
@@ -9127,18 +8158,15 @@
         <v>5362.78</v>
       </c>
       <c r="C330" t="n">
-        <v>1291.87</v>
+        <v>1710.21</v>
       </c>
       <c r="D330" t="n">
-        <v>6654.64</v>
+        <v>7072.98</v>
       </c>
       <c r="E330" t="n">
-        <v>5924.02</v>
+        <v>6018.53</v>
       </c>
       <c r="F330" t="n">
-        <v>5408.98</v>
-      </c>
-      <c r="G330" t="n">
         <v>7072.98</v>
       </c>
     </row>
@@ -9152,18 +8180,15 @@
         <v>5398.34</v>
       </c>
       <c r="C331" t="n">
-        <v>1260.86</v>
+        <v>1675.41</v>
       </c>
       <c r="D331" t="n">
-        <v>6659.2</v>
+        <v>7073.75</v>
       </c>
       <c r="E331" t="n">
-        <v>5948.81</v>
+        <v>6041.6</v>
       </c>
       <c r="F331" t="n">
-        <v>5448.1</v>
-      </c>
-      <c r="G331" t="n">
         <v>7073.75</v>
       </c>
     </row>
@@ -9177,18 +8202,15 @@
         <v>5433.91</v>
       </c>
       <c r="C332" t="n">
-        <v>1229.86</v>
+        <v>1640.61</v>
       </c>
       <c r="D332" t="n">
-        <v>6663.77</v>
+        <v>7074.52</v>
       </c>
       <c r="E332" t="n">
-        <v>5973.59</v>
+        <v>6064.68</v>
       </c>
       <c r="F332" t="n">
-        <v>5487.22</v>
-      </c>
-      <c r="G332" t="n">
         <v>7074.52</v>
       </c>
     </row>
@@ -9202,18 +8224,15 @@
         <v>5525.58</v>
       </c>
       <c r="C333" t="n">
-        <v>1142.75</v>
+        <v>1549.72</v>
       </c>
       <c r="D333" t="n">
-        <v>6668.33</v>
+        <v>7075.3</v>
       </c>
       <c r="E333" t="n">
-        <v>6009.6</v>
+        <v>6098.97</v>
       </c>
       <c r="F333" t="n">
-        <v>5526.34</v>
-      </c>
-      <c r="G333" t="n">
         <v>7075.3</v>
       </c>
     </row>
@@ -9227,18 +8246,15 @@
         <v>5565.46</v>
       </c>
       <c r="C334" t="n">
-        <v>1105.22</v>
+        <v>1510.61</v>
       </c>
       <c r="D334" t="n">
-        <v>6670.68</v>
+        <v>7076.07</v>
       </c>
       <c r="E334" t="n">
-        <v>6045.16</v>
+        <v>6132.82</v>
       </c>
       <c r="F334" t="n">
-        <v>5565.46</v>
-      </c>
-      <c r="G334" t="n">
         <v>7076.07</v>
       </c>
     </row>
@@ -9252,18 +8268,15 @@
         <v>5604.58</v>
       </c>
       <c r="C335" t="n">
-        <v>1068.44</v>
+        <v>1472.26</v>
       </c>
       <c r="D335" t="n">
-        <v>6673.02</v>
+        <v>7076.84</v>
       </c>
       <c r="E335" t="n">
-        <v>6073.7</v>
+        <v>6159.65</v>
       </c>
       <c r="F335" t="n">
-        <v>5604.58</v>
-      </c>
-      <c r="G335" t="n">
         <v>7076.84</v>
       </c>
     </row>
@@ -9277,18 +8290,15 @@
         <v>5643.7</v>
       </c>
       <c r="C336" t="n">
-        <v>1031.67</v>
+        <v>1433.91</v>
       </c>
       <c r="D336" t="n">
-        <v>6675.37</v>
+        <v>7077.61</v>
       </c>
       <c r="E336" t="n">
-        <v>6102.73</v>
+        <v>6186.47</v>
       </c>
       <c r="F336" t="n">
-        <v>5643.7</v>
-      </c>
-      <c r="G336" t="n">
         <v>7077.61</v>
       </c>
     </row>
@@ -9302,18 +8312,15 @@
         <v>5682.82</v>
       </c>
       <c r="C337" t="n">
-        <v>994.9</v>
+        <v>1419.65</v>
       </c>
       <c r="D337" t="n">
-        <v>6677.72</v>
+        <v>7102.47</v>
       </c>
       <c r="E337" t="n">
-        <v>6131.76</v>
+        <v>6218.11</v>
       </c>
       <c r="F337" t="n">
-        <v>5682.82</v>
-      </c>
-      <c r="G337" t="n">
         <v>7102.47</v>
       </c>
       <c r="H337" t="inlineStr">
@@ -9332,18 +8339,15 @@
         <v>5718.84</v>
       </c>
       <c r="C338" t="n">
-        <v>963.66</v>
+        <v>1408.48</v>
       </c>
       <c r="D338" t="n">
-        <v>6682.51</v>
+        <v>7127.32</v>
       </c>
       <c r="E338" t="n">
-        <v>6160.17</v>
+        <v>6249.14</v>
       </c>
       <c r="F338" t="n">
-        <v>5718.84</v>
-      </c>
-      <c r="G338" t="n">
         <v>7127.32</v>
       </c>
     </row>
@@ -9357,18 +8361,15 @@
         <v>5735.75</v>
       </c>
       <c r="C339" t="n">
-        <v>958.5700000000001</v>
+        <v>1416.44</v>
       </c>
       <c r="D339" t="n">
-        <v>6694.31</v>
+        <v>7152.18</v>
       </c>
       <c r="E339" t="n">
-        <v>6188.58</v>
+        <v>6280.16</v>
       </c>
       <c r="F339" t="n">
-        <v>5754.87</v>
-      </c>
-      <c r="G339" t="n">
         <v>7152.18</v>
       </c>
     </row>
@@ -9382,18 +8383,15 @@
         <v>5735.96</v>
       </c>
       <c r="C340" t="n">
-        <v>970.16</v>
+        <v>1441.08</v>
       </c>
       <c r="D340" t="n">
-        <v>6706.12</v>
+        <v>7177.04</v>
       </c>
       <c r="E340" t="n">
-        <v>6210.5</v>
+        <v>6304.68</v>
       </c>
       <c r="F340" t="n">
-        <v>5790.89</v>
-      </c>
-      <c r="G340" t="n">
         <v>7177.04</v>
       </c>
     </row>
@@ -9407,18 +8405,15 @@
         <v>5736.18</v>
       </c>
       <c r="C341" t="n">
-        <v>981.74</v>
+        <v>1465.72</v>
       </c>
       <c r="D341" t="n">
-        <v>6717.92</v>
+        <v>7201.9</v>
       </c>
       <c r="E341" t="n">
-        <v>6233.53</v>
+        <v>6330.32</v>
       </c>
       <c r="F341" t="n">
-        <v>5826.92</v>
-      </c>
-      <c r="G341" t="n">
         <v>7201.9</v>
       </c>
     </row>
@@ -9432,18 +8427,15 @@
         <v>5737.75</v>
       </c>
       <c r="C342" t="n">
-        <v>991.98</v>
+        <v>1489</v>
       </c>
       <c r="D342" t="n">
-        <v>6729.73</v>
+        <v>7226.75</v>
       </c>
       <c r="E342" t="n">
-        <v>6256.83</v>
+        <v>6356.24</v>
       </c>
       <c r="F342" t="n">
-        <v>5862.94</v>
-      </c>
-      <c r="G342" t="n">
         <v>7226.75</v>
       </c>
     </row>
@@ -9457,18 +8449,15 @@
         <v>5739.32</v>
       </c>
       <c r="C343" t="n">
-        <v>1017.52</v>
+        <v>1512.29</v>
       </c>
       <c r="D343" t="n">
-        <v>6756.84</v>
+        <v>7251.61</v>
       </c>
       <c r="E343" t="n">
-        <v>6283.2</v>
+        <v>6382.15</v>
       </c>
       <c r="F343" t="n">
-        <v>5898.97</v>
-      </c>
-      <c r="G343" t="n">
         <v>7251.61</v>
       </c>
     </row>
@@ -9482,18 +8471,15 @@
         <v>5740.89</v>
       </c>
       <c r="C344" t="n">
-        <v>1043.06</v>
+        <v>1515.06</v>
       </c>
       <c r="D344" t="n">
-        <v>6783.95</v>
+        <v>7255.95</v>
       </c>
       <c r="E344" t="n">
-        <v>6309.56</v>
+        <v>6403.96</v>
       </c>
       <c r="F344" t="n">
-        <v>5934.99</v>
-      </c>
-      <c r="G344" t="n">
         <v>7255.95</v>
       </c>
     </row>
@@ -9507,18 +8493,15 @@
         <v>5742.46</v>
       </c>
       <c r="C345" t="n">
-        <v>1068.6</v>
+        <v>1517.82</v>
       </c>
       <c r="D345" t="n">
-        <v>6811.06</v>
+        <v>7260.28</v>
       </c>
       <c r="E345" t="n">
-        <v>6338.77</v>
+        <v>6428.61</v>
       </c>
       <c r="F345" t="n">
-        <v>5985.23</v>
-      </c>
-      <c r="G345" t="n">
         <v>7260.28</v>
       </c>
     </row>
@@ -9532,18 +8515,15 @@
         <v>5744.03</v>
       </c>
       <c r="C346" t="n">
-        <v>1094.15</v>
+        <v>1520.59</v>
       </c>
       <c r="D346" t="n">
-        <v>6838.18</v>
+        <v>7264.62</v>
       </c>
       <c r="E346" t="n">
-        <v>6367.97</v>
+        <v>6453.26</v>
       </c>
       <c r="F346" t="n">
-        <v>6035.48</v>
-      </c>
-      <c r="G346" t="n">
         <v>7264.62</v>
       </c>
     </row>
@@ -9557,18 +8537,15 @@
         <v>5745.6</v>
       </c>
       <c r="C347" t="n">
-        <v>1119.69</v>
+        <v>1523.35</v>
       </c>
       <c r="D347" t="n">
-        <v>6865.29</v>
+        <v>7268.95</v>
       </c>
       <c r="E347" t="n">
-        <v>6390.12</v>
+        <v>6470.85</v>
       </c>
       <c r="F347" t="n">
-        <v>6085.72</v>
-      </c>
-      <c r="G347" t="n">
         <v>7268.95</v>
       </c>
     </row>
@@ -9582,18 +8559,15 @@
         <v>5747.17</v>
       </c>
       <c r="C348" t="n">
-        <v>1145.23</v>
+        <v>1526.12</v>
       </c>
       <c r="D348" t="n">
-        <v>6892.4</v>
+        <v>7273.29</v>
       </c>
       <c r="E348" t="n">
-        <v>6412.68</v>
+        <v>6488.85</v>
       </c>
       <c r="F348" t="n">
-        <v>6135.96</v>
-      </c>
-      <c r="G348" t="n">
         <v>7273.29</v>
       </c>
     </row>
@@ -9607,18 +8581,15 @@
         <v>5754.11</v>
       </c>
       <c r="C349" t="n">
-        <v>1165.4</v>
+        <v>1523.51</v>
       </c>
       <c r="D349" t="n">
-        <v>6919.51</v>
+        <v>7277.62</v>
       </c>
       <c r="E349" t="n">
-        <v>6436.31</v>
+        <v>6507.93</v>
       </c>
       <c r="F349" t="n">
-        <v>6186.2</v>
-      </c>
-      <c r="G349" t="n">
         <v>7277.62</v>
       </c>
     </row>
@@ -9632,18 +8603,15 @@
         <v>5761.06</v>
       </c>
       <c r="C350" t="n">
-        <v>1167.57</v>
+        <v>1520.9</v>
       </c>
       <c r="D350" t="n">
-        <v>6928.62</v>
+        <v>7281.96</v>
       </c>
       <c r="E350" t="n">
-        <v>6456.34</v>
+        <v>6527</v>
       </c>
       <c r="F350" t="n">
-        <v>6236.45</v>
-      </c>
-      <c r="G350" t="n">
         <v>7281.96</v>
       </c>
     </row>
@@ -9657,18 +8625,15 @@
         <v>5768</v>
       </c>
       <c r="C351" t="n">
-        <v>1169.73</v>
+        <v>1520.01</v>
       </c>
       <c r="D351" t="n">
-        <v>6937.73</v>
+        <v>7288.01</v>
       </c>
       <c r="E351" t="n">
-        <v>6476.37</v>
+        <v>6546.42</v>
       </c>
       <c r="F351" t="n">
-        <v>6286.69</v>
-      </c>
-      <c r="G351" t="n">
         <v>7288.01</v>
       </c>
     </row>
@@ -9682,18 +8647,15 @@
         <v>5774.94</v>
       </c>
       <c r="C352" t="n">
-        <v>1171.9</v>
+        <v>1519.12</v>
       </c>
       <c r="D352" t="n">
-        <v>6946.84</v>
+        <v>7294.06</v>
       </c>
       <c r="E352" t="n">
-        <v>6495.71</v>
+        <v>6565.15</v>
       </c>
       <c r="F352" t="n">
-        <v>6333.48</v>
-      </c>
-      <c r="G352" t="n">
         <v>7294.06</v>
       </c>
     </row>
@@ -9707,18 +8669,15 @@
         <v>5781.88</v>
       </c>
       <c r="C353" t="n">
-        <v>1174.07</v>
+        <v>1518.23</v>
       </c>
       <c r="D353" t="n">
-        <v>6955.96</v>
+        <v>7300.11</v>
       </c>
       <c r="E353" t="n">
-        <v>6515.05</v>
+        <v>6583.88</v>
       </c>
       <c r="F353" t="n">
-        <v>6380.27</v>
-      </c>
-      <c r="G353" t="n">
         <v>7300.11</v>
       </c>
     </row>
@@ -9732,18 +8691,15 @@
         <v>5788.83</v>
       </c>
       <c r="C354" t="n">
-        <v>1176.24</v>
+        <v>1517.33</v>
       </c>
       <c r="D354" t="n">
-        <v>6965.07</v>
+        <v>7306.16</v>
       </c>
       <c r="E354" t="n">
-        <v>6536.48</v>
+        <v>6604.7</v>
       </c>
       <c r="F354" t="n">
-        <v>6427.06</v>
-      </c>
-      <c r="G354" t="n">
         <v>7306.16</v>
       </c>
     </row>
@@ -9757,18 +8713,15 @@
         <v>5795.77</v>
       </c>
       <c r="C355" t="n">
-        <v>1178.41</v>
+        <v>1516.44</v>
       </c>
       <c r="D355" t="n">
-        <v>6974.18</v>
+        <v>7312.21</v>
       </c>
       <c r="E355" t="n">
-        <v>6560.89</v>
+        <v>6628.5</v>
       </c>
       <c r="F355" t="n">
-        <v>6473.86</v>
-      </c>
-      <c r="G355" t="n">
         <v>7312.21</v>
       </c>
     </row>
@@ -9782,18 +8735,15 @@
         <v>5800.15</v>
       </c>
       <c r="C356" t="n">
-        <v>1183.14</v>
+        <v>1518.11</v>
       </c>
       <c r="D356" t="n">
-        <v>6983.29</v>
+        <v>7318.26</v>
       </c>
       <c r="E356" t="n">
-        <v>6584.79</v>
+        <v>6651.79</v>
       </c>
       <c r="F356" t="n">
-        <v>6520.65</v>
-      </c>
-      <c r="G356" t="n">
         <v>7318.26</v>
       </c>
     </row>
@@ -9807,18 +8757,15 @@
         <v>5804.53</v>
       </c>
       <c r="C357" t="n">
-        <v>1206.83</v>
+        <v>1519.78</v>
       </c>
       <c r="D357" t="n">
-        <v>7011.36</v>
+        <v>7324.31</v>
       </c>
       <c r="E357" t="n">
-        <v>6612.48</v>
+        <v>6675.07</v>
       </c>
       <c r="F357" t="n">
-        <v>6567.44</v>
-      </c>
-      <c r="G357" t="n">
         <v>7324.31</v>
       </c>
     </row>
@@ -9832,18 +8779,15 @@
         <v>5808.91</v>
       </c>
       <c r="C358" t="n">
-        <v>1230.52</v>
+        <v>1514.29</v>
       </c>
       <c r="D358" t="n">
-        <v>7039.44</v>
+        <v>7323.2</v>
       </c>
       <c r="E358" t="n">
-        <v>6640.18</v>
+        <v>6696.93</v>
       </c>
       <c r="F358" t="n">
-        <v>6614.23</v>
-      </c>
-      <c r="G358" t="n">
         <v>7323.2</v>
       </c>
     </row>
@@ -9857,18 +8801,15 @@
         <v>5813.3</v>
       </c>
       <c r="C359" t="n">
-        <v>1254.22</v>
+        <v>1508.8</v>
       </c>
       <c r="D359" t="n">
-        <v>7067.51</v>
+        <v>7322.09</v>
       </c>
       <c r="E359" t="n">
-        <v>6665.8</v>
+        <v>6716.72</v>
       </c>
       <c r="F359" t="n">
-        <v>6650.68</v>
-      </c>
-      <c r="G359" t="n">
         <v>7322.09</v>
       </c>
     </row>
@@ -9882,18 +8823,15 @@
         <v>5817.68</v>
       </c>
       <c r="C360" t="n">
-        <v>1277.91</v>
+        <v>1503.31</v>
       </c>
       <c r="D360" t="n">
-        <v>7095.59</v>
+        <v>7320.98</v>
       </c>
       <c r="E360" t="n">
-        <v>6691.42</v>
+        <v>6736.5</v>
       </c>
       <c r="F360" t="n">
-        <v>6687.12</v>
-      </c>
-      <c r="G360" t="n">
         <v>7320.98</v>
       </c>
     </row>
@@ -9907,18 +8845,15 @@
         <v>5822.06</v>
       </c>
       <c r="C361" t="n">
-        <v>1301.6</v>
+        <v>1497.82</v>
       </c>
       <c r="D361" t="n">
-        <v>7123.66</v>
+        <v>7319.88</v>
       </c>
       <c r="E361" t="n">
-        <v>6711.21</v>
+        <v>6750.45</v>
       </c>
       <c r="F361" t="n">
-        <v>6723.57</v>
-      </c>
-      <c r="G361" t="n">
         <v>7319.88</v>
       </c>
     </row>
@@ -9932,18 +8867,15 @@
         <v>5826.44</v>
       </c>
       <c r="C362" t="n">
-        <v>1325.3</v>
+        <v>1492.33</v>
       </c>
       <c r="D362" t="n">
-        <v>7151.74</v>
+        <v>7318.77</v>
       </c>
       <c r="E362" t="n">
-        <v>6725.21</v>
+        <v>6758.61</v>
       </c>
       <c r="F362" t="n">
-        <v>6760.01</v>
-      </c>
-      <c r="G362" t="n">
         <v>7318.77</v>
       </c>
     </row>
@@ -9957,18 +8889,15 @@
         <v>5817.82</v>
       </c>
       <c r="C363" t="n">
-        <v>1361.99</v>
+        <v>1499.84</v>
       </c>
       <c r="D363" t="n">
-        <v>7179.81</v>
+        <v>7317.66</v>
       </c>
       <c r="E363" t="n">
-        <v>6736.6</v>
+        <v>6764.17</v>
       </c>
       <c r="F363" t="n">
-        <v>6796.46</v>
-      </c>
-      <c r="G363" t="n">
         <v>7317.66</v>
       </c>
     </row>
@@ -9982,18 +8911,15 @@
         <v>5809.19</v>
       </c>
       <c r="C364" t="n">
-        <v>1365.76</v>
+        <v>1507.36</v>
       </c>
       <c r="D364" t="n">
-        <v>7174.96</v>
+        <v>7316.55</v>
       </c>
       <c r="E364" t="n">
-        <v>6741.41</v>
+        <v>6769.73</v>
       </c>
       <c r="F364" t="n">
-        <v>6832.9</v>
-      </c>
-      <c r="G364" t="n">
         <v>7316.55</v>
       </c>
     </row>
@@ -10007,16 +8933,16 @@
         <v>5800.57</v>
       </c>
       <c r="C365" t="n">
-        <v>1369.53</v>
+        <v>1512.86</v>
       </c>
       <c r="D365" t="n">
-        <v>7170.1</v>
+        <v>7313.44</v>
       </c>
       <c r="E365" t="n">
-        <v>6746.22</v>
+        <v>6774.89</v>
       </c>
       <c r="F365" t="n">
-        <v>6869.35</v>
+        <v>7313.44</v>
       </c>
     </row>
     <row r="366">
@@ -10029,16 +8955,16 @@
         <v>5791.95</v>
       </c>
       <c r="C366" t="n">
-        <v>1373.3</v>
+        <v>1518.37</v>
       </c>
       <c r="D366" t="n">
-        <v>7165.25</v>
+        <v>7310.32</v>
       </c>
       <c r="E366" t="n">
-        <v>6748.79</v>
+        <v>6777.8</v>
       </c>
       <c r="F366" t="n">
-        <v>6894.57</v>
+        <v>7310.32</v>
       </c>
     </row>
   </sheetData>
@@ -10053,7 +8979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R315"/>
+  <dimension ref="A1:R316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27732,6 +26658,62 @@
         <v>50.5</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B316" t="n">
+        <v>681.24</v>
+      </c>
+      <c r="C316" t="n">
+        <v>533.74</v>
+      </c>
+      <c r="D316" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="E316" t="n">
+        <v>2317.73</v>
+      </c>
+      <c r="F316" t="n">
+        <v>484.25</v>
+      </c>
+      <c r="G316" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="H316" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J316" t="n">
+        <v>2808.25</v>
+      </c>
+      <c r="K316" t="n">
+        <v>190.48</v>
+      </c>
+      <c r="L316" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="M316" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N316" t="n">
+        <v>11</v>
+      </c>
+      <c r="O316" t="n">
+        <v>7277.99</v>
+      </c>
+      <c r="P316" t="n">
+        <v>1134.01</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>7294.75</v>
+      </c>
+      <c r="R316" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_hydro_storage.xlsx
+++ b/output/Data and Chart Outputs/au_hydro_storage.xlsx
@@ -152,7 +152,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tasmania hydro energy in storage (Hydro Tasmania) - water year (Oct-Sep), data to 2026-10-05</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Tasmania hydro energy in storage (Hydro Tasmania) - water year (Oct-Sep), data to 2026-10-26</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -264,7 +265,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,7 +765,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tasmania (Hydro Tasmania's storages - the NEM's largest hydro system), weekly, 28 Sep 2020 to 05 Oct 2026. Snowy Hydro (NSW/VIC) does not publish a storage series.</t>
+          <t>Tasmania (Hydro Tasmania's storages - the NEM's largest hydro system), weekly, 28 Sep 2020 to 26 Oct 2026. Snowy Hydro (NSW/VIC) does not publish a storage series.</t>
         </is>
       </c>
     </row>
@@ -1013,6 +1014,9 @@
       <c r="F7" t="n">
         <v>7045.88</v>
       </c>
+      <c r="G7" t="n">
+        <v>7291.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1035,6 +1039,9 @@
       <c r="F8" t="n">
         <v>7085.28</v>
       </c>
+      <c r="G8" t="n">
+        <v>7287.62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1057,6 +1064,9 @@
       <c r="F9" t="n">
         <v>7124.69</v>
       </c>
+      <c r="G9" t="n">
+        <v>7284.06</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1079,6 +1089,9 @@
       <c r="F10" t="n">
         <v>7164.09</v>
       </c>
+      <c r="G10" t="n">
+        <v>7280.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1101,6 +1114,9 @@
       <c r="F11" t="n">
         <v>7203.49</v>
       </c>
+      <c r="G11" t="n">
+        <v>7276.94</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1123,6 +1139,9 @@
       <c r="F12" t="n">
         <v>7242.89</v>
       </c>
+      <c r="G12" t="n">
+        <v>7273.37</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1145,6 +1164,9 @@
       <c r="F13" t="n">
         <v>7282.3</v>
       </c>
+      <c r="G13" t="n">
+        <v>7269.81</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1167,6 +1189,9 @@
       <c r="F14" t="n">
         <v>7321.7</v>
       </c>
+      <c r="G14" t="n">
+        <v>7279.05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1189,6 +1214,9 @@
       <c r="F15" t="n">
         <v>7326.57</v>
       </c>
+      <c r="G15" t="n">
+        <v>7288.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1211,6 +1239,9 @@
       <c r="F16" t="n">
         <v>7331.45</v>
       </c>
+      <c r="G16" t="n">
+        <v>7297.54</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1233,6 +1264,9 @@
       <c r="F17" t="n">
         <v>7336.32</v>
       </c>
+      <c r="G17" t="n">
+        <v>7306.78</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1255,6 +1289,9 @@
       <c r="F18" t="n">
         <v>7341.2</v>
       </c>
+      <c r="G18" t="n">
+        <v>7316.02</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1277,6 +1314,9 @@
       <c r="F19" t="n">
         <v>7346.07</v>
       </c>
+      <c r="G19" t="n">
+        <v>7325.27</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1299,6 +1339,9 @@
       <c r="F20" t="n">
         <v>7350.95</v>
       </c>
+      <c r="G20" t="n">
+        <v>7334.51</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1321,6 +1364,9 @@
       <c r="F21" t="n">
         <v>7355.82</v>
       </c>
+      <c r="G21" t="n">
+        <v>7323.72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1343,6 +1389,9 @@
       <c r="F22" t="n">
         <v>7366.06</v>
       </c>
+      <c r="G22" t="n">
+        <v>7312.93</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1365,6 +1414,9 @@
       <c r="F23" t="n">
         <v>7376.31</v>
       </c>
+      <c r="G23" t="n">
+        <v>7302.14</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1387,6 +1439,9 @@
       <c r="F24" t="n">
         <v>7386.55</v>
       </c>
+      <c r="G24" t="n">
+        <v>7291.34</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1409,6 +1464,9 @@
       <c r="F25" t="n">
         <v>7396.8</v>
       </c>
+      <c r="G25" t="n">
+        <v>7280.55</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1431,6 +1489,9 @@
       <c r="F26" t="n">
         <v>7407.04</v>
       </c>
+      <c r="G26" t="n">
+        <v>7269.76</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1452,6 +1513,9 @@
       </c>
       <c r="F27" t="n">
         <v>7417.29</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7258.97</v>
       </c>
     </row>
     <row r="28">
@@ -8979,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R316"/>
+  <dimension ref="A1:R319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26714,6 +26778,174 @@
         <v>50.4</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B317" t="n">
+        <v>675.49</v>
+      </c>
+      <c r="C317" t="n">
+        <v>535.4299999999999</v>
+      </c>
+      <c r="D317" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="E317" t="n">
+        <v>2304.7</v>
+      </c>
+      <c r="F317" t="n">
+        <v>477.76</v>
+      </c>
+      <c r="G317" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="H317" t="n">
+        <v>103.49</v>
+      </c>
+      <c r="I317" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J317" t="n">
+        <v>2805.7</v>
+      </c>
+      <c r="K317" t="n">
+        <v>190.87</v>
+      </c>
+      <c r="L317" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="M317" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="N317" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="O317" t="n">
+        <v>7250.16</v>
+      </c>
+      <c r="P317" t="n">
+        <v>1126.57</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>7269.81</v>
+      </c>
+      <c r="R317" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B318" t="n">
+        <v>686.36</v>
+      </c>
+      <c r="C318" t="n">
+        <v>540.14</v>
+      </c>
+      <c r="D318" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="E318" t="n">
+        <v>2307.7</v>
+      </c>
+      <c r="F318" t="n">
+        <v>472.73</v>
+      </c>
+      <c r="G318" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="H318" t="n">
+        <v>114.22</v>
+      </c>
+      <c r="I318" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J318" t="n">
+        <v>2818.65</v>
+      </c>
+      <c r="K318" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="L318" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="M318" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="N318" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="O318" t="n">
+        <v>7305.32</v>
+      </c>
+      <c r="P318" t="n">
+        <v>1166.1</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>7334.51</v>
+      </c>
+      <c r="R318" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B319" t="n">
+        <v>674.84</v>
+      </c>
+      <c r="C319" t="n">
+        <v>544.1900000000001</v>
+      </c>
+      <c r="D319" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="E319" t="n">
+        <v>2298.85</v>
+      </c>
+      <c r="F319" t="n">
+        <v>468.74</v>
+      </c>
+      <c r="G319" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="H319" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J319" t="n">
+        <v>2788.51</v>
+      </c>
+      <c r="K319" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="L319" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="M319" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="N319" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="O319" t="n">
+        <v>7230.82</v>
+      </c>
+      <c r="P319" t="n">
+        <v>1130.54</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>7258.97</v>
+      </c>
+      <c r="R319" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
